--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129502197</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129502192</v>
+        <v>129502195</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583114</v>
+        <v>583175</v>
       </c>
       <c r="R3" t="n">
-        <v>7014270</v>
+        <v>7014165</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129502234</v>
+        <v>129495403</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583081</v>
+        <v>583206</v>
       </c>
       <c r="R4" t="n">
-        <v>7014394</v>
+        <v>7014144</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,57 +959,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502225</v>
+        <v>129502244</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583072</v>
+        <v>583177</v>
       </c>
       <c r="R5" t="n">
-        <v>7014226</v>
+        <v>7014165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1040,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1048,21 +1057,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1079,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502237</v>
+        <v>129502188</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,7 +1111,7 @@
         <v>583139</v>
       </c>
       <c r="R6" t="n">
-        <v>7014115</v>
+        <v>7014270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,12 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502195</v>
+        <v>129502190</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>91513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583175</v>
+        <v>583136</v>
       </c>
       <c r="R7" t="n">
-        <v>7014165</v>
+        <v>7014210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,53 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129495403</v>
+        <v>129502212</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>92002</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583206</v>
+        <v>583184</v>
       </c>
       <c r="R8" t="n">
-        <v>7014144</v>
+        <v>7014173</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,44 +1352,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129502236</v>
+        <v>129502199</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>92267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1410,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583058</v>
+        <v>583141</v>
       </c>
       <c r="R9" t="n">
-        <v>7014379</v>
+        <v>7014282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,12 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1472,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129502235</v>
+        <v>129495400</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,37 +1472,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583064</v>
+        <v>583183</v>
       </c>
       <c r="R10" t="n">
-        <v>7014430</v>
+        <v>7014604</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1537,12 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1557,44 +1546,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129502182</v>
+        <v>129502254</v>
       </c>
       <c r="B11" t="n">
-        <v>91509</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1604,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583174</v>
+        <v>583140</v>
       </c>
       <c r="R11" t="n">
-        <v>7014597</v>
+        <v>7014221</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,12 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1666,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129502221</v>
+        <v>129502189</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>91513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1701,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583411</v>
+        <v>583132</v>
       </c>
       <c r="R12" t="n">
-        <v>7014380</v>
+        <v>7014235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,17 +1720,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1768,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129502251</v>
+        <v>129502186</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1803,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583055</v>
+        <v>583115</v>
       </c>
       <c r="R13" t="n">
-        <v>7014329</v>
+        <v>7014341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1833,12 +1817,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1865,32 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129502205</v>
+        <v>129502200</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>92267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1900,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583055</v>
+        <v>583132</v>
       </c>
       <c r="R14" t="n">
-        <v>7014357</v>
+        <v>7014237</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,12 +1914,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1962,49 +1946,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129502244</v>
+        <v>129502201</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>92267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583177</v>
+        <v>583149</v>
       </c>
       <c r="R15" t="n">
-        <v>7014165</v>
+        <v>7014188</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,7 +2025,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2064,7 +2043,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129502226</v>
+        <v>129495410</v>
       </c>
       <c r="B16" t="n">
         <v>80149</v>
@@ -2095,17 +2074,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583156</v>
+        <v>583139</v>
       </c>
       <c r="R16" t="n">
-        <v>7014249</v>
+        <v>7014123</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2129,12 +2108,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2143,82 +2122,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129502188</v>
+        <v>129495408</v>
       </c>
       <c r="B17" t="n">
-        <v>91509</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583139</v>
+        <v>583204</v>
       </c>
       <c r="R17" t="n">
-        <v>7014270</v>
+        <v>7014157</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2262,60 +2225,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129502190</v>
+        <v>129495406</v>
       </c>
       <c r="B18" t="n">
-        <v>91509</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583136</v>
+        <v>583170</v>
       </c>
       <c r="R18" t="n">
-        <v>7014210</v>
+        <v>7014239</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2359,60 +2322,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129502215</v>
+        <v>129495405</v>
       </c>
       <c r="B19" t="n">
-        <v>91843</v>
+        <v>92002</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583175</v>
+        <v>583128</v>
       </c>
       <c r="R19" t="n">
-        <v>7014579</v>
+        <v>7014123</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2436,12 +2399,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2456,22 +2419,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129502247</v>
+        <v>129502196</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2479,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2503,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583367</v>
+        <v>583143</v>
       </c>
       <c r="R20" t="n">
-        <v>7014331</v>
+        <v>7014216</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2533,12 +2496,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2565,32 +2528,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129502209</v>
+        <v>129502220</v>
       </c>
       <c r="B21" t="n">
-        <v>80053</v>
+        <v>91847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2600,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583167</v>
+        <v>583103</v>
       </c>
       <c r="R21" t="n">
-        <v>7014583</v>
+        <v>7014293</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,12 +2593,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2662,48 +2625,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129495400</v>
+        <v>129502202</v>
       </c>
       <c r="B22" t="n">
-        <v>91545</v>
+        <v>92267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583183</v>
+        <v>583172</v>
       </c>
       <c r="R22" t="n">
-        <v>7014604</v>
+        <v>7014182</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2747,22 +2710,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129502206</v>
+        <v>129502255</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2770,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2794,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583074</v>
+        <v>583197</v>
       </c>
       <c r="R23" t="n">
-        <v>7014351</v>
+        <v>7014149</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2824,12 +2787,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2856,32 +2819,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129502199</v>
+        <v>129502252</v>
       </c>
       <c r="B24" t="n">
-        <v>92263</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2891,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583141</v>
+        <v>583105</v>
       </c>
       <c r="R24" t="n">
-        <v>7014282</v>
+        <v>7014309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2953,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129502194</v>
+        <v>129495407</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2964,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583050</v>
+        <v>583122</v>
       </c>
       <c r="R25" t="n">
-        <v>7014242</v>
+        <v>7014418</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3018,12 +2981,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3038,60 +3001,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129502212</v>
+        <v>129495402</v>
       </c>
       <c r="B26" t="n">
-        <v>91998</v>
+        <v>91549</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583184</v>
+        <v>583080</v>
       </c>
       <c r="R26" t="n">
-        <v>7014173</v>
+        <v>7014300</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3135,60 +3098,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129502211</v>
+        <v>129495404</v>
       </c>
       <c r="B27" t="n">
-        <v>91998</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583055</v>
+        <v>583146</v>
       </c>
       <c r="R27" t="n">
-        <v>7014372</v>
+        <v>7014362</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3212,12 +3175,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3232,22 +3195,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129502230</v>
+        <v>129495413</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3255,37 +3218,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583330</v>
+        <v>583083</v>
       </c>
       <c r="R28" t="n">
-        <v>7014339</v>
+        <v>7014314</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3309,12 +3272,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,44 +3292,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129502238</v>
+        <v>129502253</v>
       </c>
       <c r="B29" t="n">
-        <v>80185</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3376,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583155</v>
+        <v>583143</v>
       </c>
       <c r="R29" t="n">
-        <v>7014250</v>
+        <v>7014258</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3406,12 +3369,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3420,24 +3383,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3454,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129502228</v>
+        <v>129495401</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>91549</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3465,37 +3412,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583073</v>
+        <v>583128</v>
       </c>
       <c r="R30" t="n">
-        <v>7014431</v>
+        <v>7014123</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3519,12 +3466,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3533,44 +3480,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129502254</v>
+        <v>129495411</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3578,37 +3509,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583140</v>
+        <v>583068</v>
       </c>
       <c r="R31" t="n">
-        <v>7014221</v>
+        <v>7014294</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3652,22 +3583,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129502223</v>
+        <v>129495409</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3675,37 +3606,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583189</v>
+        <v>583174</v>
       </c>
       <c r="R32" t="n">
-        <v>7014163</v>
+        <v>7014111</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3729,17 +3660,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska spår på gran</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3754,44 +3680,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129502186</v>
+        <v>129502213</v>
       </c>
       <c r="B33" t="n">
-        <v>91509</v>
+        <v>92002</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3801,10 +3727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583115</v>
+        <v>583198</v>
       </c>
       <c r="R33" t="n">
-        <v>7014341</v>
+        <v>7014144</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3845,6 +3771,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3863,32 +3790,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502189</v>
+        <v>129502224</v>
       </c>
       <c r="B34" t="n">
-        <v>91509</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3898,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583132</v>
+        <v>583151</v>
       </c>
       <c r="R34" t="n">
-        <v>7014235</v>
+        <v>7014252</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3942,8 +3869,24 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -3960,32 +3903,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129502200</v>
+        <v>129502234</v>
       </c>
       <c r="B35" t="n">
-        <v>92263</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3995,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583132</v>
+        <v>583081</v>
       </c>
       <c r="R35" t="n">
-        <v>7014237</v>
+        <v>7014394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4025,12 +3968,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,32 +4000,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129502208</v>
+        <v>129502192</v>
       </c>
       <c r="B36" t="n">
-        <v>80053</v>
+        <v>91549</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4092,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583304</v>
+        <v>583114</v>
       </c>
       <c r="R36" t="n">
-        <v>7014295</v>
+        <v>7014270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4154,32 +4097,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129502201</v>
+        <v>129502225</v>
       </c>
       <c r="B37" t="n">
-        <v>92263</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4189,10 +4132,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583149</v>
+        <v>583072</v>
       </c>
       <c r="R37" t="n">
-        <v>7014188</v>
+        <v>7014226</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4219,12 +4162,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4233,8 +4176,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4251,10 +4210,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129502216</v>
+        <v>129502237</v>
       </c>
       <c r="B38" t="n">
-        <v>91843</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4262,21 +4221,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4286,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583173</v>
+        <v>583139</v>
       </c>
       <c r="R38" t="n">
-        <v>7014589</v>
+        <v>7014115</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4348,49 +4307,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502243</v>
+        <v>129502182</v>
       </c>
       <c r="B39" t="n">
-        <v>98712</v>
+        <v>91513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583046</v>
+        <v>583174</v>
       </c>
       <c r="R39" t="n">
-        <v>7014393</v>
+        <v>7014597</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4431,7 +4386,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4450,48 +4404,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129495405</v>
+        <v>129502221</v>
       </c>
       <c r="B40" t="n">
-        <v>91998</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583128</v>
+        <v>583411</v>
       </c>
       <c r="R40" t="n">
-        <v>7014123</v>
+        <v>7014380</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4515,12 +4469,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4535,19 +4494,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129495408</v>
+        <v>129502236</v>
       </c>
       <c r="B41" t="n">
         <v>80149</v>
@@ -4578,17 +4537,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583204</v>
+        <v>583058</v>
       </c>
       <c r="R41" t="n">
-        <v>7014157</v>
+        <v>7014379</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4612,12 +4571,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4632,19 +4591,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129495410</v>
+        <v>129502235</v>
       </c>
       <c r="B42" t="n">
         <v>80149</v>
@@ -4675,17 +4634,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583139</v>
+        <v>583064</v>
       </c>
       <c r="R42" t="n">
-        <v>7014123</v>
+        <v>7014430</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4709,12 +4668,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4729,22 +4688,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129495406</v>
+        <v>129502215</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>91847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4752,37 +4711,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583170</v>
+        <v>583175</v>
       </c>
       <c r="R43" t="n">
-        <v>7014239</v>
+        <v>7014579</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4806,12 +4765,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4826,22 +4785,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502196</v>
+        <v>129502247</v>
       </c>
       <c r="B44" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4849,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4873,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583143</v>
+        <v>583367</v>
       </c>
       <c r="R44" t="n">
-        <v>7014216</v>
+        <v>7014331</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4903,12 +4862,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4935,32 +4894,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502227</v>
+        <v>129502209</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4970,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583045</v>
+        <v>583167</v>
       </c>
       <c r="R45" t="n">
-        <v>7014432</v>
+        <v>7014583</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5014,24 +4973,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5048,10 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502231</v>
+        <v>129502205</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5059,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5083,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583345</v>
+        <v>583055</v>
       </c>
       <c r="R46" t="n">
-        <v>7014389</v>
+        <v>7014357</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5145,32 +5088,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502184</v>
+        <v>129502251</v>
       </c>
       <c r="B47" t="n">
-        <v>91509</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5180,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583134</v>
+        <v>583055</v>
       </c>
       <c r="R47" t="n">
-        <v>7014134</v>
+        <v>7014329</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5242,10 +5185,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502249</v>
+        <v>129502226</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5253,21 +5196,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5277,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583114</v>
+        <v>583156</v>
       </c>
       <c r="R48" t="n">
-        <v>7014512</v>
+        <v>7014249</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5321,8 +5264,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5339,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502232</v>
+        <v>129502206</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5350,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5374,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583323</v>
+        <v>583074</v>
       </c>
       <c r="R49" t="n">
-        <v>7014267</v>
+        <v>7014351</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5436,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502239</v>
+        <v>129502230</v>
       </c>
       <c r="B50" t="n">
-        <v>58097</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5471,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583168</v>
+        <v>583330</v>
       </c>
       <c r="R50" t="n">
-        <v>7014188</v>
+        <v>7014339</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5533,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502220</v>
+        <v>129502194</v>
       </c>
       <c r="B51" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5544,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5568,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583103</v>
+        <v>583050</v>
       </c>
       <c r="R51" t="n">
-        <v>7014293</v>
+        <v>7014242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5598,12 +5557,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5630,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502229</v>
+        <v>129502211</v>
       </c>
       <c r="B52" t="n">
-        <v>80149</v>
+        <v>92002</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5665,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583107</v>
+        <v>583055</v>
       </c>
       <c r="R52" t="n">
-        <v>7014481</v>
+        <v>7014372</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5701,11 +5660,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5732,32 +5686,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129502246</v>
+        <v>129502238</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>80185</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,10 +5721,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>583392</v>
+        <v>583155</v>
       </c>
       <c r="R53" t="n">
-        <v>7014349</v>
+        <v>7014250</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5811,8 +5765,24 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -5829,10 +5799,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129502203</v>
+        <v>129502228</v>
       </c>
       <c r="B54" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5840,21 +5810,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5864,10 +5834,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583138</v>
+        <v>583073</v>
       </c>
       <c r="R54" t="n">
-        <v>7014232</v>
+        <v>7014431</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5908,8 +5878,24 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -5926,10 +5912,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129502248</v>
+        <v>129502223</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5937,21 +5923,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5961,10 +5947,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>583117</v>
+        <v>583189</v>
       </c>
       <c r="R55" t="n">
-        <v>7014262</v>
+        <v>7014163</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5997,6 +5983,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska spår på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6023,32 +6014,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129502180</v>
+        <v>129502208</v>
       </c>
       <c r="B56" t="n">
-        <v>83012</v>
+        <v>80053</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6058,10 +6049,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>583051</v>
+        <v>583304</v>
       </c>
       <c r="R56" t="n">
-        <v>7014327</v>
+        <v>7014295</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6120,10 +6111,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502240</v>
+        <v>129502243</v>
       </c>
       <c r="B57" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6150,7 +6141,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6159,10 +6150,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583138</v>
+        <v>583046</v>
       </c>
       <c r="R57" t="n">
-        <v>7014124</v>
+        <v>7014393</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6213,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502245</v>
+        <v>129502216</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>91847</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6233,21 +6224,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6257,10 +6248,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583158</v>
+        <v>583173</v>
       </c>
       <c r="R58" t="n">
-        <v>7014222</v>
+        <v>7014589</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6319,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502202</v>
+        <v>129502231</v>
       </c>
       <c r="B59" t="n">
-        <v>92263</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6354,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583172</v>
+        <v>583345</v>
       </c>
       <c r="R59" t="n">
-        <v>7014182</v>
+        <v>7014389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6384,12 +6375,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6416,7 +6407,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129495407</v>
+        <v>129502227</v>
       </c>
       <c r="B60" t="n">
         <v>80149</v>
@@ -6447,17 +6438,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583122</v>
+        <v>583045</v>
       </c>
       <c r="R60" t="n">
-        <v>7014418</v>
+        <v>7014432</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6481,12 +6472,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6495,66 +6486,82 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129495402</v>
+        <v>129502184</v>
       </c>
       <c r="B61" t="n">
-        <v>91545</v>
+        <v>91513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583080</v>
+        <v>583134</v>
       </c>
       <c r="R61" t="n">
-        <v>7014300</v>
+        <v>7014134</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6578,12 +6585,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6598,19 +6605,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502252</v>
+        <v>129502249</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -6645,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583105</v>
+        <v>583114</v>
       </c>
       <c r="R62" t="n">
-        <v>7014309</v>
+        <v>7014512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6675,12 +6682,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6707,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502255</v>
+        <v>129502232</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6718,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6742,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583197</v>
+        <v>583323</v>
       </c>
       <c r="R63" t="n">
-        <v>7014149</v>
+        <v>7014267</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6772,12 +6779,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6804,49 +6811,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502242</v>
+        <v>129502239</v>
       </c>
       <c r="B64" t="n">
-        <v>98712</v>
+        <v>58097</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583095</v>
+        <v>583168</v>
       </c>
       <c r="R64" t="n">
-        <v>7014377</v>
+        <v>7014188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6887,7 +6890,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6906,32 +6908,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502198</v>
+        <v>129502229</v>
       </c>
       <c r="B65" t="n">
-        <v>92263</v>
+        <v>80149</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6941,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583192</v>
+        <v>583107</v>
       </c>
       <c r="R65" t="n">
-        <v>7014120</v>
+        <v>7014481</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6977,6 +6979,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7003,10 +7010,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502218</v>
+        <v>129502246</v>
       </c>
       <c r="B66" t="n">
-        <v>91843</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7014,21 +7021,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7038,10 +7045,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583050</v>
+        <v>583392</v>
       </c>
       <c r="R66" t="n">
-        <v>7014244</v>
+        <v>7014349</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7100,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129495404</v>
+        <v>129502180</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>83012</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7111,37 +7118,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583146</v>
+        <v>583051</v>
       </c>
       <c r="R67" t="n">
-        <v>7014362</v>
+        <v>7014327</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7165,12 +7172,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7185,19 +7192,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502250</v>
+        <v>129502248</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7232,10 +7239,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583068</v>
+        <v>583117</v>
       </c>
       <c r="R68" t="n">
-        <v>7014344</v>
+        <v>7014262</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7294,10 +7301,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129502193</v>
+        <v>129502203</v>
       </c>
       <c r="B69" t="n">
-        <v>91545</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7305,34 +7312,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583174</v>
+        <v>583138</v>
       </c>
       <c r="R69" t="n">
-        <v>7014589</v>
+        <v>7014232</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7391,10 +7406,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502204</v>
+        <v>129502245</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7402,21 +7417,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7426,10 +7441,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583061</v>
+        <v>583158</v>
       </c>
       <c r="R70" t="n">
-        <v>7014418</v>
+        <v>7014222</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7488,48 +7503,52 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129495413</v>
+        <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583083</v>
+        <v>583138</v>
       </c>
       <c r="R71" t="n">
-        <v>7014314</v>
+        <v>7014124</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7553,12 +7572,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7567,63 +7586,68 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502253</v>
+        <v>129502242</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583143</v>
+        <v>583095</v>
       </c>
       <c r="R72" t="n">
-        <v>7014258</v>
+        <v>7014377</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7650,12 +7674,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7664,6 +7688,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7682,10 +7707,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502217</v>
+        <v>129502218</v>
       </c>
       <c r="B73" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7717,10 +7742,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583047</v>
+        <v>583050</v>
       </c>
       <c r="R73" t="n">
-        <v>7014432</v>
+        <v>7014244</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7779,48 +7804,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129495401</v>
+        <v>129502198</v>
       </c>
       <c r="B74" t="n">
-        <v>91545</v>
+        <v>92267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583128</v>
+        <v>583192</v>
       </c>
       <c r="R74" t="n">
-        <v>7014123</v>
+        <v>7014120</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7844,12 +7869,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7864,22 +7889,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502233</v>
+        <v>129502250</v>
       </c>
       <c r="B75" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7887,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7914,7 +7939,7 @@
         <v>583068</v>
       </c>
       <c r="R75" t="n">
-        <v>7014398</v>
+        <v>7014344</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7947,11 +7972,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7978,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502214</v>
+        <v>129502193</v>
       </c>
       <c r="B76" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7989,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8013,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583052</v>
+        <v>583174</v>
       </c>
       <c r="R76" t="n">
-        <v>7014374</v>
+        <v>7014589</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8075,10 +8095,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129502256</v>
+        <v>129502204</v>
       </c>
       <c r="B77" t="n">
-        <v>82878</v>
+        <v>57724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8086,21 +8106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8110,10 +8130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583110</v>
+        <v>583061</v>
       </c>
       <c r="R77" t="n">
-        <v>7014519</v>
+        <v>7014418</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8172,10 +8192,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129495409</v>
+        <v>129502217</v>
       </c>
       <c r="B78" t="n">
-        <v>80149</v>
+        <v>91847</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8183,37 +8203,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583174</v>
+        <v>583047</v>
       </c>
       <c r="R78" t="n">
-        <v>7014111</v>
+        <v>7014432</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8237,12 +8257,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8257,22 +8277,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129495411</v>
+        <v>129502256</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>82878</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8280,37 +8300,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583068</v>
+        <v>583110</v>
       </c>
       <c r="R79" t="n">
-        <v>7014294</v>
+        <v>7014519</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8334,12 +8354,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8354,22 +8374,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502224</v>
+        <v>129502214</v>
       </c>
       <c r="B80" t="n">
-        <v>80149</v>
+        <v>91847</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8377,21 +8397,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8401,10 +8421,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583151</v>
+        <v>583052</v>
       </c>
       <c r="R80" t="n">
-        <v>7014252</v>
+        <v>7014374</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8431,12 +8451,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8445,24 +8465,8 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -8479,32 +8483,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502241</v>
+        <v>129502233</v>
       </c>
       <c r="B81" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8514,7 +8518,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583076</v>
+        <v>583068</v>
       </c>
       <c r="R81" t="n">
         <v>7014398</v>
@@ -8552,13 +8556,17 @@
           <t>2025-11-01</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>apotecier</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8580,7 +8588,7 @@
         <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8674,10 +8682,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129502213</v>
+        <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>91998</v>
+        <v>98716</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8685,21 +8693,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8709,10 +8717,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583198</v>
+        <v>583076</v>
       </c>
       <c r="R83" t="n">
-        <v>7014144</v>
+        <v>7014398</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8739,12 +8747,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129502197</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129502195</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -971,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502244</v>
+        <v>129502188</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>91514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583177</v>
+        <v>583139</v>
       </c>
       <c r="R5" t="n">
-        <v>7014165</v>
+        <v>7014270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1050,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502188</v>
+        <v>129502190</v>
       </c>
       <c r="B6" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583139</v>
+        <v>583136</v>
       </c>
       <c r="R6" t="n">
-        <v>7014270</v>
+        <v>7014210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1165,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502190</v>
+        <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>91513</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583136</v>
+        <v>583177</v>
       </c>
       <c r="R7" t="n">
-        <v>7014210</v>
+        <v>7014165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>129502212</v>
       </c>
       <c r="B8" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129502199</v>
       </c>
       <c r="B9" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129495400</v>
       </c>
       <c r="B10" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129502189</v>
       </c>
       <c r="B12" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129502186</v>
       </c>
       <c r="B13" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>129502200</v>
       </c>
       <c r="B14" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129502201</v>
       </c>
       <c r="B15" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495410</v>
+        <v>129502196</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,37 +2054,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583139</v>
+        <v>583143</v>
       </c>
       <c r="R16" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495408</v>
+        <v>129495405</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>92003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583204</v>
+        <v>583128</v>
       </c>
       <c r="R17" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495406</v>
+        <v>129495408</v>
       </c>
       <c r="B18" t="n">
         <v>80149</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583170</v>
+        <v>583204</v>
       </c>
       <c r="R18" t="n">
-        <v>7014239</v>
+        <v>7014157</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,32 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495405</v>
+        <v>129495410</v>
       </c>
       <c r="B19" t="n">
-        <v>92002</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583128</v>
+        <v>583139</v>
       </c>
       <c r="R19" t="n">
         <v>7014123</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129502196</v>
+        <v>129495406</v>
       </c>
       <c r="B20" t="n">
-        <v>91549</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583143</v>
+        <v>583170</v>
       </c>
       <c r="R20" t="n">
-        <v>7014216</v>
+        <v>7014239</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>129502220</v>
       </c>
       <c r="B21" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129502202</v>
       </c>
       <c r="B22" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>129495402</v>
       </c>
       <c r="B26" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R28" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R29" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
         <v>129495401</v>
       </c>
       <c r="B30" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129495411</v>
+        <v>129502224</v>
       </c>
       <c r="B31" t="n">
         <v>80149</v>
@@ -3529,17 +3529,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583068</v>
+        <v>583151</v>
       </c>
       <c r="R31" t="n">
-        <v>7014294</v>
+        <v>7014252</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,66 +3577,82 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129495409</v>
+        <v>129502213</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>92003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583174</v>
+        <v>583198</v>
       </c>
       <c r="R32" t="n">
-        <v>7014111</v>
+        <v>7014144</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3674,66 +3690,67 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129502213</v>
+        <v>129495409</v>
       </c>
       <c r="B33" t="n">
-        <v>92002</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583198</v>
+        <v>583174</v>
       </c>
       <c r="R33" t="n">
-        <v>7014144</v>
+        <v>7014111</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3771,26 +3788,25 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502224</v>
+        <v>129495411</v>
       </c>
       <c r="B34" t="n">
         <v>80149</v>
@@ -3821,17 +3837,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583151</v>
+        <v>583068</v>
       </c>
       <c r="R34" t="n">
-        <v>7014252</v>
+        <v>7014294</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3869,34 +3885,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4003,7 +4003,7 @@
         <v>129502192</v>
       </c>
       <c r="B36" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129502225</v>
+        <v>129502237</v>
       </c>
       <c r="B37" t="n">
         <v>80149</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583072</v>
+        <v>583139</v>
       </c>
       <c r="R37" t="n">
-        <v>7014226</v>
+        <v>7014115</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4176,24 +4176,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4210,7 +4194,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129502237</v>
+        <v>129502225</v>
       </c>
       <c r="B38" t="n">
         <v>80149</v>
@@ -4245,10 +4229,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583139</v>
+        <v>583072</v>
       </c>
       <c r="R38" t="n">
-        <v>7014115</v>
+        <v>7014226</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,8 +4273,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502182</v>
+        <v>129502236</v>
       </c>
       <c r="B39" t="n">
-        <v>91513</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583174</v>
+        <v>583058</v>
       </c>
       <c r="R39" t="n">
-        <v>7014597</v>
+        <v>7014379</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,32 +4404,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502221</v>
+        <v>129502182</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583411</v>
+        <v>583174</v>
       </c>
       <c r="R40" t="n">
-        <v>7014380</v>
+        <v>7014597</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4475,11 +4475,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4506,7 +4501,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502236</v>
+        <v>129502235</v>
       </c>
       <c r="B41" t="n">
         <v>80149</v>
@@ -4541,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583058</v>
+        <v>583064</v>
       </c>
       <c r="R41" t="n">
-        <v>7014379</v>
+        <v>7014430</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4603,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502235</v>
+        <v>129502221</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583064</v>
+        <v>583411</v>
       </c>
       <c r="R42" t="n">
-        <v>7014430</v>
+        <v>7014380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,6 +4669,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502215</v>
+        <v>129502209</v>
       </c>
       <c r="B43" t="n">
-        <v>91847</v>
+        <v>80053</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583175</v>
+        <v>583167</v>
       </c>
       <c r="R43" t="n">
-        <v>7014579</v>
+        <v>7014583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,32 +4894,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502209</v>
+        <v>129502251</v>
       </c>
       <c r="B45" t="n">
-        <v>80053</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583167</v>
+        <v>583055</v>
       </c>
       <c r="R45" t="n">
-        <v>7014583</v>
+        <v>7014329</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4991,10 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502205</v>
+        <v>129502226</v>
       </c>
       <c r="B46" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5002,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R46" t="n">
-        <v>7014357</v>
+        <v>7014249</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5070,8 +5070,24 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5088,10 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502251</v>
+        <v>129502215</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5099,21 +5115,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5123,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583055</v>
+        <v>583175</v>
       </c>
       <c r="R47" t="n">
-        <v>7014329</v>
+        <v>7014579</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5185,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502226</v>
+        <v>129502205</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5196,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5220,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014249</v>
+        <v>7014357</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,24 +5280,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502206</v>
+        <v>129502230</v>
       </c>
       <c r="B49" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583074</v>
+        <v>583330</v>
       </c>
       <c r="R49" t="n">
-        <v>7014351</v>
+        <v>7014339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502230</v>
+        <v>129502194</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5406,21 +5406,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583330</v>
+        <v>583050</v>
       </c>
       <c r="R50" t="n">
-        <v>7014339</v>
+        <v>7014242</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,32 +5492,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502194</v>
+        <v>129502211</v>
       </c>
       <c r="B51" t="n">
-        <v>91549</v>
+        <v>92003</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583050</v>
+        <v>583055</v>
       </c>
       <c r="R51" t="n">
-        <v>7014242</v>
+        <v>7014372</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502211</v>
+        <v>129502206</v>
       </c>
       <c r="B52" t="n">
-        <v>92002</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583055</v>
+        <v>583074</v>
       </c>
       <c r="R52" t="n">
-        <v>7014372</v>
+        <v>7014351</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,49 +6111,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502243</v>
+        <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>98716</v>
+        <v>91848</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583046</v>
+        <v>583173</v>
       </c>
       <c r="R57" t="n">
-        <v>7014393</v>
+        <v>7014589</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,7 +6190,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6213,45 +6208,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502216</v>
+        <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>91847</v>
+        <v>98724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583173</v>
+        <v>583046</v>
       </c>
       <c r="R58" t="n">
-        <v>7014589</v>
+        <v>7014393</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6292,6 +6291,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>129502184</v>
       </c>
       <c r="B61" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502249</v>
+        <v>129502232</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583114</v>
+        <v>583323</v>
       </c>
       <c r="R62" t="n">
-        <v>7014512</v>
+        <v>7014267</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R63" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B65" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R65" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,11 +6979,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7010,10 +7005,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7021,21 +7016,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7045,10 +7040,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R66" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7081,6 +7076,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7506,7 +7506,7 @@
         <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7605,49 +7605,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B72" t="n">
-        <v>98716</v>
+        <v>92268</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R72" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7688,7 +7684,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7710,7 +7705,7 @@
         <v>129502218</v>
       </c>
       <c r="B73" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7804,45 +7799,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>92267</v>
+        <v>98724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R74" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,6 +7882,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>129502193</v>
       </c>
       <c r="B76" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>129502217</v>
       </c>
       <c r="B78" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502256</v>
+        <v>129502214</v>
       </c>
       <c r="B79" t="n">
-        <v>82878</v>
+        <v>91848</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583110</v>
+        <v>583052</v>
       </c>
       <c r="R79" t="n">
-        <v>7014519</v>
+        <v>7014374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8386,10 +8386,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502214</v>
+        <v>129502233</v>
       </c>
       <c r="B80" t="n">
-        <v>91847</v>
+        <v>80149</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8397,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583052</v>
+        <v>583068</v>
       </c>
       <c r="R80" t="n">
-        <v>7014374</v>
+        <v>7014398</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8457,6 +8457,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8483,10 +8488,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502233</v>
+        <v>129502256</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>82878</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8494,21 +8499,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8518,10 +8523,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583068</v>
+        <v>583110</v>
       </c>
       <c r="R81" t="n">
-        <v>7014398</v>
+        <v>7014519</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8554,11 +8559,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8588,7 +8588,7 @@
         <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -971,45 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502188</v>
+        <v>129502244</v>
       </c>
       <c r="B5" t="n">
-        <v>91514</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583139</v>
+        <v>583177</v>
       </c>
       <c r="R5" t="n">
-        <v>7014270</v>
+        <v>7014165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502190</v>
+        <v>129502188</v>
       </c>
       <c r="B6" t="n">
         <v>91514</v>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583136</v>
+        <v>583139</v>
       </c>
       <c r="R6" t="n">
-        <v>7014210</v>
+        <v>7014270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,49 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502244</v>
+        <v>129502190</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>91514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583177</v>
+        <v>583136</v>
       </c>
       <c r="R7" t="n">
-        <v>7014165</v>
+        <v>7014210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2043,48 +2043,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129502196</v>
+        <v>129495405</v>
       </c>
       <c r="B16" t="n">
-        <v>91550</v>
+        <v>92003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583143</v>
+        <v>583128</v>
       </c>
       <c r="R16" t="n">
-        <v>7014216</v>
+        <v>7014123</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495405</v>
+        <v>129495410</v>
       </c>
       <c r="B17" t="n">
-        <v>92003</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583128</v>
+        <v>583139</v>
       </c>
       <c r="R17" t="n">
         <v>7014123</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495410</v>
+        <v>129495406</v>
       </c>
       <c r="B19" t="n">
         <v>80149</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583139</v>
+        <v>583170</v>
       </c>
       <c r="R19" t="n">
-        <v>7014123</v>
+        <v>7014239</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495406</v>
+        <v>129502196</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583170</v>
+        <v>583143</v>
       </c>
       <c r="R20" t="n">
-        <v>7014239</v>
+        <v>7014216</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129502252</v>
+        <v>129495407</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583105</v>
+        <v>583122</v>
       </c>
       <c r="R24" t="n">
-        <v>7014309</v>
+        <v>7014418</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,22 +2904,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129495407</v>
+        <v>129502252</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583122</v>
+        <v>583105</v>
       </c>
       <c r="R25" t="n">
-        <v>7014418</v>
+        <v>7014309</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3498,32 +3498,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129502224</v>
+        <v>129502213</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>92003</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583151</v>
+        <v>583198</v>
       </c>
       <c r="R31" t="n">
-        <v>7014252</v>
+        <v>7014144</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3580,21 +3580,6 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3611,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129502213</v>
+        <v>129502224</v>
       </c>
       <c r="B32" t="n">
-        <v>92003</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3646,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583198</v>
+        <v>583151</v>
       </c>
       <c r="R32" t="n">
-        <v>7014144</v>
+        <v>7014252</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3693,6 +3678,21 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3709,7 +3709,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129495409</v>
+        <v>129495411</v>
       </c>
       <c r="B33" t="n">
         <v>80149</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R33" t="n">
-        <v>7014111</v>
+        <v>7014294</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3806,7 +3806,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129495411</v>
+        <v>129495409</v>
       </c>
       <c r="B34" t="n">
         <v>80149</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R34" t="n">
-        <v>7014294</v>
+        <v>7014111</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129502234</v>
+        <v>129502192</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583081</v>
+        <v>583114</v>
       </c>
       <c r="R35" t="n">
-        <v>7014394</v>
+        <v>7014270</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129502192</v>
+        <v>129502234</v>
       </c>
       <c r="B36" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583114</v>
+        <v>583081</v>
       </c>
       <c r="R36" t="n">
-        <v>7014270</v>
+        <v>7014394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502236</v>
+        <v>129502221</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4318,21 +4318,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583058</v>
+        <v>583411</v>
       </c>
       <c r="R39" t="n">
-        <v>7014379</v>
+        <v>7014380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,6 +4378,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4501,7 +4506,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502235</v>
+        <v>129502236</v>
       </c>
       <c r="B41" t="n">
         <v>80149</v>
@@ -4536,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583064</v>
+        <v>583058</v>
       </c>
       <c r="R41" t="n">
-        <v>7014430</v>
+        <v>7014379</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4598,10 +4603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502221</v>
+        <v>129502235</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,21 +4614,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583411</v>
+        <v>583064</v>
       </c>
       <c r="R42" t="n">
-        <v>7014380</v>
+        <v>7014430</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,11 +4674,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502209</v>
+        <v>129502215</v>
       </c>
       <c r="B43" t="n">
-        <v>80053</v>
+        <v>91848</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583167</v>
+        <v>583175</v>
       </c>
       <c r="R43" t="n">
-        <v>7014583</v>
+        <v>7014579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4991,32 +4991,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502226</v>
+        <v>129502209</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583156</v>
+        <v>583167</v>
       </c>
       <c r="R46" t="n">
-        <v>7014249</v>
+        <v>7014583</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5070,24 +5070,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5104,10 +5088,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502215</v>
+        <v>129502226</v>
       </c>
       <c r="B47" t="n">
-        <v>91848</v>
+        <v>80149</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5115,21 +5099,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5139,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583175</v>
+        <v>583156</v>
       </c>
       <c r="R47" t="n">
-        <v>7014579</v>
+        <v>7014249</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5183,8 +5167,24 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502230</v>
+        <v>129502194</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583330</v>
+        <v>583050</v>
       </c>
       <c r="R49" t="n">
-        <v>7014339</v>
+        <v>7014242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502194</v>
+        <v>129502211</v>
       </c>
       <c r="B50" t="n">
-        <v>91550</v>
+        <v>92003</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583050</v>
+        <v>583055</v>
       </c>
       <c r="R50" t="n">
-        <v>7014242</v>
+        <v>7014372</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,32 +5492,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502211</v>
+        <v>129502230</v>
       </c>
       <c r="B51" t="n">
-        <v>92003</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583055</v>
+        <v>583330</v>
       </c>
       <c r="R51" t="n">
-        <v>7014372</v>
+        <v>7014339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5686,32 +5686,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129502238</v>
+        <v>129502228</v>
       </c>
       <c r="B53" t="n">
-        <v>80185</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>583155</v>
+        <v>583073</v>
       </c>
       <c r="R53" t="n">
-        <v>7014250</v>
+        <v>7014431</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5771,17 +5771,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129502228</v>
+        <v>129502238</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583073</v>
+        <v>583155</v>
       </c>
       <c r="R54" t="n">
-        <v>7014431</v>
+        <v>7014250</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5884,17 +5884,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6407,32 +6407,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502227</v>
+        <v>129502184</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>91514</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583045</v>
+        <v>583134</v>
       </c>
       <c r="R60" t="n">
-        <v>7014432</v>
+        <v>7014134</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,24 +6486,8 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6520,32 +6504,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502184</v>
+        <v>129502227</v>
       </c>
       <c r="B61" t="n">
-        <v>91514</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6539,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583134</v>
+        <v>583045</v>
       </c>
       <c r="R61" t="n">
-        <v>7014134</v>
+        <v>7014432</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6599,8 +6583,24 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R62" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,32 +6714,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502249</v>
+        <v>129502239</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583114</v>
+        <v>583168</v>
       </c>
       <c r="R63" t="n">
-        <v>7014512</v>
+        <v>7014188</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502239</v>
+        <v>129502232</v>
       </c>
       <c r="B64" t="n">
-        <v>58097</v>
+        <v>80149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583168</v>
+        <v>583323</v>
       </c>
       <c r="R64" t="n">
-        <v>7014188</v>
+        <v>7014267</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R65" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,6 +6979,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7005,10 +7010,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B66" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,21 +7021,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7040,10 +7045,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R66" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7076,11 +7081,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7204,10 +7204,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502248</v>
+        <v>129502203</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7215,34 +7215,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583117</v>
+        <v>583138</v>
       </c>
       <c r="R68" t="n">
-        <v>7014262</v>
+        <v>7014232</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7301,10 +7309,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129502203</v>
+        <v>129502248</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7312,42 +7320,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583138</v>
+        <v>583117</v>
       </c>
       <c r="R69" t="n">
-        <v>7014232</v>
+        <v>7014262</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7605,32 +7605,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502198</v>
+        <v>129502218</v>
       </c>
       <c r="B72" t="n">
-        <v>92268</v>
+        <v>91848</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583192</v>
+        <v>583050</v>
       </c>
       <c r="R72" t="n">
-        <v>7014120</v>
+        <v>7014244</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7702,32 +7702,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502218</v>
+        <v>129502198</v>
       </c>
       <c r="B73" t="n">
-        <v>91848</v>
+        <v>92268</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583050</v>
+        <v>583192</v>
       </c>
       <c r="R73" t="n">
-        <v>7014244</v>
+        <v>7014120</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502214</v>
+        <v>129502256</v>
       </c>
       <c r="B79" t="n">
-        <v>91848</v>
+        <v>82878</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583052</v>
+        <v>583110</v>
       </c>
       <c r="R79" t="n">
-        <v>7014374</v>
+        <v>7014519</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8386,10 +8386,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502233</v>
+        <v>129502214</v>
       </c>
       <c r="B80" t="n">
-        <v>80149</v>
+        <v>91848</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8397,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583068</v>
+        <v>583052</v>
       </c>
       <c r="R80" t="n">
-        <v>7014398</v>
+        <v>7014374</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8457,11 +8457,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8488,10 +8483,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502256</v>
+        <v>129502233</v>
       </c>
       <c r="B81" t="n">
-        <v>82878</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8499,21 +8494,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8523,10 +8518,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583110</v>
+        <v>583068</v>
       </c>
       <c r="R81" t="n">
-        <v>7014519</v>
+        <v>7014398</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8559,6 +8554,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -971,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502244</v>
+        <v>129502188</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>91514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583177</v>
+        <v>583139</v>
       </c>
       <c r="R5" t="n">
-        <v>7014165</v>
+        <v>7014270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1050,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502188</v>
+        <v>129502190</v>
       </c>
       <c r="B6" t="n">
         <v>91514</v>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583139</v>
+        <v>583136</v>
       </c>
       <c r="R6" t="n">
-        <v>7014270</v>
+        <v>7014210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1165,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502190</v>
+        <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>91514</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583136</v>
+        <v>583177</v>
       </c>
       <c r="R7" t="n">
-        <v>7014210</v>
+        <v>7014165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502215</v>
+        <v>129502209</v>
       </c>
       <c r="B43" t="n">
-        <v>91848</v>
+        <v>80053</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583175</v>
+        <v>583167</v>
       </c>
       <c r="R43" t="n">
-        <v>7014579</v>
+        <v>7014583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502247</v>
+        <v>129502226</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4808,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583367</v>
+        <v>583156</v>
       </c>
       <c r="R44" t="n">
-        <v>7014331</v>
+        <v>7014249</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,8 +4876,24 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4894,10 +4910,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502251</v>
+        <v>129502205</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,21 +4921,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4932,7 +4948,7 @@
         <v>583055</v>
       </c>
       <c r="R45" t="n">
-        <v>7014329</v>
+        <v>7014357</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4991,32 +5007,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502209</v>
+        <v>129502215</v>
       </c>
       <c r="B46" t="n">
-        <v>80053</v>
+        <v>91848</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583167</v>
+        <v>583175</v>
       </c>
       <c r="R46" t="n">
-        <v>7014583</v>
+        <v>7014579</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,10 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502226</v>
+        <v>129502247</v>
       </c>
       <c r="B47" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5099,21 +5115,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5123,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583156</v>
+        <v>583367</v>
       </c>
       <c r="R47" t="n">
-        <v>7014249</v>
+        <v>7014331</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,24 +5183,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5201,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502205</v>
+        <v>129502251</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,7 +5239,7 @@
         <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014357</v>
+        <v>7014329</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5686,32 +5686,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129502228</v>
+        <v>129502238</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>583073</v>
+        <v>583155</v>
       </c>
       <c r="R53" t="n">
-        <v>7014431</v>
+        <v>7014250</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5771,17 +5771,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129502238</v>
+        <v>129502228</v>
       </c>
       <c r="B54" t="n">
-        <v>80185</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583155</v>
+        <v>583073</v>
       </c>
       <c r="R54" t="n">
-        <v>7014250</v>
+        <v>7014431</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5884,17 +5884,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6617,32 +6617,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502249</v>
+        <v>129502239</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583114</v>
+        <v>583168</v>
       </c>
       <c r="R62" t="n">
-        <v>7014512</v>
+        <v>7014188</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,32 +6714,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502239</v>
+        <v>129502249</v>
       </c>
       <c r="B63" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583168</v>
+        <v>583114</v>
       </c>
       <c r="R63" t="n">
-        <v>7014188</v>
+        <v>7014512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7204,10 +7204,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502203</v>
+        <v>129502248</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7215,42 +7215,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583138</v>
+        <v>583117</v>
       </c>
       <c r="R68" t="n">
-        <v>7014232</v>
+        <v>7014262</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7309,10 +7301,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129502248</v>
+        <v>129502203</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7320,34 +7312,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583117</v>
+        <v>583138</v>
       </c>
       <c r="R69" t="n">
-        <v>7014262</v>
+        <v>7014232</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7702,45 +7702,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B73" t="n">
-        <v>92268</v>
+        <v>98724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R73" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7781,6 +7785,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7799,49 +7804,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B74" t="n">
-        <v>98724</v>
+        <v>92268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R74" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7882,7 +7883,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502250</v>
+        <v>129502204</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583068</v>
+        <v>583061</v>
       </c>
       <c r="R75" t="n">
-        <v>7014344</v>
+        <v>7014418</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129502204</v>
+        <v>129502250</v>
       </c>
       <c r="B77" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583061</v>
+        <v>583068</v>
       </c>
       <c r="R77" t="n">
-        <v>7014418</v>
+        <v>7014344</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129502197</v>
       </c>
       <c r="B2" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129502195</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129502188</v>
       </c>
       <c r="B5" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129502190</v>
       </c>
       <c r="B6" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129502212</v>
+        <v>129495400</v>
       </c>
       <c r="B8" t="n">
-        <v>92003</v>
+        <v>91553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583184</v>
+        <v>583183</v>
       </c>
       <c r="R8" t="n">
-        <v>7014173</v>
+        <v>7014604</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,44 +1352,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129502199</v>
+        <v>129502212</v>
       </c>
       <c r="B9" t="n">
-        <v>92268</v>
+        <v>92006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583141</v>
+        <v>583184</v>
       </c>
       <c r="R9" t="n">
-        <v>7014282</v>
+        <v>7014173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,48 +1461,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129495400</v>
+        <v>129502199</v>
       </c>
       <c r="B10" t="n">
-        <v>91550</v>
+        <v>92271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583183</v>
+        <v>583141</v>
       </c>
       <c r="R10" t="n">
-        <v>7014604</v>
+        <v>7014282</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1546,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
         <v>129502189</v>
       </c>
       <c r="B12" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129502186</v>
       </c>
       <c r="B13" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>129502200</v>
       </c>
       <c r="B14" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129502201</v>
       </c>
       <c r="B15" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129495405</v>
       </c>
       <c r="B16" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495410</v>
+        <v>129502196</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,37 +2151,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583139</v>
+        <v>583143</v>
       </c>
       <c r="R17" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2225,19 +2225,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495408</v>
+        <v>129495410</v>
       </c>
       <c r="B18" t="n">
         <v>80149</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583204</v>
+        <v>583139</v>
       </c>
       <c r="R18" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495406</v>
+        <v>129495408</v>
       </c>
       <c r="B19" t="n">
         <v>80149</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583170</v>
+        <v>583204</v>
       </c>
       <c r="R19" t="n">
-        <v>7014239</v>
+        <v>7014157</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129502196</v>
+        <v>129495406</v>
       </c>
       <c r="B20" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583143</v>
+        <v>583170</v>
       </c>
       <c r="R20" t="n">
-        <v>7014216</v>
+        <v>7014239</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>129502220</v>
       </c>
       <c r="B21" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129502202</v>
       </c>
       <c r="B22" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129502255</v>
+        <v>129495402</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583197</v>
+        <v>583080</v>
       </c>
       <c r="R23" t="n">
-        <v>7014149</v>
+        <v>7014300</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129502252</v>
+        <v>129502255</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583105</v>
+        <v>583197</v>
       </c>
       <c r="R25" t="n">
-        <v>7014309</v>
+        <v>7014149</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129495402</v>
+        <v>129502252</v>
       </c>
       <c r="B26" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583080</v>
+        <v>583105</v>
       </c>
       <c r="R26" t="n">
-        <v>7014300</v>
+        <v>7014309</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
         <v>129495401</v>
       </c>
       <c r="B30" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3498,48 +3498,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129502213</v>
+        <v>129495411</v>
       </c>
       <c r="B31" t="n">
-        <v>92003</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583198</v>
+        <v>583068</v>
       </c>
       <c r="R31" t="n">
-        <v>7014144</v>
+        <v>7014294</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,26 +3577,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129502224</v>
+        <v>129495409</v>
       </c>
       <c r="B32" t="n">
         <v>80149</v>
@@ -3627,17 +3626,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583151</v>
+        <v>583174</v>
       </c>
       <c r="R32" t="n">
-        <v>7014252</v>
+        <v>7014111</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3675,82 +3674,66 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129495411</v>
+        <v>129502213</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583068</v>
+        <v>583198</v>
       </c>
       <c r="R33" t="n">
-        <v>7014294</v>
+        <v>7014144</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3788,25 +3771,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129495409</v>
+        <v>129502224</v>
       </c>
       <c r="B34" t="n">
         <v>80149</v>
@@ -3837,17 +3821,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583174</v>
+        <v>583151</v>
       </c>
       <c r="R34" t="n">
-        <v>7014111</v>
+        <v>7014252</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3885,18 +3869,34 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
         <v>129502192</v>
       </c>
       <c r="B35" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502221</v>
+        <v>129502182</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583411</v>
+        <v>583174</v>
       </c>
       <c r="R39" t="n">
-        <v>7014380</v>
+        <v>7014597</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,11 +4378,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4409,32 +4404,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502182</v>
+        <v>129502236</v>
       </c>
       <c r="B40" t="n">
-        <v>91514</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583174</v>
+        <v>583058</v>
       </c>
       <c r="R40" t="n">
-        <v>7014597</v>
+        <v>7014379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4506,7 +4501,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502236</v>
+        <v>129502235</v>
       </c>
       <c r="B41" t="n">
         <v>80149</v>
@@ -4541,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583058</v>
+        <v>583064</v>
       </c>
       <c r="R41" t="n">
-        <v>7014379</v>
+        <v>7014430</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4603,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502235</v>
+        <v>129502221</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583064</v>
+        <v>583411</v>
       </c>
       <c r="R42" t="n">
-        <v>7014430</v>
+        <v>7014380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,6 +4669,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502209</v>
+        <v>129502215</v>
       </c>
       <c r="B43" t="n">
-        <v>80053</v>
+        <v>91851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583167</v>
+        <v>583175</v>
       </c>
       <c r="R43" t="n">
-        <v>7014583</v>
+        <v>7014579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,32 +4797,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502226</v>
+        <v>129502209</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583156</v>
+        <v>583167</v>
       </c>
       <c r="R44" t="n">
-        <v>7014249</v>
+        <v>7014583</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,24 +4876,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4910,10 +4894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502205</v>
+        <v>129502226</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4921,21 +4905,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4945,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R45" t="n">
-        <v>7014357</v>
+        <v>7014249</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4989,8 +4973,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5007,10 +5007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502215</v>
+        <v>129502205</v>
       </c>
       <c r="B46" t="n">
-        <v>91848</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5018,21 +5018,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583175</v>
+        <v>583055</v>
       </c>
       <c r="R46" t="n">
-        <v>7014579</v>
+        <v>7014357</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502194</v>
+        <v>129502230</v>
       </c>
       <c r="B49" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583050</v>
+        <v>583330</v>
       </c>
       <c r="R49" t="n">
-        <v>7014242</v>
+        <v>7014339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502211</v>
+        <v>129502194</v>
       </c>
       <c r="B50" t="n">
-        <v>92003</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583055</v>
+        <v>583050</v>
       </c>
       <c r="R50" t="n">
-        <v>7014372</v>
+        <v>7014242</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,32 +5492,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502230</v>
+        <v>129502211</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583330</v>
+        <v>583055</v>
       </c>
       <c r="R51" t="n">
-        <v>7014339</v>
+        <v>7014372</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6114,7 +6114,7 @@
         <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6310,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502231</v>
+        <v>129502184</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>91517</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583345</v>
+        <v>583134</v>
       </c>
       <c r="R59" t="n">
-        <v>7014389</v>
+        <v>7014134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6407,32 +6407,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502184</v>
+        <v>129502231</v>
       </c>
       <c r="B60" t="n">
-        <v>91514</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583134</v>
+        <v>583345</v>
       </c>
       <c r="R60" t="n">
-        <v>7014134</v>
+        <v>7014389</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6617,32 +6617,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502239</v>
+        <v>129502232</v>
       </c>
       <c r="B62" t="n">
-        <v>58097</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583168</v>
+        <v>583323</v>
       </c>
       <c r="R62" t="n">
-        <v>7014188</v>
+        <v>7014267</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502232</v>
+        <v>129502239</v>
       </c>
       <c r="B64" t="n">
-        <v>80149</v>
+        <v>58097</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583323</v>
+        <v>583168</v>
       </c>
       <c r="R64" t="n">
-        <v>7014267</v>
+        <v>7014188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B65" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R65" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,11 +6979,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7010,10 +7005,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7021,21 +7016,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7045,10 +7040,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R66" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7081,6 +7076,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7506,7 +7506,7 @@
         <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7605,32 +7605,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502218</v>
+        <v>129502198</v>
       </c>
       <c r="B72" t="n">
-        <v>91848</v>
+        <v>92271</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583050</v>
+        <v>583192</v>
       </c>
       <c r="R72" t="n">
-        <v>7014244</v>
+        <v>7014120</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7705,7 +7705,7 @@
         <v>129502242</v>
       </c>
       <c r="B73" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7804,32 +7804,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502198</v>
+        <v>129502218</v>
       </c>
       <c r="B74" t="n">
-        <v>92268</v>
+        <v>91851</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583192</v>
+        <v>583050</v>
       </c>
       <c r="R74" t="n">
-        <v>7014120</v>
+        <v>7014244</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502204</v>
+        <v>129502193</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>91553</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583061</v>
+        <v>583174</v>
       </c>
       <c r="R75" t="n">
-        <v>7014418</v>
+        <v>7014589</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502193</v>
+        <v>129502204</v>
       </c>
       <c r="B76" t="n">
-        <v>91550</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583174</v>
+        <v>583061</v>
       </c>
       <c r="R76" t="n">
-        <v>7014589</v>
+        <v>7014418</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8195,7 +8195,7 @@
         <v>129502217</v>
       </c>
       <c r="B78" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502256</v>
+        <v>129502214</v>
       </c>
       <c r="B79" t="n">
-        <v>82878</v>
+        <v>91851</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583110</v>
+        <v>583052</v>
       </c>
       <c r="R79" t="n">
-        <v>7014519</v>
+        <v>7014374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8386,10 +8386,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502214</v>
+        <v>129502256</v>
       </c>
       <c r="B80" t="n">
-        <v>91848</v>
+        <v>82878</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8397,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583052</v>
+        <v>583110</v>
       </c>
       <c r="R80" t="n">
-        <v>7014374</v>
+        <v>7014519</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8588,7 +8588,7 @@
         <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129495400</v>
+        <v>129502199</v>
       </c>
       <c r="B8" t="n">
-        <v>91553</v>
+        <v>92271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583183</v>
+        <v>583141</v>
       </c>
       <c r="R8" t="n">
-        <v>7014604</v>
+        <v>7014282</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1461,48 +1461,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129502199</v>
+        <v>129495400</v>
       </c>
       <c r="B10" t="n">
-        <v>92271</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583141</v>
+        <v>583183</v>
       </c>
       <c r="R10" t="n">
-        <v>7014282</v>
+        <v>7014604</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1546,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2043,48 +2043,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495405</v>
+        <v>129502196</v>
       </c>
       <c r="B16" t="n">
-        <v>92006</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583128</v>
+        <v>583143</v>
       </c>
       <c r="R16" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,60 +2128,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129502196</v>
+        <v>129495405</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>92006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583143</v>
+        <v>583128</v>
       </c>
       <c r="R17" t="n">
-        <v>7014216</v>
+        <v>7014123</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129495407</v>
+        <v>129502252</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583122</v>
+        <v>583105</v>
       </c>
       <c r="R24" t="n">
-        <v>7014418</v>
+        <v>7014309</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,12 +2904,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129502252</v>
+        <v>129495407</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583105</v>
+        <v>583122</v>
       </c>
       <c r="R26" t="n">
-        <v>7014309</v>
+        <v>7014418</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3498,48 +3498,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129495411</v>
+        <v>129502213</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583068</v>
+        <v>583198</v>
       </c>
       <c r="R31" t="n">
-        <v>7014294</v>
+        <v>7014144</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,25 +3577,26 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129495409</v>
+        <v>129502224</v>
       </c>
       <c r="B32" t="n">
         <v>80149</v>
@@ -3626,17 +3627,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583174</v>
+        <v>583151</v>
       </c>
       <c r="R32" t="n">
-        <v>7014111</v>
+        <v>7014252</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3674,66 +3675,82 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129502213</v>
+        <v>129495411</v>
       </c>
       <c r="B33" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583198</v>
+        <v>583068</v>
       </c>
       <c r="R33" t="n">
-        <v>7014144</v>
+        <v>7014294</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3771,26 +3788,25 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502224</v>
+        <v>129495409</v>
       </c>
       <c r="B34" t="n">
         <v>80149</v>
@@ -3821,17 +3837,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583151</v>
+        <v>583174</v>
       </c>
       <c r="R34" t="n">
-        <v>7014252</v>
+        <v>7014111</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3869,34 +3885,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502236</v>
+        <v>129502221</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,21 +4415,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583058</v>
+        <v>583411</v>
       </c>
       <c r="R40" t="n">
-        <v>7014379</v>
+        <v>7014380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4475,6 +4475,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4598,10 +4603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502221</v>
+        <v>129502236</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,21 +4614,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583411</v>
+        <v>583058</v>
       </c>
       <c r="R42" t="n">
-        <v>7014380</v>
+        <v>7014379</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,11 +4674,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4797,32 +4797,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502209</v>
+        <v>129502226</v>
       </c>
       <c r="B44" t="n">
-        <v>80053</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583167</v>
+        <v>583156</v>
       </c>
       <c r="R44" t="n">
-        <v>7014583</v>
+        <v>7014249</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,8 +4876,24 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4894,32 +4910,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502226</v>
+        <v>129502209</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4945,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583156</v>
+        <v>583167</v>
       </c>
       <c r="R45" t="n">
-        <v>7014249</v>
+        <v>7014583</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4973,24 +4989,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5007,10 +5007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502205</v>
+        <v>129502247</v>
       </c>
       <c r="B46" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5018,21 +5018,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583055</v>
+        <v>583367</v>
       </c>
       <c r="R46" t="n">
-        <v>7014357</v>
+        <v>7014331</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502247</v>
+        <v>129502251</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583367</v>
+        <v>583055</v>
       </c>
       <c r="R47" t="n">
-        <v>7014331</v>
+        <v>7014329</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502251</v>
+        <v>129502205</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,7 +5239,7 @@
         <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014329</v>
+        <v>7014357</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502230</v>
+        <v>129502194</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583330</v>
+        <v>583050</v>
       </c>
       <c r="R49" t="n">
-        <v>7014339</v>
+        <v>7014242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502194</v>
+        <v>129502211</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>92006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583050</v>
+        <v>583055</v>
       </c>
       <c r="R50" t="n">
-        <v>7014242</v>
+        <v>7014372</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,32 +5492,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502211</v>
+        <v>129502230</v>
       </c>
       <c r="B51" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583055</v>
+        <v>583330</v>
       </c>
       <c r="R51" t="n">
-        <v>7014372</v>
+        <v>7014339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6111,45 +6111,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502216</v>
+        <v>129502243</v>
       </c>
       <c r="B57" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583173</v>
+        <v>583046</v>
       </c>
       <c r="R57" t="n">
-        <v>7014589</v>
+        <v>7014393</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6190,6 +6194,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6208,49 +6213,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502243</v>
+        <v>129502216</v>
       </c>
       <c r="B58" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583046</v>
+        <v>583173</v>
       </c>
       <c r="R58" t="n">
-        <v>7014393</v>
+        <v>7014589</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6291,7 +6292,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502231</v>
+        <v>129502227</v>
       </c>
       <c r="B60" t="n">
         <v>80149</v>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583345</v>
+        <v>583045</v>
       </c>
       <c r="R60" t="n">
-        <v>7014389</v>
+        <v>7014432</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,8 +6486,24 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6504,7 +6520,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502227</v>
+        <v>129502231</v>
       </c>
       <c r="B61" t="n">
         <v>80149</v>
@@ -6539,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583045</v>
+        <v>583345</v>
       </c>
       <c r="R61" t="n">
-        <v>7014432</v>
+        <v>7014389</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6583,24 +6599,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6617,32 +6617,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502232</v>
+        <v>129502239</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>58097</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583323</v>
+        <v>583168</v>
       </c>
       <c r="R62" t="n">
-        <v>7014267</v>
+        <v>7014188</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502249</v>
+        <v>129502232</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583114</v>
+        <v>583323</v>
       </c>
       <c r="R63" t="n">
-        <v>7014512</v>
+        <v>7014267</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502239</v>
+        <v>129502249</v>
       </c>
       <c r="B64" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583168</v>
+        <v>583114</v>
       </c>
       <c r="R64" t="n">
-        <v>7014188</v>
+        <v>7014512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7702,49 +7702,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502242</v>
+        <v>129502218</v>
       </c>
       <c r="B73" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583095</v>
+        <v>583050</v>
       </c>
       <c r="R73" t="n">
-        <v>7014377</v>
+        <v>7014244</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7785,7 +7781,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7804,45 +7799,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502218</v>
+        <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583050</v>
+        <v>583095</v>
       </c>
       <c r="R74" t="n">
-        <v>7014244</v>
+        <v>7014377</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,6 +7882,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502193</v>
+        <v>129502204</v>
       </c>
       <c r="B75" t="n">
-        <v>91553</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583174</v>
+        <v>583061</v>
       </c>
       <c r="R75" t="n">
-        <v>7014589</v>
+        <v>7014418</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502204</v>
+        <v>129502250</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583061</v>
+        <v>583068</v>
       </c>
       <c r="R76" t="n">
-        <v>7014418</v>
+        <v>7014344</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129502250</v>
+        <v>129502193</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R77" t="n">
-        <v>7014344</v>
+        <v>7014589</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -971,45 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502188</v>
+        <v>129502244</v>
       </c>
       <c r="B5" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583139</v>
+        <v>583177</v>
       </c>
       <c r="R5" t="n">
-        <v>7014270</v>
+        <v>7014165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502190</v>
+        <v>129502188</v>
       </c>
       <c r="B6" t="n">
         <v>91517</v>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583136</v>
+        <v>583139</v>
       </c>
       <c r="R6" t="n">
-        <v>7014210</v>
+        <v>7014270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,49 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502244</v>
+        <v>129502190</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583177</v>
+        <v>583136</v>
       </c>
       <c r="R7" t="n">
-        <v>7014165</v>
+        <v>7014210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129502199</v>
+        <v>129502212</v>
       </c>
       <c r="B8" t="n">
-        <v>92271</v>
+        <v>92006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583141</v>
+        <v>583184</v>
       </c>
       <c r="R8" t="n">
-        <v>7014282</v>
+        <v>7014173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129502212</v>
+        <v>129502199</v>
       </c>
       <c r="B9" t="n">
-        <v>92006</v>
+        <v>92271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583184</v>
+        <v>583141</v>
       </c>
       <c r="R9" t="n">
-        <v>7014173</v>
+        <v>7014282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129502196</v>
+        <v>129495408</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,37 +2054,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583143</v>
+        <v>583204</v>
       </c>
       <c r="R16" t="n">
-        <v>7014216</v>
+        <v>7014157</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495405</v>
+        <v>129495410</v>
       </c>
       <c r="B17" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583128</v>
+        <v>583139</v>
       </c>
       <c r="R17" t="n">
         <v>7014123</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495410</v>
+        <v>129495406</v>
       </c>
       <c r="B18" t="n">
         <v>80149</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583139</v>
+        <v>583170</v>
       </c>
       <c r="R18" t="n">
-        <v>7014123</v>
+        <v>7014239</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495408</v>
+        <v>129502196</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,37 +2345,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583204</v>
+        <v>583143</v>
       </c>
       <c r="R19" t="n">
-        <v>7014157</v>
+        <v>7014216</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2419,44 +2419,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495406</v>
+        <v>129495405</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583170</v>
+        <v>583128</v>
       </c>
       <c r="R20" t="n">
-        <v>7014239</v>
+        <v>7014123</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129502255</v>
+        <v>129495407</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583197</v>
+        <v>583122</v>
       </c>
       <c r="R25" t="n">
-        <v>7014149</v>
+        <v>7014418</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129495407</v>
+        <v>129502255</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583122</v>
+        <v>583197</v>
       </c>
       <c r="R26" t="n">
-        <v>7014418</v>
+        <v>7014149</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R28" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R29" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3596,7 +3596,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129502224</v>
+        <v>129495409</v>
       </c>
       <c r="B32" t="n">
         <v>80149</v>
@@ -3627,17 +3627,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583151</v>
+        <v>583174</v>
       </c>
       <c r="R32" t="n">
-        <v>7014252</v>
+        <v>7014111</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3675,34 +3675,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3806,7 +3790,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129495409</v>
+        <v>129502224</v>
       </c>
       <c r="B34" t="n">
         <v>80149</v>
@@ -3837,17 +3821,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583174</v>
+        <v>583151</v>
       </c>
       <c r="R34" t="n">
-        <v>7014111</v>
+        <v>7014252</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3885,18 +3869,34 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502221</v>
+        <v>129502236</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4415,21 +4415,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583411</v>
+        <v>583058</v>
       </c>
       <c r="R40" t="n">
-        <v>7014380</v>
+        <v>7014379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4475,11 +4475,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4603,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502236</v>
+        <v>129502221</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583058</v>
+        <v>583411</v>
       </c>
       <c r="R42" t="n">
-        <v>7014379</v>
+        <v>7014380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,6 +4669,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502215</v>
+        <v>129502209</v>
       </c>
       <c r="B43" t="n">
-        <v>91851</v>
+        <v>80053</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583175</v>
+        <v>583167</v>
       </c>
       <c r="R43" t="n">
-        <v>7014579</v>
+        <v>7014583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502226</v>
+        <v>129502247</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4808,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583156</v>
+        <v>583367</v>
       </c>
       <c r="R44" t="n">
-        <v>7014249</v>
+        <v>7014331</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,24 +4876,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4910,32 +4894,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502209</v>
+        <v>129502251</v>
       </c>
       <c r="B45" t="n">
-        <v>80053</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4945,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583167</v>
+        <v>583055</v>
       </c>
       <c r="R45" t="n">
-        <v>7014583</v>
+        <v>7014329</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5007,10 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502247</v>
+        <v>129502226</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5018,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5042,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583367</v>
+        <v>583156</v>
       </c>
       <c r="R46" t="n">
-        <v>7014331</v>
+        <v>7014249</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5086,8 +5070,24 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5104,10 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502251</v>
+        <v>129502215</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5115,21 +5115,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583055</v>
+        <v>583175</v>
       </c>
       <c r="R47" t="n">
-        <v>7014329</v>
+        <v>7014579</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502194</v>
+        <v>129502230</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583050</v>
+        <v>583330</v>
       </c>
       <c r="R49" t="n">
-        <v>7014242</v>
+        <v>7014339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502211</v>
+        <v>129502206</v>
       </c>
       <c r="B50" t="n">
-        <v>92006</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583055</v>
+        <v>583074</v>
       </c>
       <c r="R50" t="n">
-        <v>7014372</v>
+        <v>7014351</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502230</v>
+        <v>129502194</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583330</v>
+        <v>583050</v>
       </c>
       <c r="R51" t="n">
-        <v>7014339</v>
+        <v>7014242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502206</v>
+        <v>129502211</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>92006</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583074</v>
+        <v>583055</v>
       </c>
       <c r="R52" t="n">
-        <v>7014351</v>
+        <v>7014372</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5686,32 +5686,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129502238</v>
+        <v>129502228</v>
       </c>
       <c r="B53" t="n">
-        <v>80185</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>583155</v>
+        <v>583073</v>
       </c>
       <c r="R53" t="n">
-        <v>7014250</v>
+        <v>7014431</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5771,17 +5771,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129502228</v>
+        <v>129502238</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583073</v>
+        <v>583155</v>
       </c>
       <c r="R54" t="n">
-        <v>7014431</v>
+        <v>7014250</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5884,17 +5884,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6111,49 +6111,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502243</v>
+        <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583046</v>
+        <v>583173</v>
       </c>
       <c r="R57" t="n">
-        <v>7014393</v>
+        <v>7014589</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,7 +6190,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6213,45 +6208,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502216</v>
+        <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583173</v>
+        <v>583046</v>
       </c>
       <c r="R58" t="n">
-        <v>7014589</v>
+        <v>7014393</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6292,6 +6291,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502227</v>
+        <v>129502231</v>
       </c>
       <c r="B60" t="n">
         <v>80149</v>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583045</v>
+        <v>583345</v>
       </c>
       <c r="R60" t="n">
-        <v>7014432</v>
+        <v>7014389</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,24 +6486,8 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6520,7 +6504,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502231</v>
+        <v>129502227</v>
       </c>
       <c r="B61" t="n">
         <v>80149</v>
@@ -6555,10 +6539,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583345</v>
+        <v>583045</v>
       </c>
       <c r="R61" t="n">
-        <v>7014389</v>
+        <v>7014432</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6599,8 +6583,24 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6617,32 +6617,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502239</v>
+        <v>129502232</v>
       </c>
       <c r="B62" t="n">
-        <v>58097</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583168</v>
+        <v>583323</v>
       </c>
       <c r="R62" t="n">
-        <v>7014188</v>
+        <v>7014267</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R63" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502249</v>
+        <v>129502239</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583114</v>
+        <v>583168</v>
       </c>
       <c r="R64" t="n">
-        <v>7014512</v>
+        <v>7014188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7406,45 +7406,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502245</v>
+        <v>129502240</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583158</v>
+        <v>583138</v>
       </c>
       <c r="R70" t="n">
-        <v>7014222</v>
+        <v>7014124</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7485,6 +7489,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7503,49 +7508,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129502240</v>
+        <v>129502245</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583138</v>
+        <v>583158</v>
       </c>
       <c r="R71" t="n">
-        <v>7014124</v>
+        <v>7014222</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7586,7 +7587,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7605,45 +7605,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B72" t="n">
-        <v>92271</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R72" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7684,6 +7688,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7799,49 +7804,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B74" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R74" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7882,7 +7883,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502250</v>
+        <v>129502193</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R76" t="n">
-        <v>7014344</v>
+        <v>7014589</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129502193</v>
+        <v>129502250</v>
       </c>
       <c r="B77" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R77" t="n">
-        <v>7014589</v>
+        <v>7014344</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502214</v>
+        <v>129502233</v>
       </c>
       <c r="B79" t="n">
-        <v>91851</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583052</v>
+        <v>583068</v>
       </c>
       <c r="R79" t="n">
-        <v>7014374</v>
+        <v>7014398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,6 +8360,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8386,10 +8391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502256</v>
+        <v>129502214</v>
       </c>
       <c r="B80" t="n">
-        <v>82878</v>
+        <v>91851</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8402,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8426,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583110</v>
+        <v>583052</v>
       </c>
       <c r="R80" t="n">
-        <v>7014519</v>
+        <v>7014374</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8483,10 +8488,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502233</v>
+        <v>129502256</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>82878</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8494,21 +8499,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8518,10 +8523,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583068</v>
+        <v>583110</v>
       </c>
       <c r="R81" t="n">
-        <v>7014398</v>
+        <v>7014519</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8554,11 +8559,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -971,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502244</v>
+        <v>129502188</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583177</v>
+        <v>583139</v>
       </c>
       <c r="R5" t="n">
-        <v>7014165</v>
+        <v>7014270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1050,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502188</v>
+        <v>129502190</v>
       </c>
       <c r="B6" t="n">
         <v>91517</v>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583139</v>
+        <v>583136</v>
       </c>
       <c r="R6" t="n">
-        <v>7014270</v>
+        <v>7014210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1165,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502190</v>
+        <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583136</v>
+        <v>583177</v>
       </c>
       <c r="R7" t="n">
-        <v>7014210</v>
+        <v>7014165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495408</v>
+        <v>129502196</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,37 +2054,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583204</v>
+        <v>583143</v>
       </c>
       <c r="R16" t="n">
-        <v>7014157</v>
+        <v>7014216</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,12 +2128,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495406</v>
+        <v>129495408</v>
       </c>
       <c r="B18" t="n">
         <v>80149</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583170</v>
+        <v>583204</v>
       </c>
       <c r="R18" t="n">
-        <v>7014239</v>
+        <v>7014157</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129502196</v>
+        <v>129495406</v>
       </c>
       <c r="B19" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,37 +2345,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583143</v>
+        <v>583170</v>
       </c>
       <c r="R19" t="n">
-        <v>7014216</v>
+        <v>7014239</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2419,12 +2419,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129495402</v>
+        <v>129502255</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583080</v>
+        <v>583197</v>
       </c>
       <c r="R23" t="n">
-        <v>7014300</v>
+        <v>7014149</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129495407</v>
+        <v>129495402</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,21 +2927,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583122</v>
+        <v>583080</v>
       </c>
       <c r="R25" t="n">
-        <v>7014418</v>
+        <v>7014300</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129502255</v>
+        <v>129495407</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583197</v>
+        <v>583122</v>
       </c>
       <c r="R26" t="n">
-        <v>7014149</v>
+        <v>7014418</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R28" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R29" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3498,48 +3498,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129502213</v>
+        <v>129495411</v>
       </c>
       <c r="B31" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583198</v>
+        <v>583068</v>
       </c>
       <c r="R31" t="n">
-        <v>7014144</v>
+        <v>7014294</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,19 +3577,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3693,48 +3692,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129495411</v>
+        <v>129502213</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583068</v>
+        <v>583198</v>
       </c>
       <c r="R33" t="n">
-        <v>7014294</v>
+        <v>7014144</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3772,18 +3771,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502209</v>
+        <v>129502215</v>
       </c>
       <c r="B43" t="n">
-        <v>80053</v>
+        <v>91851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583167</v>
+        <v>583175</v>
       </c>
       <c r="R43" t="n">
-        <v>7014583</v>
+        <v>7014579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502247</v>
+        <v>129502205</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4808,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583367</v>
+        <v>583055</v>
       </c>
       <c r="R44" t="n">
-        <v>7014331</v>
+        <v>7014357</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4894,7 +4894,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502251</v>
+        <v>129502247</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583055</v>
+        <v>583367</v>
       </c>
       <c r="R45" t="n">
-        <v>7014329</v>
+        <v>7014331</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4991,10 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502226</v>
+        <v>129502251</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5002,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R46" t="n">
-        <v>7014249</v>
+        <v>7014329</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5070,24 +5070,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5104,32 +5088,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502215</v>
+        <v>129502209</v>
       </c>
       <c r="B47" t="n">
-        <v>91851</v>
+        <v>80053</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5139,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583175</v>
+        <v>583167</v>
       </c>
       <c r="R47" t="n">
-        <v>7014579</v>
+        <v>7014583</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,10 +5185,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502205</v>
+        <v>129502226</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5196,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5236,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R48" t="n">
-        <v>7014357</v>
+        <v>7014249</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5280,8 +5264,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502230</v>
+        <v>129502194</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583330</v>
+        <v>583050</v>
       </c>
       <c r="R49" t="n">
-        <v>7014339</v>
+        <v>7014242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502206</v>
+        <v>129502211</v>
       </c>
       <c r="B50" t="n">
-        <v>57724</v>
+        <v>92006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583074</v>
+        <v>583055</v>
       </c>
       <c r="R50" t="n">
-        <v>7014351</v>
+        <v>7014372</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502194</v>
+        <v>129502206</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>57724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583050</v>
+        <v>583074</v>
       </c>
       <c r="R51" t="n">
-        <v>7014242</v>
+        <v>7014351</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502211</v>
+        <v>129502230</v>
       </c>
       <c r="B52" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583055</v>
+        <v>583330</v>
       </c>
       <c r="R52" t="n">
-        <v>7014372</v>
+        <v>7014339</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5686,32 +5686,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129502228</v>
+        <v>129502238</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>583073</v>
+        <v>583155</v>
       </c>
       <c r="R53" t="n">
-        <v>7014431</v>
+        <v>7014250</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5771,17 +5771,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129502238</v>
+        <v>129502228</v>
       </c>
       <c r="B54" t="n">
-        <v>80185</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583155</v>
+        <v>583073</v>
       </c>
       <c r="R54" t="n">
-        <v>7014250</v>
+        <v>7014431</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5884,17 +5884,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R62" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502249</v>
+        <v>129502232</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583114</v>
+        <v>583323</v>
       </c>
       <c r="R63" t="n">
-        <v>7014512</v>
+        <v>7014267</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129502180</v>
+        <v>129502203</v>
       </c>
       <c r="B67" t="n">
-        <v>83012</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7118,34 +7118,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583051</v>
+        <v>583138</v>
       </c>
       <c r="R67" t="n">
-        <v>7014327</v>
+        <v>7014232</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7204,10 +7212,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502248</v>
+        <v>129502180</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7215,21 +7223,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7239,10 +7247,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583117</v>
+        <v>583051</v>
       </c>
       <c r="R68" t="n">
-        <v>7014262</v>
+        <v>7014327</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7301,10 +7309,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129502203</v>
+        <v>129502248</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7312,42 +7320,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583138</v>
+        <v>583117</v>
       </c>
       <c r="R69" t="n">
-        <v>7014232</v>
+        <v>7014262</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7406,49 +7406,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502240</v>
+        <v>129502245</v>
       </c>
       <c r="B70" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583138</v>
+        <v>583158</v>
       </c>
       <c r="R70" t="n">
-        <v>7014124</v>
+        <v>7014222</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7489,7 +7485,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7508,45 +7503,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129502245</v>
+        <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583158</v>
+        <v>583138</v>
       </c>
       <c r="R71" t="n">
-        <v>7014222</v>
+        <v>7014124</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7587,6 +7586,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7605,49 +7605,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B72" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R72" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7688,7 +7684,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7804,45 +7799,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>92271</v>
+        <v>98727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R74" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,6 +7882,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502204</v>
+        <v>129502250</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583061</v>
+        <v>583068</v>
       </c>
       <c r="R75" t="n">
-        <v>7014418</v>
+        <v>7014344</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129502250</v>
+        <v>129502204</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583068</v>
+        <v>583061</v>
       </c>
       <c r="R77" t="n">
-        <v>7014344</v>
+        <v>7014418</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502233</v>
+        <v>129502214</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>91851</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583068</v>
+        <v>583052</v>
       </c>
       <c r="R79" t="n">
-        <v>7014398</v>
+        <v>7014374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,11 +8360,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8391,10 +8386,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502214</v>
+        <v>129502256</v>
       </c>
       <c r="B80" t="n">
-        <v>91851</v>
+        <v>82878</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8402,21 +8397,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8426,10 +8421,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583052</v>
+        <v>583110</v>
       </c>
       <c r="R80" t="n">
-        <v>7014374</v>
+        <v>7014519</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8488,10 +8483,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502256</v>
+        <v>129502233</v>
       </c>
       <c r="B81" t="n">
-        <v>82878</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8499,21 +8494,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8523,10 +8518,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583110</v>
+        <v>583068</v>
       </c>
       <c r="R81" t="n">
-        <v>7014519</v>
+        <v>7014398</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8559,6 +8554,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8585,32 +8585,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129502219</v>
+        <v>129502241</v>
       </c>
       <c r="B82" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8620,10 +8620,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583137</v>
+        <v>583076</v>
       </c>
       <c r="R82" t="n">
-        <v>7014134</v>
+        <v>7014398</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8664,6 +8664,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8682,32 +8683,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129502241</v>
+        <v>129502219</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8717,10 +8718,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583076</v>
+        <v>583137</v>
       </c>
       <c r="R83" t="n">
-        <v>7014398</v>
+        <v>7014134</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8761,7 +8762,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -2043,48 +2043,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129502196</v>
+        <v>129495405</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>92006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583143</v>
+        <v>583128</v>
       </c>
       <c r="R16" t="n">
-        <v>7014216</v>
+        <v>7014123</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,12 +2128,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2431,48 +2431,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495405</v>
+        <v>129502196</v>
       </c>
       <c r="B20" t="n">
-        <v>92006</v>
+        <v>91553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583128</v>
+        <v>583143</v>
       </c>
       <c r="R20" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129502255</v>
+        <v>129495402</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583197</v>
+        <v>583080</v>
       </c>
       <c r="R23" t="n">
-        <v>7014149</v>
+        <v>7014300</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129502252</v>
+        <v>129495407</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583105</v>
+        <v>583122</v>
       </c>
       <c r="R24" t="n">
-        <v>7014309</v>
+        <v>7014418</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,22 +2904,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129495402</v>
+        <v>129502252</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583080</v>
+        <v>583105</v>
       </c>
       <c r="R25" t="n">
-        <v>7014300</v>
+        <v>7014309</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129495407</v>
+        <v>129502255</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583122</v>
+        <v>583197</v>
       </c>
       <c r="R26" t="n">
-        <v>7014418</v>
+        <v>7014149</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R28" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R29" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129502192</v>
+        <v>129502234</v>
       </c>
       <c r="B35" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583114</v>
+        <v>583081</v>
       </c>
       <c r="R35" t="n">
-        <v>7014270</v>
+        <v>7014394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129502234</v>
+        <v>129502192</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583081</v>
+        <v>583114</v>
       </c>
       <c r="R36" t="n">
-        <v>7014394</v>
+        <v>7014270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502215</v>
+        <v>129502209</v>
       </c>
       <c r="B43" t="n">
-        <v>91851</v>
+        <v>80053</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583175</v>
+        <v>583167</v>
       </c>
       <c r="R43" t="n">
-        <v>7014579</v>
+        <v>7014583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502205</v>
+        <v>129502226</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4808,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R44" t="n">
-        <v>7014357</v>
+        <v>7014249</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,8 +4876,24 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4894,10 +4910,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502247</v>
+        <v>129502215</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,21 +4921,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4945,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583367</v>
+        <v>583175</v>
       </c>
       <c r="R45" t="n">
-        <v>7014331</v>
+        <v>7014579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5088,32 +5104,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502209</v>
+        <v>129502247</v>
       </c>
       <c r="B47" t="n">
-        <v>80053</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5123,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583167</v>
+        <v>583367</v>
       </c>
       <c r="R47" t="n">
-        <v>7014583</v>
+        <v>7014331</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5185,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502226</v>
+        <v>129502205</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5196,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5220,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014249</v>
+        <v>7014357</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,24 +5280,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502206</v>
+        <v>129502230</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583074</v>
+        <v>583330</v>
       </c>
       <c r="R51" t="n">
-        <v>7014351</v>
+        <v>7014339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,10 +5589,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502230</v>
+        <v>129502206</v>
       </c>
       <c r="B52" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5600,21 +5600,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583330</v>
+        <v>583074</v>
       </c>
       <c r="R52" t="n">
-        <v>7014339</v>
+        <v>7014351</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502249</v>
+        <v>129502232</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583114</v>
+        <v>583323</v>
       </c>
       <c r="R62" t="n">
-        <v>7014512</v>
+        <v>7014267</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R63" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129502203</v>
+        <v>129502180</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>83012</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7118,42 +7118,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583138</v>
+        <v>583051</v>
       </c>
       <c r="R67" t="n">
-        <v>7014232</v>
+        <v>7014327</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7212,10 +7204,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502180</v>
+        <v>129502248</v>
       </c>
       <c r="B68" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7223,21 +7215,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7247,10 +7239,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583051</v>
+        <v>583117</v>
       </c>
       <c r="R68" t="n">
-        <v>7014327</v>
+        <v>7014262</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7309,10 +7301,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129502248</v>
+        <v>129502203</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7320,34 +7312,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583117</v>
+        <v>583138</v>
       </c>
       <c r="R69" t="n">
-        <v>7014262</v>
+        <v>7014232</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7605,45 +7605,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B72" t="n">
-        <v>92271</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R72" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7684,6 +7688,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7799,49 +7804,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B74" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R74" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7882,7 +7883,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502250</v>
+        <v>129502193</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R75" t="n">
-        <v>7014344</v>
+        <v>7014589</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502193</v>
+        <v>129502250</v>
       </c>
       <c r="B76" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R76" t="n">
-        <v>7014589</v>
+        <v>7014344</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502214</v>
+        <v>129502256</v>
       </c>
       <c r="B79" t="n">
-        <v>91851</v>
+        <v>82878</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583052</v>
+        <v>583110</v>
       </c>
       <c r="R79" t="n">
-        <v>7014374</v>
+        <v>7014519</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8386,10 +8386,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502256</v>
+        <v>129502214</v>
       </c>
       <c r="B80" t="n">
-        <v>82878</v>
+        <v>91851</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8397,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583110</v>
+        <v>583052</v>
       </c>
       <c r="R80" t="n">
-        <v>7014519</v>
+        <v>7014374</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -971,45 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502188</v>
+        <v>129502244</v>
       </c>
       <c r="B5" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583139</v>
+        <v>583177</v>
       </c>
       <c r="R5" t="n">
-        <v>7014270</v>
+        <v>7014165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502190</v>
+        <v>129502188</v>
       </c>
       <c r="B6" t="n">
         <v>91517</v>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583136</v>
+        <v>583139</v>
       </c>
       <c r="R6" t="n">
-        <v>7014210</v>
+        <v>7014270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,49 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502244</v>
+        <v>129502190</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583177</v>
+        <v>583136</v>
       </c>
       <c r="R7" t="n">
-        <v>7014165</v>
+        <v>7014210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495405</v>
+        <v>129495410</v>
       </c>
       <c r="B16" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583128</v>
+        <v>583139</v>
       </c>
       <c r="R16" t="n">
         <v>7014123</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495410</v>
+        <v>129495408</v>
       </c>
       <c r="B17" t="n">
         <v>80149</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583139</v>
+        <v>583204</v>
       </c>
       <c r="R17" t="n">
-        <v>7014123</v>
+        <v>7014157</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495408</v>
+        <v>129495406</v>
       </c>
       <c r="B18" t="n">
         <v>80149</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583204</v>
+        <v>583170</v>
       </c>
       <c r="R18" t="n">
-        <v>7014157</v>
+        <v>7014239</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,32 +2334,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495406</v>
+        <v>129495405</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583170</v>
+        <v>583128</v>
       </c>
       <c r="R19" t="n">
-        <v>7014239</v>
+        <v>7014123</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129495402</v>
+        <v>129495407</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583080</v>
+        <v>583122</v>
       </c>
       <c r="R23" t="n">
-        <v>7014300</v>
+        <v>7014418</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129495407</v>
+        <v>129495402</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583122</v>
+        <v>583080</v>
       </c>
       <c r="R24" t="n">
-        <v>7014418</v>
+        <v>7014300</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129502252</v>
+        <v>129502255</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583105</v>
+        <v>583197</v>
       </c>
       <c r="R25" t="n">
-        <v>7014309</v>
+        <v>7014149</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129502255</v>
+        <v>129502252</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583197</v>
+        <v>583105</v>
       </c>
       <c r="R26" t="n">
-        <v>7014149</v>
+        <v>7014309</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3692,32 +3692,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129502213</v>
+        <v>129502224</v>
       </c>
       <c r="B33" t="n">
-        <v>92006</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583198</v>
+        <v>583151</v>
       </c>
       <c r="R33" t="n">
-        <v>7014144</v>
+        <v>7014252</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3774,21 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3790,32 +3805,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502224</v>
+        <v>129502213</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>92006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,10 +3840,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583151</v>
+        <v>583198</v>
       </c>
       <c r="R34" t="n">
-        <v>7014252</v>
+        <v>7014144</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3872,21 +3887,6 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -3903,10 +3903,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129502234</v>
+        <v>129502192</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583081</v>
+        <v>583114</v>
       </c>
       <c r="R35" t="n">
-        <v>7014394</v>
+        <v>7014270</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129502192</v>
+        <v>129502234</v>
       </c>
       <c r="B36" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583114</v>
+        <v>583081</v>
       </c>
       <c r="R36" t="n">
-        <v>7014270</v>
+        <v>7014394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502182</v>
+        <v>129502236</v>
       </c>
       <c r="B39" t="n">
-        <v>91517</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583174</v>
+        <v>583058</v>
       </c>
       <c r="R39" t="n">
-        <v>7014597</v>
+        <v>7014379</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502236</v>
+        <v>129502235</v>
       </c>
       <c r="B40" t="n">
         <v>80149</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583058</v>
+        <v>583064</v>
       </c>
       <c r="R40" t="n">
-        <v>7014379</v>
+        <v>7014430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,10 +4501,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502235</v>
+        <v>129502221</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583064</v>
+        <v>583411</v>
       </c>
       <c r="R41" t="n">
-        <v>7014430</v>
+        <v>7014380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,6 +4572,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4598,32 +4603,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502221</v>
+        <v>129502182</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583411</v>
+        <v>583174</v>
       </c>
       <c r="R42" t="n">
-        <v>7014380</v>
+        <v>7014597</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,11 +4674,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502209</v>
+        <v>129502205</v>
       </c>
       <c r="B43" t="n">
-        <v>80053</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583167</v>
+        <v>583055</v>
       </c>
       <c r="R43" t="n">
-        <v>7014583</v>
+        <v>7014357</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502226</v>
+        <v>129502215</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>91851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4808,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583156</v>
+        <v>583175</v>
       </c>
       <c r="R44" t="n">
-        <v>7014249</v>
+        <v>7014579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,24 +4876,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4910,32 +4894,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502215</v>
+        <v>129502209</v>
       </c>
       <c r="B45" t="n">
-        <v>91851</v>
+        <v>80053</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4945,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583175</v>
+        <v>583167</v>
       </c>
       <c r="R45" t="n">
-        <v>7014579</v>
+        <v>7014583</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5007,10 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502251</v>
+        <v>129502226</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5018,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5042,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R46" t="n">
-        <v>7014329</v>
+        <v>7014249</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5086,8 +5070,24 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5201,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502205</v>
+        <v>129502251</v>
       </c>
       <c r="B48" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,7 +5239,7 @@
         <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014357</v>
+        <v>7014329</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6310,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502184</v>
+        <v>129502231</v>
       </c>
       <c r="B59" t="n">
-        <v>91517</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583134</v>
+        <v>583345</v>
       </c>
       <c r="R59" t="n">
-        <v>7014134</v>
+        <v>7014389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502231</v>
+        <v>129502227</v>
       </c>
       <c r="B60" t="n">
         <v>80149</v>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583345</v>
+        <v>583045</v>
       </c>
       <c r="R60" t="n">
-        <v>7014389</v>
+        <v>7014432</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,8 +6486,24 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6504,32 +6520,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502227</v>
+        <v>129502184</v>
       </c>
       <c r="B61" t="n">
-        <v>80149</v>
+        <v>91517</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6539,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583045</v>
+        <v>583134</v>
       </c>
       <c r="R61" t="n">
-        <v>7014432</v>
+        <v>7014134</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6583,24 +6599,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R62" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,32 +6714,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502249</v>
+        <v>129502239</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583114</v>
+        <v>583168</v>
       </c>
       <c r="R63" t="n">
-        <v>7014512</v>
+        <v>7014188</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502239</v>
+        <v>129502232</v>
       </c>
       <c r="B64" t="n">
-        <v>58097</v>
+        <v>80149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583168</v>
+        <v>583323</v>
       </c>
       <c r="R64" t="n">
-        <v>7014188</v>
+        <v>7014267</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R65" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,6 +6979,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7005,10 +7010,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B66" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,21 +7021,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7040,10 +7045,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R66" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7076,11 +7081,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,45 +7406,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502245</v>
+        <v>129502240</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583158</v>
+        <v>583138</v>
       </c>
       <c r="R70" t="n">
-        <v>7014222</v>
+        <v>7014124</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7485,6 +7489,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7503,49 +7508,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129502240</v>
+        <v>129502245</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583138</v>
+        <v>583158</v>
       </c>
       <c r="R71" t="n">
-        <v>7014124</v>
+        <v>7014222</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7586,7 +7587,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7605,49 +7605,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502242</v>
+        <v>129502218</v>
       </c>
       <c r="B72" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583095</v>
+        <v>583050</v>
       </c>
       <c r="R72" t="n">
-        <v>7014377</v>
+        <v>7014244</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7688,7 +7684,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7707,32 +7702,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502218</v>
+        <v>129502198</v>
       </c>
       <c r="B73" t="n">
-        <v>91851</v>
+        <v>92271</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7742,10 +7737,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583050</v>
+        <v>583192</v>
       </c>
       <c r="R73" t="n">
-        <v>7014244</v>
+        <v>7014120</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7804,45 +7799,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>92271</v>
+        <v>98727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R74" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,6 +7882,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502256</v>
+        <v>129502233</v>
       </c>
       <c r="B79" t="n">
-        <v>82878</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583110</v>
+        <v>583068</v>
       </c>
       <c r="R79" t="n">
-        <v>7014519</v>
+        <v>7014398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,6 +8360,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8386,10 +8391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502214</v>
+        <v>129502256</v>
       </c>
       <c r="B80" t="n">
-        <v>91851</v>
+        <v>82878</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8402,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8426,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583052</v>
+        <v>583110</v>
       </c>
       <c r="R80" t="n">
-        <v>7014374</v>
+        <v>7014519</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8483,10 +8488,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502233</v>
+        <v>129502214</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>91851</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8494,21 +8499,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8518,10 +8523,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583068</v>
+        <v>583052</v>
       </c>
       <c r="R81" t="n">
-        <v>7014398</v>
+        <v>7014374</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8554,11 +8559,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8585,32 +8585,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129502241</v>
+        <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8620,10 +8620,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583076</v>
+        <v>583137</v>
       </c>
       <c r="R82" t="n">
-        <v>7014398</v>
+        <v>7014134</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8664,7 +8664,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8683,32 +8682,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129502219</v>
+        <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8718,10 +8717,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583137</v>
+        <v>583076</v>
       </c>
       <c r="R83" t="n">
-        <v>7014134</v>
+        <v>7014398</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8762,6 +8761,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129502197</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129502195</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129495403</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502244</v>
+        <v>129502188</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583177</v>
+        <v>583139</v>
       </c>
       <c r="R5" t="n">
-        <v>7014165</v>
+        <v>7014270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1050,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502188</v>
+        <v>129502190</v>
       </c>
       <c r="B6" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583139</v>
+        <v>583136</v>
       </c>
       <c r="R6" t="n">
-        <v>7014270</v>
+        <v>7014210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1165,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502190</v>
+        <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>91517</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583136</v>
+        <v>583177</v>
       </c>
       <c r="R7" t="n">
-        <v>7014210</v>
+        <v>7014165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129502212</v>
+        <v>129502199</v>
       </c>
       <c r="B8" t="n">
-        <v>92006</v>
+        <v>92299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583184</v>
+        <v>583141</v>
       </c>
       <c r="R8" t="n">
-        <v>7014173</v>
+        <v>7014282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,48 +1364,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129502199</v>
+        <v>129495400</v>
       </c>
       <c r="B9" t="n">
-        <v>92271</v>
+        <v>91581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583141</v>
+        <v>583183</v>
       </c>
       <c r="R9" t="n">
-        <v>7014282</v>
+        <v>7014604</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,60 +1449,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129495400</v>
+        <v>129502212</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>92034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583183</v>
+        <v>583184</v>
       </c>
       <c r="R10" t="n">
-        <v>7014604</v>
+        <v>7014173</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1546,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         <v>129502254</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129502189</v>
+        <v>129502186</v>
       </c>
       <c r="B12" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583132</v>
+        <v>583115</v>
       </c>
       <c r="R12" t="n">
-        <v>7014235</v>
+        <v>7014341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129502186</v>
+        <v>129502189</v>
       </c>
       <c r="B13" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583115</v>
+        <v>583132</v>
       </c>
       <c r="R13" t="n">
-        <v>7014341</v>
+        <v>7014235</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
         <v>129502200</v>
       </c>
       <c r="B14" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129502201</v>
       </c>
       <c r="B15" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495410</v>
+        <v>129495406</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583139</v>
+        <v>583170</v>
       </c>
       <c r="R16" t="n">
-        <v>7014123</v>
+        <v>7014239</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495408</v>
+        <v>129495405</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>92034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583204</v>
+        <v>583128</v>
       </c>
       <c r="R17" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495406</v>
+        <v>129502196</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>91581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,37 +2248,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583170</v>
+        <v>583143</v>
       </c>
       <c r="R18" t="n">
-        <v>7014239</v>
+        <v>7014216</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2322,44 +2322,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495405</v>
+        <v>129495410</v>
       </c>
       <c r="B19" t="n">
-        <v>92006</v>
+        <v>80175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583128</v>
+        <v>583139</v>
       </c>
       <c r="R19" t="n">
         <v>7014123</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129502196</v>
+        <v>129495408</v>
       </c>
       <c r="B20" t="n">
-        <v>91553</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583143</v>
+        <v>583204</v>
       </c>
       <c r="R20" t="n">
-        <v>7014216</v>
+        <v>7014157</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>129502220</v>
       </c>
       <c r="B21" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129502202</v>
       </c>
       <c r="B22" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129495407</v>
+        <v>129495402</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>91581</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583122</v>
+        <v>583080</v>
       </c>
       <c r="R23" t="n">
-        <v>7014418</v>
+        <v>7014300</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129495402</v>
+        <v>129495407</v>
       </c>
       <c r="B24" t="n">
-        <v>91553</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583080</v>
+        <v>583122</v>
       </c>
       <c r="R24" t="n">
-        <v>7014300</v>
+        <v>7014418</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2919,7 +2919,7 @@
         <v>129502255</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>129502252</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>129495404</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129495413</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>129502253</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>129495401</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>129495411</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>129495409</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3692,32 +3692,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129502224</v>
+        <v>129502213</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>92034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583151</v>
+        <v>583198</v>
       </c>
       <c r="R33" t="n">
-        <v>7014252</v>
+        <v>7014144</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,21 +3774,6 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3805,32 +3790,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502213</v>
+        <v>129502224</v>
       </c>
       <c r="B34" t="n">
-        <v>92006</v>
+        <v>80175</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3840,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583198</v>
+        <v>583151</v>
       </c>
       <c r="R34" t="n">
-        <v>7014144</v>
+        <v>7014252</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3887,6 +3872,21 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -3906,7 +3906,7 @@
         <v>129502192</v>
       </c>
       <c r="B35" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>129502234</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129502237</v>
+        <v>129502225</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583139</v>
+        <v>583072</v>
       </c>
       <c r="R37" t="n">
-        <v>7014115</v>
+        <v>7014226</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4176,8 +4176,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4194,10 +4210,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129502225</v>
+        <v>129502237</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4229,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583072</v>
+        <v>583139</v>
       </c>
       <c r="R38" t="n">
-        <v>7014226</v>
+        <v>7014115</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4273,24 +4289,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502236</v>
+        <v>129502182</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>91545</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583058</v>
+        <v>583174</v>
       </c>
       <c r="R39" t="n">
-        <v>7014379</v>
+        <v>7014597</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4407,7 +4407,7 @@
         <v>129502235</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>129502221</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,32 +4603,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502182</v>
+        <v>129502236</v>
       </c>
       <c r="B42" t="n">
-        <v>91517</v>
+        <v>80175</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583174</v>
+        <v>583058</v>
       </c>
       <c r="R42" t="n">
-        <v>7014597</v>
+        <v>7014379</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4703,7 +4703,7 @@
         <v>129502205</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>129502215</v>
       </c>
       <c r="B44" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>129502209</v>
       </c>
       <c r="B45" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4991,10 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502226</v>
+        <v>129502247</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5002,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583156</v>
+        <v>583367</v>
       </c>
       <c r="R46" t="n">
-        <v>7014249</v>
+        <v>7014331</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5070,24 +5070,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5104,10 +5088,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502247</v>
+        <v>129502251</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5139,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583367</v>
+        <v>583055</v>
       </c>
       <c r="R47" t="n">
-        <v>7014331</v>
+        <v>7014329</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,10 +5185,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502251</v>
+        <v>129502226</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>80175</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5196,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5236,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R48" t="n">
-        <v>7014329</v>
+        <v>7014249</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5280,8 +5264,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502194</v>
+        <v>129502230</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>80175</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583050</v>
+        <v>583330</v>
       </c>
       <c r="R49" t="n">
-        <v>7014242</v>
+        <v>7014339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502211</v>
+        <v>129502206</v>
       </c>
       <c r="B50" t="n">
-        <v>92006</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583055</v>
+        <v>583074</v>
       </c>
       <c r="R50" t="n">
-        <v>7014372</v>
+        <v>7014351</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502230</v>
+        <v>129502194</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>91581</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583330</v>
+        <v>583050</v>
       </c>
       <c r="R51" t="n">
-        <v>7014339</v>
+        <v>7014242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502206</v>
+        <v>129502211</v>
       </c>
       <c r="B52" t="n">
-        <v>57724</v>
+        <v>92034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583074</v>
+        <v>583055</v>
       </c>
       <c r="R52" t="n">
-        <v>7014351</v>
+        <v>7014372</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
         <v>129502238</v>
       </c>
       <c r="B53" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>129502228</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>129502223</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>129502208</v>
       </c>
       <c r="B56" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6310,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502231</v>
+        <v>129502184</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>91545</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583345</v>
+        <v>583134</v>
       </c>
       <c r="R59" t="n">
-        <v>7014389</v>
+        <v>7014134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6407,10 +6407,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502227</v>
+        <v>129502231</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583045</v>
+        <v>583345</v>
       </c>
       <c r="R60" t="n">
-        <v>7014432</v>
+        <v>7014389</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,24 +6486,8 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6520,32 +6504,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502184</v>
+        <v>129502227</v>
       </c>
       <c r="B61" t="n">
-        <v>91517</v>
+        <v>80175</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6539,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583134</v>
+        <v>583045</v>
       </c>
       <c r="R61" t="n">
-        <v>7014134</v>
+        <v>7014432</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6599,8 +6583,24 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6620,7 +6620,7 @@
         <v>129502249</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6714,32 +6714,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502239</v>
+        <v>129502232</v>
       </c>
       <c r="B63" t="n">
-        <v>58097</v>
+        <v>80175</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583168</v>
+        <v>583323</v>
       </c>
       <c r="R63" t="n">
-        <v>7014188</v>
+        <v>7014267</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502232</v>
+        <v>129502239</v>
       </c>
       <c r="B64" t="n">
-        <v>80149</v>
+        <v>58100</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583323</v>
+        <v>583168</v>
       </c>
       <c r="R64" t="n">
-        <v>7014267</v>
+        <v>7014188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6911,7 +6911,7 @@
         <v>129502229</v>
       </c>
       <c r="B65" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>129502246</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>129502180</v>
       </c>
       <c r="B67" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>129502248</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>129502203</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7406,49 +7406,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502240</v>
+        <v>129502245</v>
       </c>
       <c r="B70" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583138</v>
+        <v>583158</v>
       </c>
       <c r="R70" t="n">
-        <v>7014124</v>
+        <v>7014222</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7489,7 +7485,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7508,45 +7503,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129502245</v>
+        <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583158</v>
+        <v>583138</v>
       </c>
       <c r="R71" t="n">
-        <v>7014222</v>
+        <v>7014124</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7587,6 +7586,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>129502218</v>
       </c>
       <c r="B72" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>129502198</v>
       </c>
       <c r="B73" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>129502193</v>
       </c>
       <c r="B75" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>129502250</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>129502204</v>
       </c>
       <c r="B77" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>129502217</v>
       </c>
       <c r="B78" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502233</v>
+        <v>129502214</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>91879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583068</v>
+        <v>583052</v>
       </c>
       <c r="R79" t="n">
-        <v>7014398</v>
+        <v>7014374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,11 +8360,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8394,7 +8389,7 @@
         <v>129502256</v>
       </c>
       <c r="B80" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8488,10 +8483,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502214</v>
+        <v>129502233</v>
       </c>
       <c r="B81" t="n">
-        <v>91851</v>
+        <v>80175</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8499,21 +8494,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8523,10 +8518,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583052</v>
+        <v>583068</v>
       </c>
       <c r="R81" t="n">
-        <v>7014374</v>
+        <v>7014398</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8559,6 +8554,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8588,7 +8588,7 @@
         <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -971,45 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502188</v>
+        <v>129502244</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583139</v>
+        <v>583177</v>
       </c>
       <c r="R5" t="n">
-        <v>7014270</v>
+        <v>7014165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502190</v>
+        <v>129502188</v>
       </c>
       <c r="B6" t="n">
         <v>91545</v>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583136</v>
+        <v>583139</v>
       </c>
       <c r="R6" t="n">
-        <v>7014210</v>
+        <v>7014270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,49 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502244</v>
+        <v>129502190</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583177</v>
+        <v>583136</v>
       </c>
       <c r="R7" t="n">
-        <v>7014165</v>
+        <v>7014210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129502199</v>
+        <v>129495400</v>
       </c>
       <c r="B8" t="n">
-        <v>92299</v>
+        <v>91581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583141</v>
+        <v>583183</v>
       </c>
       <c r="R8" t="n">
-        <v>7014282</v>
+        <v>7014604</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,60 +1352,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129495400</v>
+        <v>129502212</v>
       </c>
       <c r="B9" t="n">
-        <v>91581</v>
+        <v>92034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583183</v>
+        <v>583184</v>
       </c>
       <c r="R9" t="n">
-        <v>7014604</v>
+        <v>7014173</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,44 +1449,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129502212</v>
+        <v>129502199</v>
       </c>
       <c r="B10" t="n">
-        <v>92034</v>
+        <v>92299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583184</v>
+        <v>583141</v>
       </c>
       <c r="R10" t="n">
-        <v>7014173</v>
+        <v>7014282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495406</v>
+        <v>129502196</v>
       </c>
       <c r="B16" t="n">
-        <v>80175</v>
+        <v>91581</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,37 +2054,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583170</v>
+        <v>583143</v>
       </c>
       <c r="R16" t="n">
-        <v>7014239</v>
+        <v>7014216</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495405</v>
+        <v>129495410</v>
       </c>
       <c r="B17" t="n">
-        <v>92034</v>
+        <v>80175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583128</v>
+        <v>583139</v>
       </c>
       <c r="R17" t="n">
         <v>7014123</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129502196</v>
+        <v>129495408</v>
       </c>
       <c r="B18" t="n">
-        <v>91581</v>
+        <v>80175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,37 +2248,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583143</v>
+        <v>583204</v>
       </c>
       <c r="R18" t="n">
-        <v>7014216</v>
+        <v>7014157</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2322,19 +2322,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495410</v>
+        <v>129495406</v>
       </c>
       <c r="B19" t="n">
         <v>80175</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583139</v>
+        <v>583170</v>
       </c>
       <c r="R19" t="n">
-        <v>7014123</v>
+        <v>7014239</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,32 +2431,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495408</v>
+        <v>129495405</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>92034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583204</v>
+        <v>583128</v>
       </c>
       <c r="R20" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129495411</v>
+        <v>129502224</v>
       </c>
       <c r="B31" t="n">
         <v>80175</v>
@@ -3529,17 +3529,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583068</v>
+        <v>583151</v>
       </c>
       <c r="R31" t="n">
-        <v>7014294</v>
+        <v>7014252</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,25 +3577,41 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129495409</v>
+        <v>129495411</v>
       </c>
       <c r="B32" t="n">
         <v>80175</v>
@@ -3630,10 +3646,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R32" t="n">
-        <v>7014111</v>
+        <v>7014294</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3692,48 +3708,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129502213</v>
+        <v>129495409</v>
       </c>
       <c r="B33" t="n">
-        <v>92034</v>
+        <v>80175</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583198</v>
+        <v>583174</v>
       </c>
       <c r="R33" t="n">
-        <v>7014144</v>
+        <v>7014111</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3771,51 +3787,50 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502224</v>
+        <v>129502213</v>
       </c>
       <c r="B34" t="n">
-        <v>80175</v>
+        <v>92034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,10 +3840,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583151</v>
+        <v>583198</v>
       </c>
       <c r="R34" t="n">
-        <v>7014252</v>
+        <v>7014144</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3872,21 +3887,6 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4097,7 +4097,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129502225</v>
+        <v>129502237</v>
       </c>
       <c r="B37" t="n">
         <v>80175</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583072</v>
+        <v>583139</v>
       </c>
       <c r="R37" t="n">
-        <v>7014226</v>
+        <v>7014115</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4176,24 +4176,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4210,7 +4194,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129502237</v>
+        <v>129502225</v>
       </c>
       <c r="B38" t="n">
         <v>80175</v>
@@ -4245,10 +4229,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583139</v>
+        <v>583072</v>
       </c>
       <c r="R38" t="n">
-        <v>7014115</v>
+        <v>7014226</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,8 +4273,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502230</v>
+        <v>129502194</v>
       </c>
       <c r="B49" t="n">
-        <v>80175</v>
+        <v>91581</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583330</v>
+        <v>583050</v>
       </c>
       <c r="R49" t="n">
-        <v>7014339</v>
+        <v>7014242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502206</v>
+        <v>129502211</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>92034</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583074</v>
+        <v>583055</v>
       </c>
       <c r="R50" t="n">
-        <v>7014351</v>
+        <v>7014372</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502194</v>
+        <v>129502230</v>
       </c>
       <c r="B51" t="n">
-        <v>91581</v>
+        <v>80175</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583050</v>
+        <v>583330</v>
       </c>
       <c r="R51" t="n">
-        <v>7014242</v>
+        <v>7014339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502211</v>
+        <v>129502206</v>
       </c>
       <c r="B52" t="n">
-        <v>92034</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583055</v>
+        <v>583074</v>
       </c>
       <c r="R52" t="n">
-        <v>7014372</v>
+        <v>7014351</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7406,45 +7406,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502245</v>
+        <v>129502240</v>
       </c>
       <c r="B70" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583158</v>
+        <v>583138</v>
       </c>
       <c r="R70" t="n">
-        <v>7014222</v>
+        <v>7014124</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7485,6 +7489,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7503,49 +7508,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129502240</v>
+        <v>129502245</v>
       </c>
       <c r="B71" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583138</v>
+        <v>583158</v>
       </c>
       <c r="R71" t="n">
-        <v>7014124</v>
+        <v>7014222</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7586,7 +7587,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7605,45 +7605,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502218</v>
+        <v>129502242</v>
       </c>
       <c r="B72" t="n">
-        <v>91879</v>
+        <v>98756</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583050</v>
+        <v>583095</v>
       </c>
       <c r="R72" t="n">
-        <v>7014244</v>
+        <v>7014377</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7684,6 +7688,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7799,49 +7804,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502242</v>
+        <v>129502218</v>
       </c>
       <c r="B74" t="n">
-        <v>98756</v>
+        <v>91879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583095</v>
+        <v>583050</v>
       </c>
       <c r="R74" t="n">
-        <v>7014377</v>
+        <v>7014244</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7882,7 +7883,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129502197</v>
       </c>
       <c r="B2" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129502195</v>
       </c>
       <c r="B3" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129495403</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502244</v>
+        <v>129502188</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>91551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583177</v>
+        <v>583139</v>
       </c>
       <c r="R5" t="n">
-        <v>7014165</v>
+        <v>7014270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1050,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502188</v>
+        <v>129502190</v>
       </c>
       <c r="B6" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583139</v>
+        <v>583136</v>
       </c>
       <c r="R6" t="n">
-        <v>7014270</v>
+        <v>7014210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1165,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502190</v>
+        <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583136</v>
+        <v>583177</v>
       </c>
       <c r="R7" t="n">
-        <v>7014210</v>
+        <v>7014165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129495400</v>
+        <v>129502212</v>
       </c>
       <c r="B8" t="n">
-        <v>91581</v>
+        <v>92040</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583183</v>
+        <v>583184</v>
       </c>
       <c r="R8" t="n">
-        <v>7014604</v>
+        <v>7014173</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,44 +1352,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129502212</v>
+        <v>129502199</v>
       </c>
       <c r="B9" t="n">
-        <v>92034</v>
+        <v>92305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583184</v>
+        <v>583141</v>
       </c>
       <c r="R9" t="n">
-        <v>7014173</v>
+        <v>7014282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,48 +1461,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129502199</v>
+        <v>129495400</v>
       </c>
       <c r="B10" t="n">
-        <v>92299</v>
+        <v>91587</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583141</v>
+        <v>583183</v>
       </c>
       <c r="R10" t="n">
-        <v>7014282</v>
+        <v>7014604</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1546,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         <v>129502254</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129502186</v>
+        <v>129502189</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583115</v>
+        <v>583132</v>
       </c>
       <c r="R12" t="n">
-        <v>7014341</v>
+        <v>7014235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129502189</v>
+        <v>129502186</v>
       </c>
       <c r="B13" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583132</v>
+        <v>583115</v>
       </c>
       <c r="R13" t="n">
-        <v>7014235</v>
+        <v>7014341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
         <v>129502200</v>
       </c>
       <c r="B14" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129502201</v>
       </c>
       <c r="B15" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129502196</v>
       </c>
       <c r="B16" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,32 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495410</v>
+        <v>129495405</v>
       </c>
       <c r="B17" t="n">
-        <v>80175</v>
+        <v>92040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583139</v>
+        <v>583128</v>
       </c>
       <c r="R17" t="n">
         <v>7014123</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495408</v>
+        <v>129495410</v>
       </c>
       <c r="B18" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583204</v>
+        <v>583139</v>
       </c>
       <c r="R18" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495406</v>
+        <v>129495408</v>
       </c>
       <c r="B19" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583170</v>
+        <v>583204</v>
       </c>
       <c r="R19" t="n">
-        <v>7014239</v>
+        <v>7014157</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,32 +2431,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495405</v>
+        <v>129495406</v>
       </c>
       <c r="B20" t="n">
-        <v>92034</v>
+        <v>80180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583128</v>
+        <v>583170</v>
       </c>
       <c r="R20" t="n">
-        <v>7014123</v>
+        <v>7014239</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2531,7 +2531,7 @@
         <v>129502220</v>
       </c>
       <c r="B21" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129502202</v>
       </c>
       <c r="B22" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129495402</v>
+        <v>129502255</v>
       </c>
       <c r="B23" t="n">
-        <v>91581</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583080</v>
+        <v>583197</v>
       </c>
       <c r="R23" t="n">
-        <v>7014300</v>
+        <v>7014149</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129495407</v>
+        <v>129502252</v>
       </c>
       <c r="B24" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583122</v>
+        <v>583105</v>
       </c>
       <c r="R24" t="n">
-        <v>7014418</v>
+        <v>7014309</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,22 +2904,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129502255</v>
+        <v>129495402</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>91587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583197</v>
+        <v>583080</v>
       </c>
       <c r="R25" t="n">
-        <v>7014149</v>
+        <v>7014300</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129502252</v>
+        <v>129495407</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583105</v>
+        <v>583122</v>
       </c>
       <c r="R26" t="n">
-        <v>7014309</v>
+        <v>7014418</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
         <v>129495404</v>
       </c>
       <c r="B27" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R28" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,22 +3292,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R29" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
         <v>129495401</v>
       </c>
       <c r="B30" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3498,32 +3498,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129502224</v>
+        <v>129502213</v>
       </c>
       <c r="B31" t="n">
-        <v>80175</v>
+        <v>92040</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583151</v>
+        <v>583198</v>
       </c>
       <c r="R31" t="n">
-        <v>7014252</v>
+        <v>7014144</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3580,21 +3580,6 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3611,10 +3596,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129495411</v>
+        <v>129502224</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3642,17 +3627,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583068</v>
+        <v>583151</v>
       </c>
       <c r="R32" t="n">
-        <v>7014294</v>
+        <v>7014252</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3690,28 +3675,44 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129495409</v>
+        <v>129495411</v>
       </c>
       <c r="B33" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3743,10 +3744,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R33" t="n">
-        <v>7014111</v>
+        <v>7014294</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3805,48 +3806,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502213</v>
+        <v>129495409</v>
       </c>
       <c r="B34" t="n">
-        <v>92034</v>
+        <v>80180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583198</v>
+        <v>583174</v>
       </c>
       <c r="R34" t="n">
-        <v>7014144</v>
+        <v>7014111</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3884,19 +3885,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
         <v>129502192</v>
       </c>
       <c r="B35" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>129502234</v>
       </c>
       <c r="B36" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>129502237</v>
       </c>
       <c r="B37" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>129502225</v>
       </c>
       <c r="B38" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>129502182</v>
       </c>
       <c r="B39" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502235</v>
+        <v>129502236</v>
       </c>
       <c r="B40" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583064</v>
+        <v>583058</v>
       </c>
       <c r="R40" t="n">
-        <v>7014430</v>
+        <v>7014379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,10 +4501,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502221</v>
+        <v>129502235</v>
       </c>
       <c r="B41" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583411</v>
+        <v>583064</v>
       </c>
       <c r="R41" t="n">
-        <v>7014380</v>
+        <v>7014430</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,11 +4572,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4603,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502236</v>
+        <v>129502221</v>
       </c>
       <c r="B42" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583058</v>
+        <v>583411</v>
       </c>
       <c r="R42" t="n">
-        <v>7014379</v>
+        <v>7014380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,6 +4669,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,10 +4700,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502205</v>
+        <v>129502215</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>91885</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583055</v>
+        <v>583175</v>
       </c>
       <c r="R43" t="n">
-        <v>7014357</v>
+        <v>7014579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502215</v>
+        <v>129502247</v>
       </c>
       <c r="B44" t="n">
-        <v>91879</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4808,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583175</v>
+        <v>583367</v>
       </c>
       <c r="R44" t="n">
-        <v>7014579</v>
+        <v>7014331</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4894,32 +4894,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502209</v>
+        <v>129502251</v>
       </c>
       <c r="B45" t="n">
-        <v>80079</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583167</v>
+        <v>583055</v>
       </c>
       <c r="R45" t="n">
-        <v>7014583</v>
+        <v>7014329</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4991,32 +4991,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502247</v>
+        <v>129502209</v>
       </c>
       <c r="B46" t="n">
-        <v>79070</v>
+        <v>80084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583367</v>
+        <v>583167</v>
       </c>
       <c r="R46" t="n">
-        <v>7014331</v>
+        <v>7014583</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502251</v>
+        <v>129502226</v>
       </c>
       <c r="B47" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5099,21 +5099,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R47" t="n">
-        <v>7014329</v>
+        <v>7014249</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,8 +5167,24 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5185,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502226</v>
+        <v>129502205</v>
       </c>
       <c r="B48" t="n">
-        <v>80175</v>
+        <v>57732</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5196,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5220,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014249</v>
+        <v>7014357</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,24 +5280,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5301,7 +5301,7 @@
         <v>129502194</v>
       </c>
       <c r="B49" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>129502211</v>
       </c>
       <c r="B50" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>129502230</v>
       </c>
       <c r="B51" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>129502206</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>129502238</v>
       </c>
       <c r="B53" t="n">
-        <v>80211</v>
+        <v>80216</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>129502228</v>
       </c>
       <c r="B54" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>129502223</v>
       </c>
       <c r="B55" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>129502208</v>
       </c>
       <c r="B56" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>129502184</v>
       </c>
       <c r="B59" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>129502231</v>
       </c>
       <c r="B60" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>129502227</v>
       </c>
       <c r="B61" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502249</v>
+        <v>129502232</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583114</v>
+        <v>583323</v>
       </c>
       <c r="R62" t="n">
-        <v>7014512</v>
+        <v>7014267</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,32 +6714,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502232</v>
+        <v>129502239</v>
       </c>
       <c r="B63" t="n">
-        <v>80175</v>
+        <v>58105</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583323</v>
+        <v>583168</v>
       </c>
       <c r="R63" t="n">
-        <v>7014267</v>
+        <v>7014188</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502239</v>
+        <v>129502249</v>
       </c>
       <c r="B64" t="n">
-        <v>58100</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583168</v>
+        <v>583114</v>
       </c>
       <c r="R64" t="n">
-        <v>7014188</v>
+        <v>7014512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B65" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R65" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,11 +6979,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7010,10 +7005,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B66" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7021,21 +7016,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7045,10 +7040,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R66" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7081,6 +7076,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7110,7 +7110,7 @@
         <v>129502180</v>
       </c>
       <c r="B67" t="n">
-        <v>83039</v>
+        <v>83044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>129502248</v>
       </c>
       <c r="B68" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>129502203</v>
       </c>
       <c r="B69" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7406,49 +7406,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502240</v>
+        <v>129502245</v>
       </c>
       <c r="B70" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583138</v>
+        <v>583158</v>
       </c>
       <c r="R70" t="n">
-        <v>7014124</v>
+        <v>7014222</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7489,7 +7485,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7508,45 +7503,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129502245</v>
+        <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583158</v>
+        <v>583138</v>
       </c>
       <c r="R71" t="n">
-        <v>7014222</v>
+        <v>7014124</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7587,6 +7586,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7605,49 +7605,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502242</v>
+        <v>129502218</v>
       </c>
       <c r="B72" t="n">
-        <v>98756</v>
+        <v>91885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583095</v>
+        <v>583050</v>
       </c>
       <c r="R72" t="n">
-        <v>7014377</v>
+        <v>7014244</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7688,7 +7684,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7710,7 +7705,7 @@
         <v>129502198</v>
       </c>
       <c r="B73" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7804,45 +7799,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502218</v>
+        <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>91879</v>
+        <v>98768</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583050</v>
+        <v>583095</v>
       </c>
       <c r="R74" t="n">
-        <v>7014244</v>
+        <v>7014377</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,6 +7882,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>129502193</v>
       </c>
       <c r="B75" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>129502250</v>
       </c>
       <c r="B76" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>129502204</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>129502217</v>
       </c>
       <c r="B78" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502214</v>
+        <v>129502233</v>
       </c>
       <c r="B79" t="n">
-        <v>91879</v>
+        <v>80180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583052</v>
+        <v>583068</v>
       </c>
       <c r="R79" t="n">
-        <v>7014374</v>
+        <v>7014398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,6 +8360,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8389,7 +8394,7 @@
         <v>129502256</v>
       </c>
       <c r="B80" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8483,10 +8488,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502233</v>
+        <v>129502214</v>
       </c>
       <c r="B81" t="n">
-        <v>80175</v>
+        <v>91885</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8494,21 +8499,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8518,10 +8523,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583068</v>
+        <v>583052</v>
       </c>
       <c r="R81" t="n">
-        <v>7014398</v>
+        <v>7014374</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8554,11 +8559,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8588,7 +8588,7 @@
         <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129502197</v>
       </c>
       <c r="B2" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129502195</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129495403</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,45 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502188</v>
+        <v>129502244</v>
       </c>
       <c r="B5" t="n">
-        <v>91551</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583139</v>
+        <v>583177</v>
       </c>
       <c r="R5" t="n">
-        <v>7014270</v>
+        <v>7014165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502190</v>
+        <v>129502188</v>
       </c>
       <c r="B6" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583136</v>
+        <v>583139</v>
       </c>
       <c r="R6" t="n">
-        <v>7014210</v>
+        <v>7014270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,49 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502244</v>
+        <v>129502190</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>91552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583177</v>
+        <v>583136</v>
       </c>
       <c r="R7" t="n">
-        <v>7014165</v>
+        <v>7014210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>129502212</v>
       </c>
       <c r="B8" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,48 +1364,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129502199</v>
+        <v>129495400</v>
       </c>
       <c r="B9" t="n">
-        <v>92305</v>
+        <v>91588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583141</v>
+        <v>583183</v>
       </c>
       <c r="R9" t="n">
-        <v>7014282</v>
+        <v>7014604</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,60 +1449,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129495400</v>
+        <v>129502199</v>
       </c>
       <c r="B10" t="n">
-        <v>91587</v>
+        <v>92306</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583183</v>
+        <v>583141</v>
       </c>
       <c r="R10" t="n">
-        <v>7014604</v>
+        <v>7014282</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1546,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1561,7 +1561,7 @@
         <v>129502254</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129502189</v>
       </c>
       <c r="B12" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129502186</v>
       </c>
       <c r="B13" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>129502200</v>
       </c>
       <c r="B14" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129502201</v>
       </c>
       <c r="B15" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,48 +2043,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129502196</v>
+        <v>129495405</v>
       </c>
       <c r="B16" t="n">
-        <v>91587</v>
+        <v>92041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583143</v>
+        <v>583128</v>
       </c>
       <c r="R16" t="n">
-        <v>7014216</v>
+        <v>7014123</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495405</v>
+        <v>129495410</v>
       </c>
       <c r="B17" t="n">
-        <v>92040</v>
+        <v>80181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583128</v>
+        <v>583139</v>
       </c>
       <c r="R17" t="n">
         <v>7014123</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495410</v>
+        <v>129495408</v>
       </c>
       <c r="B18" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583139</v>
+        <v>583204</v>
       </c>
       <c r="R18" t="n">
-        <v>7014123</v>
+        <v>7014157</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495408</v>
+        <v>129495406</v>
       </c>
       <c r="B19" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583204</v>
+        <v>583170</v>
       </c>
       <c r="R19" t="n">
-        <v>7014157</v>
+        <v>7014239</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495406</v>
+        <v>129502196</v>
       </c>
       <c r="B20" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583170</v>
+        <v>583143</v>
       </c>
       <c r="R20" t="n">
-        <v>7014239</v>
+        <v>7014216</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>129502220</v>
       </c>
       <c r="B21" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129502202</v>
       </c>
       <c r="B22" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129502255</v>
+        <v>129495407</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583197</v>
+        <v>583122</v>
       </c>
       <c r="R23" t="n">
-        <v>7014149</v>
+        <v>7014418</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129502252</v>
+        <v>129495402</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583105</v>
+        <v>583080</v>
       </c>
       <c r="R24" t="n">
-        <v>7014309</v>
+        <v>7014300</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,22 +2904,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129495402</v>
+        <v>129502255</v>
       </c>
       <c r="B25" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583080</v>
+        <v>583197</v>
       </c>
       <c r="R25" t="n">
-        <v>7014300</v>
+        <v>7014149</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129495407</v>
+        <v>129502252</v>
       </c>
       <c r="B26" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583122</v>
+        <v>583105</v>
       </c>
       <c r="R26" t="n">
-        <v>7014418</v>
+        <v>7014309</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
         <v>129495404</v>
       </c>
       <c r="B27" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R28" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,22 +3292,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R29" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
         <v>129495401</v>
       </c>
       <c r="B30" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3498,48 +3498,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129502213</v>
+        <v>129495411</v>
       </c>
       <c r="B31" t="n">
-        <v>92040</v>
+        <v>80181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583198</v>
+        <v>583068</v>
       </c>
       <c r="R31" t="n">
-        <v>7014144</v>
+        <v>7014294</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,29 +3577,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129502224</v>
+        <v>129495409</v>
       </c>
       <c r="B32" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3627,17 +3626,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583151</v>
+        <v>583174</v>
       </c>
       <c r="R32" t="n">
-        <v>7014252</v>
+        <v>7014111</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3675,82 +3674,66 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129495411</v>
+        <v>129502213</v>
       </c>
       <c r="B33" t="n">
-        <v>80180</v>
+        <v>92041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583068</v>
+        <v>583198</v>
       </c>
       <c r="R33" t="n">
-        <v>7014294</v>
+        <v>7014144</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3788,28 +3771,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129495409</v>
+        <v>129502224</v>
       </c>
       <c r="B34" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3837,17 +3821,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583174</v>
+        <v>583151</v>
       </c>
       <c r="R34" t="n">
-        <v>7014111</v>
+        <v>7014252</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3885,28 +3869,44 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129502192</v>
+        <v>129502234</v>
       </c>
       <c r="B35" t="n">
-        <v>91587</v>
+        <v>80181</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583114</v>
+        <v>583081</v>
       </c>
       <c r="R35" t="n">
-        <v>7014270</v>
+        <v>7014394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129502234</v>
+        <v>129502192</v>
       </c>
       <c r="B36" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583081</v>
+        <v>583114</v>
       </c>
       <c r="R36" t="n">
-        <v>7014394</v>
+        <v>7014270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4100,7 +4100,7 @@
         <v>129502237</v>
       </c>
       <c r="B37" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>129502225</v>
       </c>
       <c r="B38" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502182</v>
+        <v>129502221</v>
       </c>
       <c r="B39" t="n">
-        <v>91551</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583174</v>
+        <v>583411</v>
       </c>
       <c r="R39" t="n">
-        <v>7014597</v>
+        <v>7014380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,6 +4378,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4404,32 +4409,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502236</v>
+        <v>129502182</v>
       </c>
       <c r="B40" t="n">
-        <v>80180</v>
+        <v>91552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583058</v>
+        <v>583174</v>
       </c>
       <c r="R40" t="n">
-        <v>7014379</v>
+        <v>7014597</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,10 +4506,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502235</v>
+        <v>129502236</v>
       </c>
       <c r="B41" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4536,10 +4541,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583064</v>
+        <v>583058</v>
       </c>
       <c r="R41" t="n">
-        <v>7014430</v>
+        <v>7014379</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4598,10 +4603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502221</v>
+        <v>129502235</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4609,21 +4614,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583411</v>
+        <v>583064</v>
       </c>
       <c r="R42" t="n">
-        <v>7014380</v>
+        <v>7014430</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,11 +4674,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502215</v>
+        <v>129502209</v>
       </c>
       <c r="B43" t="n">
-        <v>91885</v>
+        <v>80085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583175</v>
+        <v>583167</v>
       </c>
       <c r="R43" t="n">
-        <v>7014579</v>
+        <v>7014583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502247</v>
+        <v>129502226</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4808,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583367</v>
+        <v>583156</v>
       </c>
       <c r="R44" t="n">
-        <v>7014331</v>
+        <v>7014249</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,8 +4876,24 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4894,10 +4910,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502251</v>
+        <v>129502205</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,21 +4921,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4932,7 +4948,7 @@
         <v>583055</v>
       </c>
       <c r="R45" t="n">
-        <v>7014329</v>
+        <v>7014357</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4991,32 +5007,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502209</v>
+        <v>129502247</v>
       </c>
       <c r="B46" t="n">
-        <v>80084</v>
+        <v>79076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583167</v>
+        <v>583367</v>
       </c>
       <c r="R46" t="n">
-        <v>7014583</v>
+        <v>7014331</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,10 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502226</v>
+        <v>129502251</v>
       </c>
       <c r="B47" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5099,21 +5115,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5123,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R47" t="n">
-        <v>7014249</v>
+        <v>7014329</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,24 +5183,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5201,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502205</v>
+        <v>129502215</v>
       </c>
       <c r="B48" t="n">
-        <v>57732</v>
+        <v>91886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583055</v>
+        <v>583175</v>
       </c>
       <c r="R48" t="n">
-        <v>7014357</v>
+        <v>7014579</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
         <v>129502194</v>
       </c>
       <c r="B49" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>129502211</v>
       </c>
       <c r="B50" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502230</v>
+        <v>129502206</v>
       </c>
       <c r="B51" t="n">
-        <v>80180</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583330</v>
+        <v>583074</v>
       </c>
       <c r="R51" t="n">
-        <v>7014339</v>
+        <v>7014351</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,10 +5589,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502206</v>
+        <v>129502230</v>
       </c>
       <c r="B52" t="n">
-        <v>57732</v>
+        <v>80181</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5600,21 +5600,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583074</v>
+        <v>583330</v>
       </c>
       <c r="R52" t="n">
-        <v>7014351</v>
+        <v>7014339</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
         <v>129502238</v>
       </c>
       <c r="B53" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>129502228</v>
       </c>
       <c r="B54" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>129502223</v>
       </c>
       <c r="B55" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>129502208</v>
       </c>
       <c r="B56" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6111,45 +6111,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502216</v>
+        <v>129502243</v>
       </c>
       <c r="B57" t="n">
-        <v>91885</v>
+        <v>98769</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583173</v>
+        <v>583046</v>
       </c>
       <c r="R57" t="n">
-        <v>7014589</v>
+        <v>7014393</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6190,6 +6194,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6208,49 +6213,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502243</v>
+        <v>129502216</v>
       </c>
       <c r="B58" t="n">
-        <v>98768</v>
+        <v>91886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583046</v>
+        <v>583173</v>
       </c>
       <c r="R58" t="n">
-        <v>7014393</v>
+        <v>7014589</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6291,7 +6292,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6310,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502184</v>
+        <v>129502231</v>
       </c>
       <c r="B59" t="n">
-        <v>91551</v>
+        <v>80181</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583134</v>
+        <v>583345</v>
       </c>
       <c r="R59" t="n">
-        <v>7014134</v>
+        <v>7014389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6407,10 +6407,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502231</v>
+        <v>129502227</v>
       </c>
       <c r="B60" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583345</v>
+        <v>583045</v>
       </c>
       <c r="R60" t="n">
-        <v>7014389</v>
+        <v>7014432</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,8 +6486,24 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6504,32 +6520,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502227</v>
+        <v>129502184</v>
       </c>
       <c r="B61" t="n">
-        <v>80180</v>
+        <v>91552</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6539,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583045</v>
+        <v>583134</v>
       </c>
       <c r="R61" t="n">
-        <v>7014432</v>
+        <v>7014134</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6583,24 +6599,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B62" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R62" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,32 +6714,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502239</v>
+        <v>129502232</v>
       </c>
       <c r="B63" t="n">
-        <v>58105</v>
+        <v>80181</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583168</v>
+        <v>583323</v>
       </c>
       <c r="R63" t="n">
-        <v>7014188</v>
+        <v>7014267</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502249</v>
+        <v>129502239</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>58106</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583114</v>
+        <v>583168</v>
       </c>
       <c r="R64" t="n">
-        <v>7014512</v>
+        <v>7014188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6911,7 +6911,7 @@
         <v>129502246</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>129502229</v>
       </c>
       <c r="B66" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129502180</v>
+        <v>129502203</v>
       </c>
       <c r="B67" t="n">
-        <v>83044</v>
+        <v>57896</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7118,34 +7118,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583051</v>
+        <v>583138</v>
       </c>
       <c r="R67" t="n">
-        <v>7014327</v>
+        <v>7014232</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7207,7 +7215,7 @@
         <v>129502248</v>
       </c>
       <c r="B68" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7301,10 +7309,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129502203</v>
+        <v>129502180</v>
       </c>
       <c r="B69" t="n">
-        <v>57895</v>
+        <v>83045</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7312,42 +7320,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583138</v>
+        <v>583051</v>
       </c>
       <c r="R69" t="n">
-        <v>7014232</v>
+        <v>7014327</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
         <v>129502245</v>
       </c>
       <c r="B70" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>129502218</v>
       </c>
       <c r="B72" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>129502198</v>
       </c>
       <c r="B73" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502193</v>
+        <v>129502250</v>
       </c>
       <c r="B75" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R75" t="n">
-        <v>7014589</v>
+        <v>7014344</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502250</v>
+        <v>129502193</v>
       </c>
       <c r="B76" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R76" t="n">
-        <v>7014344</v>
+        <v>7014589</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8098,7 +8098,7 @@
         <v>129502204</v>
       </c>
       <c r="B77" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>129502217</v>
       </c>
       <c r="B78" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502233</v>
+        <v>129502214</v>
       </c>
       <c r="B79" t="n">
-        <v>80180</v>
+        <v>91886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583068</v>
+        <v>583052</v>
       </c>
       <c r="R79" t="n">
-        <v>7014398</v>
+        <v>7014374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,11 +8360,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8394,7 +8389,7 @@
         <v>129502256</v>
       </c>
       <c r="B80" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8488,10 +8483,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502214</v>
+        <v>129502233</v>
       </c>
       <c r="B81" t="n">
-        <v>91885</v>
+        <v>80181</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8499,21 +8494,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8523,10 +8518,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583052</v>
+        <v>583068</v>
       </c>
       <c r="R81" t="n">
-        <v>7014374</v>
+        <v>7014398</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8559,6 +8554,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8588,7 +8588,7 @@
         <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -2043,48 +2043,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495405</v>
+        <v>129502196</v>
       </c>
       <c r="B16" t="n">
-        <v>92041</v>
+        <v>91588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583128</v>
+        <v>583143</v>
       </c>
       <c r="R16" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495410</v>
+        <v>129495405</v>
       </c>
       <c r="B17" t="n">
-        <v>80181</v>
+        <v>92041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583139</v>
+        <v>583128</v>
       </c>
       <c r="R17" t="n">
         <v>7014123</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495408</v>
+        <v>129495410</v>
       </c>
       <c r="B18" t="n">
         <v>80181</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583204</v>
+        <v>583139</v>
       </c>
       <c r="R18" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495406</v>
+        <v>129495408</v>
       </c>
       <c r="B19" t="n">
         <v>80181</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583170</v>
+        <v>583204</v>
       </c>
       <c r="R19" t="n">
-        <v>7014239</v>
+        <v>7014157</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129502196</v>
+        <v>129495406</v>
       </c>
       <c r="B20" t="n">
-        <v>91588</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583143</v>
+        <v>583170</v>
       </c>
       <c r="R20" t="n">
-        <v>7014216</v>
+        <v>7014239</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502221</v>
+        <v>129502182</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>91552</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583411</v>
+        <v>583174</v>
       </c>
       <c r="R39" t="n">
-        <v>7014380</v>
+        <v>7014597</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,11 +4378,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4409,32 +4404,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502182</v>
+        <v>129502236</v>
       </c>
       <c r="B40" t="n">
-        <v>91552</v>
+        <v>80181</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583174</v>
+        <v>583058</v>
       </c>
       <c r="R40" t="n">
-        <v>7014597</v>
+        <v>7014379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4506,7 +4501,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502236</v>
+        <v>129502235</v>
       </c>
       <c r="B41" t="n">
         <v>80181</v>
@@ -4541,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583058</v>
+        <v>583064</v>
       </c>
       <c r="R41" t="n">
-        <v>7014379</v>
+        <v>7014430</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4603,10 +4598,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502235</v>
+        <v>129502221</v>
       </c>
       <c r="B42" t="n">
-        <v>80181</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4614,21 +4609,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583064</v>
+        <v>583411</v>
       </c>
       <c r="R42" t="n">
-        <v>7014430</v>
+        <v>7014380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,6 +4669,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502206</v>
+        <v>129502230</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>80181</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583074</v>
+        <v>583330</v>
       </c>
       <c r="R51" t="n">
-        <v>7014351</v>
+        <v>7014339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,10 +5589,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502230</v>
+        <v>129502206</v>
       </c>
       <c r="B52" t="n">
-        <v>80181</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5600,21 +5600,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583330</v>
+        <v>583074</v>
       </c>
       <c r="R52" t="n">
-        <v>7014339</v>
+        <v>7014351</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7702,45 +7702,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B73" t="n">
-        <v>92306</v>
+        <v>98769</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R73" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7781,6 +7785,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7799,49 +7804,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B74" t="n">
-        <v>98769</v>
+        <v>92306</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R74" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7882,7 +7883,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129502197</v>
       </c>
       <c r="B2" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129502195</v>
       </c>
       <c r="B3" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129502244</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129502188</v>
       </c>
       <c r="B6" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129502190</v>
       </c>
       <c r="B7" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129502212</v>
+        <v>129495400</v>
       </c>
       <c r="B8" t="n">
-        <v>92041</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583184</v>
+        <v>583183</v>
       </c>
       <c r="R8" t="n">
-        <v>7014173</v>
+        <v>7014604</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,60 +1352,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129495400</v>
+        <v>129502212</v>
       </c>
       <c r="B9" t="n">
-        <v>91588</v>
+        <v>92046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583183</v>
+        <v>583184</v>
       </c>
       <c r="R9" t="n">
-        <v>7014604</v>
+        <v>7014173</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,12 +1449,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1464,7 +1464,7 @@
         <v>129502199</v>
       </c>
       <c r="B10" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129502254</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129502189</v>
       </c>
       <c r="B12" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129502186</v>
       </c>
       <c r="B13" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>129502200</v>
       </c>
       <c r="B14" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129502201</v>
       </c>
       <c r="B15" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129502196</v>
       </c>
       <c r="B16" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>129495405</v>
       </c>
       <c r="B17" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>129495410</v>
       </c>
       <c r="B18" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>129495408</v>
       </c>
       <c r="B19" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>129495406</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>129502220</v>
       </c>
       <c r="B21" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129502202</v>
       </c>
       <c r="B22" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129495407</v>
+        <v>129495402</v>
       </c>
       <c r="B23" t="n">
-        <v>80181</v>
+        <v>91593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583122</v>
+        <v>583080</v>
       </c>
       <c r="R23" t="n">
-        <v>7014418</v>
+        <v>7014300</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129495402</v>
+        <v>129495407</v>
       </c>
       <c r="B24" t="n">
-        <v>91588</v>
+        <v>80186</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583080</v>
+        <v>583122</v>
       </c>
       <c r="R24" t="n">
-        <v>7014300</v>
+        <v>7014418</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2919,7 +2919,7 @@
         <v>129502255</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>129502252</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>129495413</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>129502253</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>129495401</v>
       </c>
       <c r="B30" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3498,48 +3498,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129495411</v>
+        <v>129502213</v>
       </c>
       <c r="B31" t="n">
-        <v>80181</v>
+        <v>92046</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583068</v>
+        <v>583198</v>
       </c>
       <c r="R31" t="n">
-        <v>7014294</v>
+        <v>7014144</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,28 +3577,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129495409</v>
+        <v>129502224</v>
       </c>
       <c r="B32" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3626,17 +3627,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583174</v>
+        <v>583151</v>
       </c>
       <c r="R32" t="n">
-        <v>7014111</v>
+        <v>7014252</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3674,66 +3675,82 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129502213</v>
+        <v>129495411</v>
       </c>
       <c r="B33" t="n">
-        <v>92041</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583198</v>
+        <v>583068</v>
       </c>
       <c r="R33" t="n">
-        <v>7014144</v>
+        <v>7014294</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3771,29 +3788,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502224</v>
+        <v>129495409</v>
       </c>
       <c r="B34" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3821,17 +3837,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583151</v>
+        <v>583174</v>
       </c>
       <c r="R34" t="n">
-        <v>7014252</v>
+        <v>7014111</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3869,34 +3885,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
         <v>129502234</v>
       </c>
       <c r="B35" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>129502192</v>
       </c>
       <c r="B36" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129502237</v>
+        <v>129502225</v>
       </c>
       <c r="B37" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583139</v>
+        <v>583072</v>
       </c>
       <c r="R37" t="n">
-        <v>7014115</v>
+        <v>7014226</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4176,8 +4176,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4194,10 +4210,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129502225</v>
+        <v>129502237</v>
       </c>
       <c r="B38" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4229,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583072</v>
+        <v>583139</v>
       </c>
       <c r="R38" t="n">
-        <v>7014226</v>
+        <v>7014115</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4273,24 +4289,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502182</v>
+        <v>129502235</v>
       </c>
       <c r="B39" t="n">
-        <v>91552</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583174</v>
+        <v>583064</v>
       </c>
       <c r="R39" t="n">
-        <v>7014597</v>
+        <v>7014430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4407,7 +4407,7 @@
         <v>129502236</v>
       </c>
       <c r="B40" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4501,32 +4501,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502235</v>
+        <v>129502182</v>
       </c>
       <c r="B41" t="n">
-        <v>80181</v>
+        <v>91557</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583064</v>
+        <v>583174</v>
       </c>
       <c r="R41" t="n">
-        <v>7014430</v>
+        <v>7014597</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502209</v>
+        <v>129502215</v>
       </c>
       <c r="B43" t="n">
-        <v>80085</v>
+        <v>91891</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583167</v>
+        <v>583175</v>
       </c>
       <c r="R43" t="n">
-        <v>7014583</v>
+        <v>7014579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4800,7 +4800,7 @@
         <v>129502226</v>
       </c>
       <c r="B44" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4910,32 +4910,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502205</v>
+        <v>129502209</v>
       </c>
       <c r="B45" t="n">
-        <v>57733</v>
+        <v>80090</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583055</v>
+        <v>583167</v>
       </c>
       <c r="R45" t="n">
-        <v>7014357</v>
+        <v>7014583</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5007,10 +5007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502247</v>
+        <v>129502205</v>
       </c>
       <c r="B46" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5018,21 +5018,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583367</v>
+        <v>583055</v>
       </c>
       <c r="R46" t="n">
-        <v>7014331</v>
+        <v>7014357</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502251</v>
+        <v>129502247</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583055</v>
+        <v>583367</v>
       </c>
       <c r="R47" t="n">
-        <v>7014329</v>
+        <v>7014331</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502215</v>
+        <v>129502251</v>
       </c>
       <c r="B48" t="n">
-        <v>91886</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583175</v>
+        <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014579</v>
+        <v>7014329</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502194</v>
+        <v>129502230</v>
       </c>
       <c r="B49" t="n">
-        <v>91588</v>
+        <v>80186</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583050</v>
+        <v>583330</v>
       </c>
       <c r="R49" t="n">
-        <v>7014242</v>
+        <v>7014339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502211</v>
+        <v>129502194</v>
       </c>
       <c r="B50" t="n">
-        <v>92041</v>
+        <v>91593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583055</v>
+        <v>583050</v>
       </c>
       <c r="R50" t="n">
-        <v>7014372</v>
+        <v>7014242</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,32 +5492,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502230</v>
+        <v>129502211</v>
       </c>
       <c r="B51" t="n">
-        <v>80181</v>
+        <v>92046</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583330</v>
+        <v>583055</v>
       </c>
       <c r="R51" t="n">
-        <v>7014339</v>
+        <v>7014372</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5689,7 +5689,7 @@
         <v>129502238</v>
       </c>
       <c r="B53" t="n">
-        <v>80217</v>
+        <v>80222</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>129502228</v>
       </c>
       <c r="B54" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>129502208</v>
       </c>
       <c r="B56" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6111,49 +6111,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502243</v>
+        <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>98769</v>
+        <v>91891</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583046</v>
+        <v>583173</v>
       </c>
       <c r="R57" t="n">
-        <v>7014393</v>
+        <v>7014589</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,7 +6190,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6213,45 +6208,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502216</v>
+        <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>91886</v>
+        <v>98774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583173</v>
+        <v>583046</v>
       </c>
       <c r="R58" t="n">
-        <v>7014589</v>
+        <v>7014393</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6292,6 +6291,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6310,10 +6310,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502231</v>
+        <v>129502227</v>
       </c>
       <c r="B59" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583345</v>
+        <v>583045</v>
       </c>
       <c r="R59" t="n">
-        <v>7014389</v>
+        <v>7014432</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6389,8 +6389,24 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6407,10 +6423,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502227</v>
+        <v>129502231</v>
       </c>
       <c r="B60" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6442,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583045</v>
+        <v>583345</v>
       </c>
       <c r="R60" t="n">
-        <v>7014432</v>
+        <v>7014389</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,24 +6502,8 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6523,7 +6523,7 @@
         <v>129502184</v>
       </c>
       <c r="B61" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>129502249</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>129502232</v>
       </c>
       <c r="B63" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R65" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,6 +6979,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7005,10 +7010,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B66" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,21 +7021,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7040,10 +7045,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R66" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7076,11 +7081,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7107,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129502203</v>
+        <v>129502248</v>
       </c>
       <c r="B67" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7118,42 +7118,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583138</v>
+        <v>583117</v>
       </c>
       <c r="R67" t="n">
-        <v>7014232</v>
+        <v>7014262</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7212,10 +7204,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502248</v>
+        <v>129502180</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>83050</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7223,21 +7215,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7247,10 +7239,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583117</v>
+        <v>583051</v>
       </c>
       <c r="R68" t="n">
-        <v>7014262</v>
+        <v>7014327</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7309,10 +7301,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129502180</v>
+        <v>129502203</v>
       </c>
       <c r="B69" t="n">
-        <v>83045</v>
+        <v>57896</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7320,34 +7312,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583051</v>
+        <v>583138</v>
       </c>
       <c r="R69" t="n">
-        <v>7014327</v>
+        <v>7014232</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
         <v>129502245</v>
       </c>
       <c r="B70" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>129502218</v>
       </c>
       <c r="B72" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7702,49 +7702,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B73" t="n">
-        <v>98769</v>
+        <v>92311</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R73" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7785,7 +7781,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7804,45 +7799,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>92306</v>
+        <v>98774</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R74" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,6 +7882,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502250</v>
+        <v>129502193</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R75" t="n">
-        <v>7014344</v>
+        <v>7014589</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502193</v>
+        <v>129502250</v>
       </c>
       <c r="B76" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R76" t="n">
-        <v>7014589</v>
+        <v>7014344</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8195,7 +8195,7 @@
         <v>129502217</v>
       </c>
       <c r="B78" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502214</v>
+        <v>129502233</v>
       </c>
       <c r="B79" t="n">
-        <v>91886</v>
+        <v>80186</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583052</v>
+        <v>583068</v>
       </c>
       <c r="R79" t="n">
-        <v>7014374</v>
+        <v>7014398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,6 +8360,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8386,10 +8391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502256</v>
+        <v>129502214</v>
       </c>
       <c r="B80" t="n">
-        <v>82911</v>
+        <v>91891</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8402,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8426,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583110</v>
+        <v>583052</v>
       </c>
       <c r="R80" t="n">
-        <v>7014519</v>
+        <v>7014374</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8483,10 +8488,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502233</v>
+        <v>129502256</v>
       </c>
       <c r="B81" t="n">
-        <v>80181</v>
+        <v>82916</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8494,21 +8499,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8518,10 +8523,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583068</v>
+        <v>583110</v>
       </c>
       <c r="R81" t="n">
-        <v>7014398</v>
+        <v>7014519</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8554,11 +8559,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8585,32 +8585,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129502219</v>
+        <v>129502241</v>
       </c>
       <c r="B82" t="n">
-        <v>91886</v>
+        <v>98774</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8620,10 +8620,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583137</v>
+        <v>583076</v>
       </c>
       <c r="R82" t="n">
-        <v>7014134</v>
+        <v>7014398</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8664,6 +8664,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8682,32 +8683,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129502241</v>
+        <v>129502219</v>
       </c>
       <c r="B83" t="n">
-        <v>98769</v>
+        <v>91891</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8717,10 +8718,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583076</v>
+        <v>583137</v>
       </c>
       <c r="R83" t="n">
-        <v>7014398</v>
+        <v>7014134</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8761,7 +8762,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -971,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502244</v>
+        <v>129502188</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>91557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583177</v>
+        <v>583139</v>
       </c>
       <c r="R5" t="n">
-        <v>7014165</v>
+        <v>7014270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1050,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502188</v>
+        <v>129502190</v>
       </c>
       <c r="B6" t="n">
         <v>91557</v>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583139</v>
+        <v>583136</v>
       </c>
       <c r="R6" t="n">
-        <v>7014270</v>
+        <v>7014210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1165,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502190</v>
+        <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>91557</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583136</v>
+        <v>583177</v>
       </c>
       <c r="R7" t="n">
-        <v>7014210</v>
+        <v>7014165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2043,48 +2043,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129502196</v>
+        <v>129495405</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583143</v>
+        <v>583128</v>
       </c>
       <c r="R16" t="n">
-        <v>7014216</v>
+        <v>7014123</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495405</v>
+        <v>129495408</v>
       </c>
       <c r="B17" t="n">
-        <v>92046</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583128</v>
+        <v>583204</v>
       </c>
       <c r="R17" t="n">
-        <v>7014123</v>
+        <v>7014157</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495408</v>
+        <v>129495406</v>
       </c>
       <c r="B19" t="n">
         <v>80186</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583204</v>
+        <v>583170</v>
       </c>
       <c r="R19" t="n">
-        <v>7014157</v>
+        <v>7014239</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495406</v>
+        <v>129502196</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583170</v>
+        <v>583143</v>
       </c>
       <c r="R20" t="n">
-        <v>7014239</v>
+        <v>7014216</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129502255</v>
+        <v>129502252</v>
       </c>
       <c r="B25" t="n">
         <v>79081</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583197</v>
+        <v>583105</v>
       </c>
       <c r="R25" t="n">
-        <v>7014149</v>
+        <v>7014309</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129502252</v>
+        <v>129502255</v>
       </c>
       <c r="B26" t="n">
         <v>79081</v>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583105</v>
+        <v>583197</v>
       </c>
       <c r="R26" t="n">
-        <v>7014309</v>
+        <v>7014149</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R28" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R29" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3596,7 +3596,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129502224</v>
+        <v>129495409</v>
       </c>
       <c r="B32" t="n">
         <v>80186</v>
@@ -3627,17 +3627,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583151</v>
+        <v>583174</v>
       </c>
       <c r="R32" t="n">
-        <v>7014252</v>
+        <v>7014111</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3675,34 +3675,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3806,7 +3790,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129495409</v>
+        <v>129502224</v>
       </c>
       <c r="B34" t="n">
         <v>80186</v>
@@ -3837,17 +3821,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583174</v>
+        <v>583151</v>
       </c>
       <c r="R34" t="n">
-        <v>7014111</v>
+        <v>7014252</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3885,28 +3869,44 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129502234</v>
+        <v>129502192</v>
       </c>
       <c r="B35" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583081</v>
+        <v>583114</v>
       </c>
       <c r="R35" t="n">
-        <v>7014394</v>
+        <v>7014270</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129502192</v>
+        <v>129502234</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583114</v>
+        <v>583081</v>
       </c>
       <c r="R36" t="n">
-        <v>7014270</v>
+        <v>7014394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502235</v>
+        <v>129502182</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>91557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583064</v>
+        <v>583174</v>
       </c>
       <c r="R39" t="n">
-        <v>7014430</v>
+        <v>7014597</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502236</v>
+        <v>129502235</v>
       </c>
       <c r="B40" t="n">
         <v>80186</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583058</v>
+        <v>583064</v>
       </c>
       <c r="R40" t="n">
-        <v>7014379</v>
+        <v>7014430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,32 +4501,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502182</v>
+        <v>129502236</v>
       </c>
       <c r="B41" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583174</v>
+        <v>583058</v>
       </c>
       <c r="R41" t="n">
-        <v>7014597</v>
+        <v>7014379</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502215</v>
+        <v>129502226</v>
       </c>
       <c r="B43" t="n">
-        <v>91891</v>
+        <v>80186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4711,21 +4711,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583175</v>
+        <v>583156</v>
       </c>
       <c r="R43" t="n">
-        <v>7014579</v>
+        <v>7014249</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4779,8 +4779,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4797,32 +4813,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502226</v>
+        <v>129502209</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4848,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583156</v>
+        <v>583167</v>
       </c>
       <c r="R44" t="n">
-        <v>7014249</v>
+        <v>7014583</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,24 +4892,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4910,32 +4910,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502209</v>
+        <v>129502247</v>
       </c>
       <c r="B45" t="n">
-        <v>80090</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583167</v>
+        <v>583367</v>
       </c>
       <c r="R45" t="n">
-        <v>7014583</v>
+        <v>7014331</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5007,10 +5007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502205</v>
+        <v>129502251</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5018,21 +5018,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
         <v>583055</v>
       </c>
       <c r="R46" t="n">
-        <v>7014357</v>
+        <v>7014329</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502247</v>
+        <v>129502205</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5115,21 +5115,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583367</v>
+        <v>583055</v>
       </c>
       <c r="R47" t="n">
-        <v>7014331</v>
+        <v>7014357</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502251</v>
+        <v>129502215</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>91891</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583055</v>
+        <v>583175</v>
       </c>
       <c r="R48" t="n">
-        <v>7014329</v>
+        <v>7014579</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502194</v>
+        <v>129502206</v>
       </c>
       <c r="B50" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5406,21 +5406,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583050</v>
+        <v>583074</v>
       </c>
       <c r="R50" t="n">
-        <v>7014242</v>
+        <v>7014351</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,32 +5492,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502211</v>
+        <v>129502194</v>
       </c>
       <c r="B51" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583055</v>
+        <v>583050</v>
       </c>
       <c r="R51" t="n">
-        <v>7014372</v>
+        <v>7014242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502206</v>
+        <v>129502211</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>92046</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583074</v>
+        <v>583055</v>
       </c>
       <c r="R52" t="n">
-        <v>7014351</v>
+        <v>7014372</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6617,32 +6617,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502249</v>
+        <v>129502239</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>58106</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583114</v>
+        <v>583168</v>
       </c>
       <c r="R62" t="n">
-        <v>7014512</v>
+        <v>7014188</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B63" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R63" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502239</v>
+        <v>129502232</v>
       </c>
       <c r="B64" t="n">
-        <v>58106</v>
+        <v>80186</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583168</v>
+        <v>583323</v>
       </c>
       <c r="R64" t="n">
-        <v>7014188</v>
+        <v>7014267</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7605,45 +7605,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502218</v>
+        <v>129502242</v>
       </c>
       <c r="B72" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583050</v>
+        <v>583095</v>
       </c>
       <c r="R72" t="n">
-        <v>7014244</v>
+        <v>7014377</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7684,6 +7688,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7702,32 +7707,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502198</v>
+        <v>129502218</v>
       </c>
       <c r="B73" t="n">
-        <v>92311</v>
+        <v>91891</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7737,10 +7742,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583192</v>
+        <v>583050</v>
       </c>
       <c r="R73" t="n">
-        <v>7014120</v>
+        <v>7014244</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7799,49 +7804,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B74" t="n">
-        <v>98774</v>
+        <v>92311</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R74" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7882,7 +7883,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502193</v>
+        <v>129502204</v>
       </c>
       <c r="B75" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583174</v>
+        <v>583061</v>
       </c>
       <c r="R75" t="n">
-        <v>7014589</v>
+        <v>7014418</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502250</v>
+        <v>129502193</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R76" t="n">
-        <v>7014344</v>
+        <v>7014589</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129502204</v>
+        <v>129502250</v>
       </c>
       <c r="B77" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583061</v>
+        <v>583068</v>
       </c>
       <c r="R77" t="n">
-        <v>7014418</v>
+        <v>7014344</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502233</v>
+        <v>129502256</v>
       </c>
       <c r="B79" t="n">
-        <v>80186</v>
+        <v>82916</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583068</v>
+        <v>583110</v>
       </c>
       <c r="R79" t="n">
-        <v>7014398</v>
+        <v>7014519</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,11 +8360,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8488,10 +8483,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502256</v>
+        <v>129502233</v>
       </c>
       <c r="B81" t="n">
-        <v>82916</v>
+        <v>80186</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8499,21 +8494,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8523,10 +8518,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583110</v>
+        <v>583068</v>
       </c>
       <c r="R81" t="n">
-        <v>7014519</v>
+        <v>7014398</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8559,6 +8554,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129495400</v>
+        <v>129502199</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>92311</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583183</v>
+        <v>583141</v>
       </c>
       <c r="R8" t="n">
-        <v>7014604</v>
+        <v>7014282</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1461,48 +1461,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129502199</v>
+        <v>129495400</v>
       </c>
       <c r="B10" t="n">
-        <v>92311</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583141</v>
+        <v>583183</v>
       </c>
       <c r="R10" t="n">
-        <v>7014282</v>
+        <v>7014604</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1546,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2043,48 +2043,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495405</v>
+        <v>129502196</v>
       </c>
       <c r="B16" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583128</v>
+        <v>583143</v>
       </c>
       <c r="R16" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495408</v>
+        <v>129495405</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>92046</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583204</v>
+        <v>583128</v>
       </c>
       <c r="R17" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495410</v>
+        <v>129495408</v>
       </c>
       <c r="B18" t="n">
         <v>80186</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583139</v>
+        <v>583204</v>
       </c>
       <c r="R18" t="n">
-        <v>7014123</v>
+        <v>7014157</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495406</v>
+        <v>129495410</v>
       </c>
       <c r="B19" t="n">
         <v>80186</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583170</v>
+        <v>583139</v>
       </c>
       <c r="R19" t="n">
-        <v>7014239</v>
+        <v>7014123</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129502196</v>
+        <v>129495406</v>
       </c>
       <c r="B20" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583143</v>
+        <v>583170</v>
       </c>
       <c r="R20" t="n">
-        <v>7014216</v>
+        <v>7014239</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129495402</v>
+        <v>129495407</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583080</v>
+        <v>583122</v>
       </c>
       <c r="R23" t="n">
-        <v>7014300</v>
+        <v>7014418</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129495407</v>
+        <v>129502255</v>
       </c>
       <c r="B24" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583122</v>
+        <v>583197</v>
       </c>
       <c r="R24" t="n">
-        <v>7014418</v>
+        <v>7014149</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,12 +2904,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129502255</v>
+        <v>129495402</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583197</v>
+        <v>583080</v>
       </c>
       <c r="R26" t="n">
-        <v>7014149</v>
+        <v>7014300</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R28" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R29" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129502192</v>
+        <v>129502234</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583114</v>
+        <v>583081</v>
       </c>
       <c r="R35" t="n">
-        <v>7014270</v>
+        <v>7014394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129502234</v>
+        <v>129502192</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583081</v>
+        <v>583114</v>
       </c>
       <c r="R36" t="n">
-        <v>7014394</v>
+        <v>7014270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129502225</v>
+        <v>129502237</v>
       </c>
       <c r="B37" t="n">
         <v>80186</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583072</v>
+        <v>583139</v>
       </c>
       <c r="R37" t="n">
-        <v>7014226</v>
+        <v>7014115</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4176,24 +4176,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4210,7 +4194,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129502237</v>
+        <v>129502225</v>
       </c>
       <c r="B38" t="n">
         <v>80186</v>
@@ -4245,10 +4229,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583139</v>
+        <v>583072</v>
       </c>
       <c r="R38" t="n">
-        <v>7014115</v>
+        <v>7014226</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,8 +4273,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502182</v>
+        <v>129502235</v>
       </c>
       <c r="B39" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583174</v>
+        <v>583064</v>
       </c>
       <c r="R39" t="n">
-        <v>7014597</v>
+        <v>7014430</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,32 +4404,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502235</v>
+        <v>129502182</v>
       </c>
       <c r="B40" t="n">
-        <v>80186</v>
+        <v>91557</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583064</v>
+        <v>583174</v>
       </c>
       <c r="R40" t="n">
-        <v>7014430</v>
+        <v>7014597</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502226</v>
+        <v>129502209</v>
       </c>
       <c r="B43" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583156</v>
+        <v>583167</v>
       </c>
       <c r="R43" t="n">
-        <v>7014249</v>
+        <v>7014583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4779,24 +4779,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -4813,32 +4797,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502209</v>
+        <v>129502247</v>
       </c>
       <c r="B44" t="n">
-        <v>80090</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4848,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583167</v>
+        <v>583367</v>
       </c>
       <c r="R44" t="n">
-        <v>7014583</v>
+        <v>7014331</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4910,7 +4894,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502247</v>
+        <v>129502251</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -4945,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583367</v>
+        <v>583055</v>
       </c>
       <c r="R45" t="n">
-        <v>7014331</v>
+        <v>7014329</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5007,10 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502251</v>
+        <v>129502226</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5018,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5042,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R46" t="n">
-        <v>7014329</v>
+        <v>7014249</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5086,8 +5070,24 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5104,10 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502205</v>
+        <v>129502215</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>91891</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5115,21 +5115,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583055</v>
+        <v>583175</v>
       </c>
       <c r="R47" t="n">
-        <v>7014357</v>
+        <v>7014579</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502215</v>
+        <v>129502205</v>
       </c>
       <c r="B48" t="n">
-        <v>91891</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583175</v>
+        <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014579</v>
+        <v>7014357</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502206</v>
+        <v>129502194</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>91593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5406,21 +5406,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583074</v>
+        <v>583050</v>
       </c>
       <c r="R50" t="n">
-        <v>7014351</v>
+        <v>7014242</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,32 +5492,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502194</v>
+        <v>129502211</v>
       </c>
       <c r="B51" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583050</v>
+        <v>583055</v>
       </c>
       <c r="R51" t="n">
-        <v>7014242</v>
+        <v>7014372</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502211</v>
+        <v>129502206</v>
       </c>
       <c r="B52" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583055</v>
+        <v>583074</v>
       </c>
       <c r="R52" t="n">
-        <v>7014372</v>
+        <v>7014351</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,45 +6111,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502216</v>
+        <v>129502243</v>
       </c>
       <c r="B57" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583173</v>
+        <v>583046</v>
       </c>
       <c r="R57" t="n">
-        <v>7014589</v>
+        <v>7014393</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6190,6 +6194,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6208,49 +6213,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502243</v>
+        <v>129502216</v>
       </c>
       <c r="B58" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583046</v>
+        <v>583173</v>
       </c>
       <c r="R58" t="n">
-        <v>7014393</v>
+        <v>7014589</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6291,7 +6292,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6310,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502227</v>
+        <v>129502184</v>
       </c>
       <c r="B59" t="n">
-        <v>80186</v>
+        <v>91557</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583045</v>
+        <v>583134</v>
       </c>
       <c r="R59" t="n">
-        <v>7014432</v>
+        <v>7014134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6389,24 +6389,8 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -6520,32 +6504,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502184</v>
+        <v>129502227</v>
       </c>
       <c r="B61" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6539,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583134</v>
+        <v>583045</v>
       </c>
       <c r="R61" t="n">
-        <v>7014134</v>
+        <v>7014432</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6599,8 +6583,24 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6617,32 +6617,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502239</v>
+        <v>129502232</v>
       </c>
       <c r="B62" t="n">
-        <v>58106</v>
+        <v>80186</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583168</v>
+        <v>583323</v>
       </c>
       <c r="R62" t="n">
-        <v>7014188</v>
+        <v>7014267</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502232</v>
+        <v>129502239</v>
       </c>
       <c r="B64" t="n">
-        <v>80186</v>
+        <v>58106</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583323</v>
+        <v>583168</v>
       </c>
       <c r="R64" t="n">
-        <v>7014267</v>
+        <v>7014188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B65" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R65" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,11 +6979,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7010,10 +7005,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7021,21 +7016,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7045,10 +7040,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R66" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7081,6 +7076,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7107,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129502248</v>
+        <v>129502180</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>83050</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7118,21 +7118,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583117</v>
+        <v>583051</v>
       </c>
       <c r="R67" t="n">
-        <v>7014262</v>
+        <v>7014327</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7204,10 +7204,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502180</v>
+        <v>129502248</v>
       </c>
       <c r="B68" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7215,21 +7215,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583051</v>
+        <v>583117</v>
       </c>
       <c r="R68" t="n">
-        <v>7014327</v>
+        <v>7014262</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7406,45 +7406,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502245</v>
+        <v>129502240</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583158</v>
+        <v>583138</v>
       </c>
       <c r="R70" t="n">
-        <v>7014222</v>
+        <v>7014124</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7485,6 +7489,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7503,49 +7508,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129502240</v>
+        <v>129502245</v>
       </c>
       <c r="B71" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583138</v>
+        <v>583158</v>
       </c>
       <c r="R71" t="n">
-        <v>7014124</v>
+        <v>7014222</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7586,7 +7587,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7605,49 +7605,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502242</v>
+        <v>129502218</v>
       </c>
       <c r="B72" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583095</v>
+        <v>583050</v>
       </c>
       <c r="R72" t="n">
-        <v>7014377</v>
+        <v>7014244</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7688,7 +7684,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7707,45 +7702,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502218</v>
+        <v>129502242</v>
       </c>
       <c r="B73" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583050</v>
+        <v>583095</v>
       </c>
       <c r="R73" t="n">
-        <v>7014244</v>
+        <v>7014377</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7786,6 +7785,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502204</v>
+        <v>129502250</v>
       </c>
       <c r="B75" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583061</v>
+        <v>583068</v>
       </c>
       <c r="R75" t="n">
-        <v>7014418</v>
+        <v>7014344</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129502250</v>
+        <v>129502204</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583068</v>
+        <v>583061</v>
       </c>
       <c r="R77" t="n">
-        <v>7014344</v>
+        <v>7014418</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502256</v>
+        <v>129502214</v>
       </c>
       <c r="B79" t="n">
-        <v>82916</v>
+        <v>91891</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583110</v>
+        <v>583052</v>
       </c>
       <c r="R79" t="n">
-        <v>7014519</v>
+        <v>7014374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8386,10 +8386,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502214</v>
+        <v>129502256</v>
       </c>
       <c r="B80" t="n">
-        <v>91891</v>
+        <v>82916</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8397,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583052</v>
+        <v>583110</v>
       </c>
       <c r="R80" t="n">
-        <v>7014374</v>
+        <v>7014519</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8585,32 +8585,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129502241</v>
+        <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8620,10 +8620,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583076</v>
+        <v>583137</v>
       </c>
       <c r="R82" t="n">
-        <v>7014398</v>
+        <v>7014134</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8664,7 +8664,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8683,32 +8682,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129502219</v>
+        <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8718,10 +8717,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583137</v>
+        <v>583076</v>
       </c>
       <c r="R83" t="n">
-        <v>7014134</v>
+        <v>7014398</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8762,6 +8761,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -1364,48 +1364,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129502212</v>
+        <v>129495400</v>
       </c>
       <c r="B9" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583184</v>
+        <v>583183</v>
       </c>
       <c r="R9" t="n">
-        <v>7014173</v>
+        <v>7014604</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,60 +1449,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129495400</v>
+        <v>129502212</v>
       </c>
       <c r="B10" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583183</v>
+        <v>583184</v>
       </c>
       <c r="R10" t="n">
-        <v>7014604</v>
+        <v>7014173</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1546,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129502196</v>
+        <v>129495410</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2054,37 +2054,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583143</v>
+        <v>583139</v>
       </c>
       <c r="R16" t="n">
-        <v>7014216</v>
+        <v>7014123</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495405</v>
+        <v>129495408</v>
       </c>
       <c r="B17" t="n">
-        <v>92046</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583128</v>
+        <v>583204</v>
       </c>
       <c r="R17" t="n">
-        <v>7014123</v>
+        <v>7014157</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495408</v>
+        <v>129495406</v>
       </c>
       <c r="B18" t="n">
         <v>80186</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583204</v>
+        <v>583170</v>
       </c>
       <c r="R18" t="n">
-        <v>7014157</v>
+        <v>7014239</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495410</v>
+        <v>129502196</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,37 +2345,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583139</v>
+        <v>583143</v>
       </c>
       <c r="R19" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2419,44 +2419,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495406</v>
+        <v>129495405</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>92046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583170</v>
+        <v>583128</v>
       </c>
       <c r="R20" t="n">
-        <v>7014239</v>
+        <v>7014123</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129495407</v>
+        <v>129502255</v>
       </c>
       <c r="B23" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583122</v>
+        <v>583197</v>
       </c>
       <c r="R23" t="n">
-        <v>7014418</v>
+        <v>7014149</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,19 +2807,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129502255</v>
+        <v>129502252</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583197</v>
+        <v>583105</v>
       </c>
       <c r="R24" t="n">
-        <v>7014149</v>
+        <v>7014309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129502252</v>
+        <v>129495407</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583105</v>
+        <v>583122</v>
       </c>
       <c r="R25" t="n">
-        <v>7014309</v>
+        <v>7014418</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R28" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R29" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3498,48 +3498,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129502213</v>
+        <v>129495411</v>
       </c>
       <c r="B31" t="n">
-        <v>92046</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583198</v>
+        <v>583068</v>
       </c>
       <c r="R31" t="n">
-        <v>7014144</v>
+        <v>7014294</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,19 +3577,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3693,48 +3692,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129495411</v>
+        <v>129502213</v>
       </c>
       <c r="B33" t="n">
-        <v>80186</v>
+        <v>92046</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583068</v>
+        <v>583198</v>
       </c>
       <c r="R33" t="n">
-        <v>7014294</v>
+        <v>7014144</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3772,18 +3771,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129502234</v>
+        <v>129502192</v>
       </c>
       <c r="B35" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583081</v>
+        <v>583114</v>
       </c>
       <c r="R35" t="n">
-        <v>7014394</v>
+        <v>7014270</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129502192</v>
+        <v>129502234</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583114</v>
+        <v>583081</v>
       </c>
       <c r="R36" t="n">
-        <v>7014270</v>
+        <v>7014394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502235</v>
+        <v>129502182</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>91557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583064</v>
+        <v>583174</v>
       </c>
       <c r="R39" t="n">
-        <v>7014430</v>
+        <v>7014597</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,32 +4404,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502182</v>
+        <v>129502236</v>
       </c>
       <c r="B40" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583174</v>
+        <v>583058</v>
       </c>
       <c r="R40" t="n">
-        <v>7014597</v>
+        <v>7014379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502236</v>
+        <v>129502235</v>
       </c>
       <c r="B41" t="n">
         <v>80186</v>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583058</v>
+        <v>583064</v>
       </c>
       <c r="R41" t="n">
-        <v>7014379</v>
+        <v>7014430</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502209</v>
+        <v>129502215</v>
       </c>
       <c r="B43" t="n">
-        <v>80090</v>
+        <v>91891</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583167</v>
+        <v>583175</v>
       </c>
       <c r="R43" t="n">
-        <v>7014583</v>
+        <v>7014579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4991,32 +4991,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502226</v>
+        <v>129502209</v>
       </c>
       <c r="B46" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583156</v>
+        <v>583167</v>
       </c>
       <c r="R46" t="n">
-        <v>7014249</v>
+        <v>7014583</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5070,24 +5070,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5104,10 +5088,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502215</v>
+        <v>129502226</v>
       </c>
       <c r="B47" t="n">
-        <v>91891</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5115,21 +5099,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5139,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583175</v>
+        <v>583156</v>
       </c>
       <c r="R47" t="n">
-        <v>7014579</v>
+        <v>7014249</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5183,8 +5167,24 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6111,49 +6111,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502243</v>
+        <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583046</v>
+        <v>583173</v>
       </c>
       <c r="R57" t="n">
-        <v>7014393</v>
+        <v>7014589</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,7 +6190,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6213,45 +6208,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502216</v>
+        <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583173</v>
+        <v>583046</v>
       </c>
       <c r="R58" t="n">
-        <v>7014589</v>
+        <v>7014393</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6292,6 +6291,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B62" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R62" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502249</v>
+        <v>129502232</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583114</v>
+        <v>583323</v>
       </c>
       <c r="R63" t="n">
-        <v>7014512</v>
+        <v>7014267</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129502180</v>
+        <v>129502248</v>
       </c>
       <c r="B67" t="n">
-        <v>83050</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7118,21 +7118,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583051</v>
+        <v>583117</v>
       </c>
       <c r="R67" t="n">
-        <v>7014327</v>
+        <v>7014262</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7204,10 +7204,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502248</v>
+        <v>129502203</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7215,34 +7215,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583117</v>
+        <v>583138</v>
       </c>
       <c r="R68" t="n">
-        <v>7014262</v>
+        <v>7014232</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7301,10 +7309,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129502203</v>
+        <v>129502180</v>
       </c>
       <c r="B69" t="n">
-        <v>57896</v>
+        <v>83050</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7312,42 +7320,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583138</v>
+        <v>583051</v>
       </c>
       <c r="R69" t="n">
-        <v>7014232</v>
+        <v>7014327</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7406,49 +7406,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502240</v>
+        <v>129502245</v>
       </c>
       <c r="B70" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583138</v>
+        <v>583158</v>
       </c>
       <c r="R70" t="n">
-        <v>7014124</v>
+        <v>7014222</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7489,7 +7485,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7508,45 +7503,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129502245</v>
+        <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583158</v>
+        <v>583138</v>
       </c>
       <c r="R71" t="n">
-        <v>7014222</v>
+        <v>7014124</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7587,6 +7586,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7605,32 +7605,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502218</v>
+        <v>129502198</v>
       </c>
       <c r="B72" t="n">
-        <v>91891</v>
+        <v>92311</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583050</v>
+        <v>583192</v>
       </c>
       <c r="R72" t="n">
-        <v>7014244</v>
+        <v>7014120</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7702,49 +7702,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502242</v>
+        <v>129502218</v>
       </c>
       <c r="B73" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583095</v>
+        <v>583050</v>
       </c>
       <c r="R73" t="n">
-        <v>7014377</v>
+        <v>7014244</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7785,7 +7781,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7804,45 +7799,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>92311</v>
+        <v>98774</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R74" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,6 +7882,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502250</v>
+        <v>129502193</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R75" t="n">
-        <v>7014344</v>
+        <v>7014589</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502193</v>
+        <v>129502204</v>
       </c>
       <c r="B76" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583174</v>
+        <v>583061</v>
       </c>
       <c r="R76" t="n">
-        <v>7014589</v>
+        <v>7014418</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129502204</v>
+        <v>129502250</v>
       </c>
       <c r="B77" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583061</v>
+        <v>583068</v>
       </c>
       <c r="R77" t="n">
-        <v>7014418</v>
+        <v>7014344</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502214</v>
+        <v>129502233</v>
       </c>
       <c r="B79" t="n">
-        <v>91891</v>
+        <v>80186</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583052</v>
+        <v>583068</v>
       </c>
       <c r="R79" t="n">
-        <v>7014374</v>
+        <v>7014398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,6 +8360,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8386,10 +8391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502256</v>
+        <v>129502214</v>
       </c>
       <c r="B80" t="n">
-        <v>82916</v>
+        <v>91891</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8402,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8426,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583110</v>
+        <v>583052</v>
       </c>
       <c r="R80" t="n">
-        <v>7014519</v>
+        <v>7014374</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8483,10 +8488,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502233</v>
+        <v>129502256</v>
       </c>
       <c r="B81" t="n">
-        <v>80186</v>
+        <v>82916</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8494,21 +8499,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8518,10 +8523,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583068</v>
+        <v>583110</v>
       </c>
       <c r="R81" t="n">
-        <v>7014398</v>
+        <v>7014519</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8554,11 +8559,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129502197</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129502195</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -971,45 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502188</v>
+        <v>129502244</v>
       </c>
       <c r="B5" t="n">
-        <v>91557</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583139</v>
+        <v>583177</v>
       </c>
       <c r="R5" t="n">
-        <v>7014270</v>
+        <v>7014165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1054,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502190</v>
+        <v>129502188</v>
       </c>
       <c r="B6" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583136</v>
+        <v>583139</v>
       </c>
       <c r="R6" t="n">
-        <v>7014210</v>
+        <v>7014270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,49 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502244</v>
+        <v>129502190</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>91561</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583177</v>
+        <v>583136</v>
       </c>
       <c r="R7" t="n">
-        <v>7014165</v>
+        <v>7014210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129502199</v>
+        <v>129495400</v>
       </c>
       <c r="B8" t="n">
-        <v>92311</v>
+        <v>91597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583141</v>
+        <v>583183</v>
       </c>
       <c r="R8" t="n">
-        <v>7014282</v>
+        <v>7014604</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,60 +1352,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129495400</v>
+        <v>129502199</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>92315</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583183</v>
+        <v>583141</v>
       </c>
       <c r="R9" t="n">
-        <v>7014604</v>
+        <v>7014282</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1449,12 +1449,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1464,7 +1464,7 @@
         <v>129502212</v>
       </c>
       <c r="B10" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129502189</v>
       </c>
       <c r="B12" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129502186</v>
       </c>
       <c r="B13" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>129502200</v>
       </c>
       <c r="B14" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129502201</v>
       </c>
       <c r="B15" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495410</v>
+        <v>129495405</v>
       </c>
       <c r="B16" t="n">
-        <v>80186</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583139</v>
+        <v>583128</v>
       </c>
       <c r="R16" t="n">
         <v>7014123</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495408</v>
+        <v>129495410</v>
       </c>
       <c r="B17" t="n">
         <v>80186</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583204</v>
+        <v>583139</v>
       </c>
       <c r="R17" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495406</v>
+        <v>129495408</v>
       </c>
       <c r="B18" t="n">
         <v>80186</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583170</v>
+        <v>583204</v>
       </c>
       <c r="R18" t="n">
-        <v>7014239</v>
+        <v>7014157</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129502196</v>
+        <v>129495406</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,37 +2345,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583143</v>
+        <v>583170</v>
       </c>
       <c r="R19" t="n">
-        <v>7014216</v>
+        <v>7014239</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2419,60 +2419,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495405</v>
+        <v>129502196</v>
       </c>
       <c r="B20" t="n">
-        <v>92046</v>
+        <v>91597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583128</v>
+        <v>583143</v>
       </c>
       <c r="R20" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>129502220</v>
       </c>
       <c r="B21" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129502202</v>
       </c>
       <c r="B22" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129502255</v>
+        <v>129502252</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583197</v>
+        <v>583105</v>
       </c>
       <c r="R23" t="n">
-        <v>7014149</v>
+        <v>7014309</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129502252</v>
+        <v>129502255</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583105</v>
+        <v>583197</v>
       </c>
       <c r="R24" t="n">
-        <v>7014309</v>
+        <v>7014149</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129495407</v>
+        <v>129495402</v>
       </c>
       <c r="B25" t="n">
-        <v>80186</v>
+        <v>91597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,21 +2927,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583122</v>
+        <v>583080</v>
       </c>
       <c r="R25" t="n">
-        <v>7014418</v>
+        <v>7014300</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129495402</v>
+        <v>129495407</v>
       </c>
       <c r="B26" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583080</v>
+        <v>583122</v>
       </c>
       <c r="R26" t="n">
-        <v>7014300</v>
+        <v>7014418</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3404,7 +3404,7 @@
         <v>129495401</v>
       </c>
       <c r="B30" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3692,32 +3692,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129502213</v>
+        <v>129502224</v>
       </c>
       <c r="B33" t="n">
-        <v>92046</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583198</v>
+        <v>583151</v>
       </c>
       <c r="R33" t="n">
-        <v>7014144</v>
+        <v>7014252</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3774,21 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -3790,32 +3805,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502224</v>
+        <v>129502213</v>
       </c>
       <c r="B34" t="n">
-        <v>80186</v>
+        <v>92050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,10 +3840,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583151</v>
+        <v>583198</v>
       </c>
       <c r="R34" t="n">
-        <v>7014252</v>
+        <v>7014144</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3872,21 +3887,6 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -3906,7 +3906,7 @@
         <v>129502192</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502182</v>
+        <v>129502236</v>
       </c>
       <c r="B39" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583174</v>
+        <v>583058</v>
       </c>
       <c r="R39" t="n">
-        <v>7014597</v>
+        <v>7014379</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502236</v>
+        <v>129502235</v>
       </c>
       <c r="B40" t="n">
         <v>80186</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583058</v>
+        <v>583064</v>
       </c>
       <c r="R40" t="n">
-        <v>7014379</v>
+        <v>7014430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,10 +4501,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502235</v>
+        <v>129502221</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583064</v>
+        <v>583411</v>
       </c>
       <c r="R41" t="n">
-        <v>7014430</v>
+        <v>7014380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,6 +4572,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4598,32 +4603,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502221</v>
+        <v>129502182</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>91561</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4633,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583411</v>
+        <v>583174</v>
       </c>
       <c r="R42" t="n">
-        <v>7014380</v>
+        <v>7014597</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,11 +4674,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4703,7 +4703,7 @@
         <v>129502215</v>
       </c>
       <c r="B43" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,32 +4797,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502247</v>
+        <v>129502209</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>80090</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583367</v>
+        <v>583167</v>
       </c>
       <c r="R44" t="n">
-        <v>7014331</v>
+        <v>7014583</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502251</v>
+        <v>129502226</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,21 +4905,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R45" t="n">
-        <v>7014329</v>
+        <v>7014249</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4973,8 +4973,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -4991,32 +5007,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502209</v>
+        <v>129502247</v>
       </c>
       <c r="B46" t="n">
-        <v>80090</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583167</v>
+        <v>583367</v>
       </c>
       <c r="R46" t="n">
-        <v>7014583</v>
+        <v>7014331</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,10 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502226</v>
+        <v>129502251</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5099,21 +5115,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5123,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R47" t="n">
-        <v>7014249</v>
+        <v>7014329</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,24 +5183,8 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502230</v>
+        <v>129502206</v>
       </c>
       <c r="B49" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583330</v>
+        <v>583074</v>
       </c>
       <c r="R49" t="n">
-        <v>7014339</v>
+        <v>7014351</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502194</v>
+        <v>129502230</v>
       </c>
       <c r="B50" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5406,21 +5406,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583050</v>
+        <v>583330</v>
       </c>
       <c r="R50" t="n">
-        <v>7014242</v>
+        <v>7014339</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,32 +5492,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502211</v>
+        <v>129502194</v>
       </c>
       <c r="B51" t="n">
-        <v>92046</v>
+        <v>91597</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583055</v>
+        <v>583050</v>
       </c>
       <c r="R51" t="n">
-        <v>7014372</v>
+        <v>7014242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502206</v>
+        <v>129502211</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>92050</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583074</v>
+        <v>583055</v>
       </c>
       <c r="R52" t="n">
-        <v>7014351</v>
+        <v>7014372</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6114,7 +6114,7 @@
         <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6310,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502184</v>
+        <v>129502231</v>
       </c>
       <c r="B59" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583134</v>
+        <v>583345</v>
       </c>
       <c r="R59" t="n">
-        <v>7014134</v>
+        <v>7014389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502231</v>
+        <v>129502227</v>
       </c>
       <c r="B60" t="n">
         <v>80186</v>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583345</v>
+        <v>583045</v>
       </c>
       <c r="R60" t="n">
-        <v>7014389</v>
+        <v>7014432</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,8 +6486,24 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6504,32 +6520,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502227</v>
+        <v>129502184</v>
       </c>
       <c r="B61" t="n">
-        <v>80186</v>
+        <v>91561</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6539,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583045</v>
+        <v>583134</v>
       </c>
       <c r="R61" t="n">
-        <v>7014432</v>
+        <v>7014134</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6583,24 +6599,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502249</v>
+        <v>129502232</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583114</v>
+        <v>583323</v>
       </c>
       <c r="R62" t="n">
-        <v>7014512</v>
+        <v>7014267</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B63" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R63" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R65" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,6 +6979,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7005,10 +7010,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B66" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,21 +7021,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7040,10 +7045,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R66" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7076,11 +7081,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7107,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129502248</v>
+        <v>129502203</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7118,34 +7118,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583117</v>
+        <v>583138</v>
       </c>
       <c r="R67" t="n">
-        <v>7014262</v>
+        <v>7014232</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7204,10 +7212,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502203</v>
+        <v>129502248</v>
       </c>
       <c r="B68" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7215,42 +7223,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583138</v>
+        <v>583117</v>
       </c>
       <c r="R68" t="n">
-        <v>7014232</v>
+        <v>7014262</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7506,7 +7506,7 @@
         <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7605,32 +7605,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502198</v>
+        <v>129502218</v>
       </c>
       <c r="B72" t="n">
-        <v>92311</v>
+        <v>91895</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583192</v>
+        <v>583050</v>
       </c>
       <c r="R72" t="n">
-        <v>7014120</v>
+        <v>7014244</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7702,45 +7702,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502218</v>
+        <v>129502242</v>
       </c>
       <c r="B73" t="n">
-        <v>91891</v>
+        <v>98778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583050</v>
+        <v>583095</v>
       </c>
       <c r="R73" t="n">
-        <v>7014244</v>
+        <v>7014377</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7781,6 +7785,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7799,49 +7804,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B74" t="n">
-        <v>98774</v>
+        <v>92315</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R74" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7882,7 +7883,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502193</v>
+        <v>129502250</v>
       </c>
       <c r="B75" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R75" t="n">
-        <v>7014589</v>
+        <v>7014344</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502204</v>
+        <v>129502193</v>
       </c>
       <c r="B76" t="n">
-        <v>57733</v>
+        <v>91597</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583061</v>
+        <v>583174</v>
       </c>
       <c r="R76" t="n">
-        <v>7014418</v>
+        <v>7014589</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129502250</v>
+        <v>129502204</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583068</v>
+        <v>583061</v>
       </c>
       <c r="R77" t="n">
-        <v>7014344</v>
+        <v>7014418</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8195,7 +8195,7 @@
         <v>129502217</v>
       </c>
       <c r="B78" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502233</v>
+        <v>129502214</v>
       </c>
       <c r="B79" t="n">
-        <v>80186</v>
+        <v>91895</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583068</v>
+        <v>583052</v>
       </c>
       <c r="R79" t="n">
-        <v>7014398</v>
+        <v>7014374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,11 +8360,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8391,10 +8386,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502214</v>
+        <v>129502233</v>
       </c>
       <c r="B80" t="n">
-        <v>91891</v>
+        <v>80186</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8402,21 +8397,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8426,10 +8421,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583052</v>
+        <v>583068</v>
       </c>
       <c r="R80" t="n">
-        <v>7014374</v>
+        <v>7014398</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8462,6 +8457,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8588,7 +8588,7 @@
         <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129502197</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129502195</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -971,49 +971,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502244</v>
+        <v>129502188</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>91563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583177</v>
+        <v>583139</v>
       </c>
       <c r="R5" t="n">
-        <v>7014165</v>
+        <v>7014270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,7 +1050,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502188</v>
+        <v>129502190</v>
       </c>
       <c r="B6" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583139</v>
+        <v>583136</v>
       </c>
       <c r="R6" t="n">
-        <v>7014270</v>
+        <v>7014210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1165,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502190</v>
+        <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>91561</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583136</v>
+        <v>583177</v>
       </c>
       <c r="R7" t="n">
-        <v>7014210</v>
+        <v>7014165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129495400</v>
+        <v>129502212</v>
       </c>
       <c r="B8" t="n">
-        <v>91597</v>
+        <v>92052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583183</v>
+        <v>583184</v>
       </c>
       <c r="R8" t="n">
-        <v>7014604</v>
+        <v>7014173</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1367,7 +1367,7 @@
         <v>129502199</v>
       </c>
       <c r="B9" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,48 +1461,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129502212</v>
+        <v>129495400</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583184</v>
+        <v>583183</v>
       </c>
       <c r="R10" t="n">
-        <v>7014173</v>
+        <v>7014604</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1546,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
         <v>129502189</v>
       </c>
       <c r="B12" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129502186</v>
       </c>
       <c r="B13" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>129502200</v>
       </c>
       <c r="B14" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129502201</v>
       </c>
       <c r="B15" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129495405</v>
       </c>
       <c r="B16" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495410</v>
+        <v>129502196</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,37 +2151,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583139</v>
+        <v>583143</v>
       </c>
       <c r="R17" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2225,19 +2225,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495408</v>
+        <v>129495410</v>
       </c>
       <c r="B18" t="n">
         <v>80186</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583204</v>
+        <v>583139</v>
       </c>
       <c r="R18" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495406</v>
+        <v>129495408</v>
       </c>
       <c r="B19" t="n">
         <v>80186</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583170</v>
+        <v>583204</v>
       </c>
       <c r="R19" t="n">
-        <v>7014239</v>
+        <v>7014157</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129502196</v>
+        <v>129495406</v>
       </c>
       <c r="B20" t="n">
-        <v>91597</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583143</v>
+        <v>583170</v>
       </c>
       <c r="R20" t="n">
-        <v>7014216</v>
+        <v>7014239</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>129502220</v>
       </c>
       <c r="B21" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>129502202</v>
       </c>
       <c r="B22" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129502252</v>
+        <v>129495407</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583105</v>
+        <v>583122</v>
       </c>
       <c r="R23" t="n">
-        <v>7014309</v>
+        <v>7014418</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129502255</v>
+        <v>129495402</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583197</v>
+        <v>583080</v>
       </c>
       <c r="R24" t="n">
-        <v>7014149</v>
+        <v>7014300</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,22 +2904,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129495402</v>
+        <v>129502255</v>
       </c>
       <c r="B25" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583080</v>
+        <v>583197</v>
       </c>
       <c r="R25" t="n">
-        <v>7014300</v>
+        <v>7014149</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129495407</v>
+        <v>129502252</v>
       </c>
       <c r="B26" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583122</v>
+        <v>583105</v>
       </c>
       <c r="R26" t="n">
-        <v>7014418</v>
+        <v>7014309</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R28" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R29" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3404,7 +3404,7 @@
         <v>129495401</v>
       </c>
       <c r="B30" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3498,48 +3498,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129495411</v>
+        <v>129502213</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>92052</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583068</v>
+        <v>583198</v>
       </c>
       <c r="R31" t="n">
-        <v>7014294</v>
+        <v>7014144</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,25 +3577,26 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129495409</v>
+        <v>129502224</v>
       </c>
       <c r="B32" t="n">
         <v>80186</v>
@@ -3626,17 +3627,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583174</v>
+        <v>583151</v>
       </c>
       <c r="R32" t="n">
-        <v>7014111</v>
+        <v>7014252</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3674,25 +3675,41 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129502224</v>
+        <v>129495411</v>
       </c>
       <c r="B33" t="n">
         <v>80186</v>
@@ -3723,17 +3740,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583151</v>
+        <v>583068</v>
       </c>
       <c r="R33" t="n">
-        <v>7014252</v>
+        <v>7014294</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3771,82 +3788,66 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129502213</v>
+        <v>129495409</v>
       </c>
       <c r="B34" t="n">
-        <v>92050</v>
+        <v>80186</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583198</v>
+        <v>583174</v>
       </c>
       <c r="R34" t="n">
-        <v>7014144</v>
+        <v>7014111</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3884,19 +3885,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
         <v>129502192</v>
       </c>
       <c r="B35" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502236</v>
+        <v>129502182</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>91563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583058</v>
+        <v>583174</v>
       </c>
       <c r="R39" t="n">
-        <v>7014379</v>
+        <v>7014597</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502235</v>
+        <v>129502236</v>
       </c>
       <c r="B40" t="n">
         <v>80186</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583064</v>
+        <v>583058</v>
       </c>
       <c r="R40" t="n">
-        <v>7014430</v>
+        <v>7014379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,10 +4501,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502221</v>
+        <v>129502235</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583411</v>
+        <v>583064</v>
       </c>
       <c r="R41" t="n">
-        <v>7014380</v>
+        <v>7014430</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,11 +4572,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4603,32 +4598,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129502182</v>
+        <v>129502221</v>
       </c>
       <c r="B42" t="n">
-        <v>91561</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4638,10 +4633,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583174</v>
+        <v>583411</v>
       </c>
       <c r="R42" t="n">
-        <v>7014597</v>
+        <v>7014380</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4674,6 +4669,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4703,7 +4703,7 @@
         <v>129502215</v>
       </c>
       <c r="B43" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,32 +4797,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502209</v>
+        <v>129502247</v>
       </c>
       <c r="B44" t="n">
-        <v>80090</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583167</v>
+        <v>583367</v>
       </c>
       <c r="R44" t="n">
-        <v>7014583</v>
+        <v>7014331</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502226</v>
+        <v>129502251</v>
       </c>
       <c r="B45" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,21 +4905,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R45" t="n">
-        <v>7014249</v>
+        <v>7014329</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4973,24 +4973,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5007,10 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502247</v>
+        <v>129502205</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5018,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5042,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583367</v>
+        <v>583055</v>
       </c>
       <c r="R46" t="n">
-        <v>7014331</v>
+        <v>7014357</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5104,32 +5088,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502251</v>
+        <v>129502209</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>80090</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5139,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583055</v>
+        <v>583167</v>
       </c>
       <c r="R47" t="n">
-        <v>7014329</v>
+        <v>7014583</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,10 +5185,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502205</v>
+        <v>129502226</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>80186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5196,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5236,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R48" t="n">
-        <v>7014357</v>
+        <v>7014249</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5280,8 +5264,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502206</v>
+        <v>129502194</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583074</v>
+        <v>583050</v>
       </c>
       <c r="R49" t="n">
-        <v>7014351</v>
+        <v>7014242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502230</v>
+        <v>129502211</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>92052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583330</v>
+        <v>583055</v>
       </c>
       <c r="R50" t="n">
-        <v>7014339</v>
+        <v>7014372</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502194</v>
+        <v>129502230</v>
       </c>
       <c r="B51" t="n">
-        <v>91597</v>
+        <v>80186</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583050</v>
+        <v>583330</v>
       </c>
       <c r="R51" t="n">
-        <v>7014242</v>
+        <v>7014339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502211</v>
+        <v>129502206</v>
       </c>
       <c r="B52" t="n">
-        <v>92050</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583055</v>
+        <v>583074</v>
       </c>
       <c r="R52" t="n">
-        <v>7014372</v>
+        <v>7014351</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6114,7 +6114,7 @@
         <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6310,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502231</v>
+        <v>129502184</v>
       </c>
       <c r="B59" t="n">
-        <v>80186</v>
+        <v>91563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583345</v>
+        <v>583134</v>
       </c>
       <c r="R59" t="n">
-        <v>7014389</v>
+        <v>7014134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502227</v>
+        <v>129502231</v>
       </c>
       <c r="B60" t="n">
         <v>80186</v>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583045</v>
+        <v>583345</v>
       </c>
       <c r="R60" t="n">
-        <v>7014432</v>
+        <v>7014389</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,24 +6486,8 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6520,32 +6504,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502184</v>
+        <v>129502227</v>
       </c>
       <c r="B61" t="n">
-        <v>91561</v>
+        <v>80186</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6539,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583134</v>
+        <v>583045</v>
       </c>
       <c r="R61" t="n">
-        <v>7014134</v>
+        <v>7014432</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6599,8 +6583,24 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502232</v>
+        <v>129502249</v>
       </c>
       <c r="B62" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583323</v>
+        <v>583114</v>
       </c>
       <c r="R62" t="n">
-        <v>7014267</v>
+        <v>7014512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502249</v>
+        <v>129502232</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583114</v>
+        <v>583323</v>
       </c>
       <c r="R63" t="n">
-        <v>7014512</v>
+        <v>7014267</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B65" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R65" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,11 +6979,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7010,10 +7005,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7021,21 +7016,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7045,10 +7040,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R66" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7081,6 +7076,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7107,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129502203</v>
+        <v>129502248</v>
       </c>
       <c r="B67" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7118,42 +7118,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583138</v>
+        <v>583117</v>
       </c>
       <c r="R67" t="n">
-        <v>7014232</v>
+        <v>7014262</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7212,10 +7204,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502248</v>
+        <v>129502180</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7223,21 +7215,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7247,10 +7239,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583117</v>
+        <v>583051</v>
       </c>
       <c r="R68" t="n">
-        <v>7014262</v>
+        <v>7014327</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7309,10 +7301,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129502180</v>
+        <v>129502203</v>
       </c>
       <c r="B69" t="n">
-        <v>83050</v>
+        <v>57896</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7320,34 +7312,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583051</v>
+        <v>583138</v>
       </c>
       <c r="R69" t="n">
-        <v>7014327</v>
+        <v>7014232</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7506,7 +7506,7 @@
         <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>129502218</v>
       </c>
       <c r="B72" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7702,49 +7702,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502242</v>
+        <v>129502198</v>
       </c>
       <c r="B73" t="n">
-        <v>98778</v>
+        <v>92317</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583095</v>
+        <v>583192</v>
       </c>
       <c r="R73" t="n">
-        <v>7014377</v>
+        <v>7014120</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7785,7 +7781,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7804,45 +7799,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B74" t="n">
-        <v>92315</v>
+        <v>98780</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R74" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7883,6 +7882,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502250</v>
+        <v>129502193</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R75" t="n">
-        <v>7014344</v>
+        <v>7014589</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502193</v>
+        <v>129502250</v>
       </c>
       <c r="B76" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R76" t="n">
-        <v>7014589</v>
+        <v>7014344</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8195,7 +8195,7 @@
         <v>129502217</v>
       </c>
       <c r="B78" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>129502214</v>
       </c>
       <c r="B79" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8386,10 +8386,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502233</v>
+        <v>129502256</v>
       </c>
       <c r="B80" t="n">
-        <v>80186</v>
+        <v>82918</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8397,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8421,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583068</v>
+        <v>583110</v>
       </c>
       <c r="R80" t="n">
-        <v>7014398</v>
+        <v>7014519</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8457,11 +8457,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8488,10 +8483,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502256</v>
+        <v>129502233</v>
       </c>
       <c r="B81" t="n">
-        <v>82916</v>
+        <v>80186</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8499,21 +8494,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8523,10 +8518,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583110</v>
+        <v>583068</v>
       </c>
       <c r="R81" t="n">
-        <v>7014519</v>
+        <v>7014398</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8559,6 +8554,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8588,7 +8588,7 @@
         <v>129502219</v>
       </c>
       <c r="B82" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502188</v>
+        <v>129502190</v>
       </c>
       <c r="B5" t="n">
         <v>91563</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583139</v>
+        <v>583136</v>
       </c>
       <c r="R5" t="n">
-        <v>7014270</v>
+        <v>7014210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,45 +1068,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502190</v>
+        <v>129502244</v>
       </c>
       <c r="B6" t="n">
-        <v>91563</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583136</v>
+        <v>583177</v>
       </c>
       <c r="R6" t="n">
-        <v>7014210</v>
+        <v>7014165</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1147,6 +1151,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1165,49 +1170,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502244</v>
+        <v>129502188</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>91563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583177</v>
+        <v>583139</v>
       </c>
       <c r="R7" t="n">
-        <v>7014165</v>
+        <v>7014270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,7 +1249,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129502196</v>
+        <v>129495410</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,37 +2151,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583143</v>
+        <v>583139</v>
       </c>
       <c r="R17" t="n">
-        <v>7014216</v>
+        <v>7014123</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2225,19 +2225,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495410</v>
+        <v>129495408</v>
       </c>
       <c r="B18" t="n">
         <v>80186</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583139</v>
+        <v>583204</v>
       </c>
       <c r="R18" t="n">
-        <v>7014123</v>
+        <v>7014157</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495408</v>
+        <v>129495406</v>
       </c>
       <c r="B19" t="n">
         <v>80186</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583204</v>
+        <v>583170</v>
       </c>
       <c r="R19" t="n">
-        <v>7014157</v>
+        <v>7014239</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495406</v>
+        <v>129502196</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583170</v>
+        <v>583143</v>
       </c>
       <c r="R20" t="n">
-        <v>7014239</v>
+        <v>7014216</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129495407</v>
+        <v>129502255</v>
       </c>
       <c r="B23" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583122</v>
+        <v>583197</v>
       </c>
       <c r="R23" t="n">
-        <v>7014418</v>
+        <v>7014149</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129495402</v>
+        <v>129502252</v>
       </c>
       <c r="B24" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583080</v>
+        <v>583105</v>
       </c>
       <c r="R24" t="n">
-        <v>7014300</v>
+        <v>7014309</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,22 +2904,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129502255</v>
+        <v>129495402</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583197</v>
+        <v>583080</v>
       </c>
       <c r="R25" t="n">
-        <v>7014149</v>
+        <v>7014300</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129502252</v>
+        <v>129495407</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583105</v>
+        <v>583122</v>
       </c>
       <c r="R26" t="n">
-        <v>7014309</v>
+        <v>7014418</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -6111,45 +6111,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502216</v>
+        <v>129502243</v>
       </c>
       <c r="B57" t="n">
-        <v>91897</v>
+        <v>98780</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583173</v>
+        <v>583046</v>
       </c>
       <c r="R57" t="n">
-        <v>7014589</v>
+        <v>7014393</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6190,6 +6194,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6208,49 +6213,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502243</v>
+        <v>129502216</v>
       </c>
       <c r="B58" t="n">
-        <v>98780</v>
+        <v>91897</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583046</v>
+        <v>583173</v>
       </c>
       <c r="R58" t="n">
-        <v>7014393</v>
+        <v>7014589</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6291,7 +6292,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7605,32 +7605,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129502218</v>
+        <v>129502198</v>
       </c>
       <c r="B72" t="n">
-        <v>91897</v>
+        <v>92317</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583050</v>
+        <v>583192</v>
       </c>
       <c r="R72" t="n">
-        <v>7014244</v>
+        <v>7014120</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7702,45 +7702,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129502198</v>
+        <v>129502242</v>
       </c>
       <c r="B73" t="n">
-        <v>92317</v>
+        <v>98780</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583192</v>
+        <v>583095</v>
       </c>
       <c r="R73" t="n">
-        <v>7014120</v>
+        <v>7014377</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7781,6 +7785,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7799,49 +7804,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129502242</v>
+        <v>129502218</v>
       </c>
       <c r="B74" t="n">
-        <v>98780</v>
+        <v>91897</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583095</v>
+        <v>583050</v>
       </c>
       <c r="R74" t="n">
-        <v>7014377</v>
+        <v>7014244</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7882,7 +7883,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129502190</v>
+        <v>129502188</v>
       </c>
       <c r="B5" t="n">
         <v>91563</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583136</v>
+        <v>583139</v>
       </c>
       <c r="R5" t="n">
-        <v>7014210</v>
+        <v>7014270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,49 +1068,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129502244</v>
+        <v>129502190</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>91563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583177</v>
+        <v>583136</v>
       </c>
       <c r="R6" t="n">
-        <v>7014165</v>
+        <v>7014210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,7 +1147,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1170,45 +1165,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129502188</v>
+        <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>91563</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583139</v>
+        <v>583177</v>
       </c>
       <c r="R7" t="n">
-        <v>7014270</v>
+        <v>7014165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1249,6 +1248,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1267,48 +1267,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129502212</v>
+        <v>129495400</v>
       </c>
       <c r="B8" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583184</v>
+        <v>583183</v>
       </c>
       <c r="R8" t="n">
-        <v>7014173</v>
+        <v>7014604</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1352,44 +1352,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129502199</v>
+        <v>129502212</v>
       </c>
       <c r="B9" t="n">
-        <v>92317</v>
+        <v>92052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583141</v>
+        <v>583184</v>
       </c>
       <c r="R9" t="n">
-        <v>7014282</v>
+        <v>7014173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,48 +1461,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129495400</v>
+        <v>129502199</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>92317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583183</v>
+        <v>583141</v>
       </c>
       <c r="R10" t="n">
-        <v>7014604</v>
+        <v>7014282</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,12 +1546,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129495410</v>
+        <v>129502196</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,37 +2151,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583139</v>
+        <v>583143</v>
       </c>
       <c r="R17" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2225,19 +2225,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495408</v>
+        <v>129495410</v>
       </c>
       <c r="B18" t="n">
         <v>80186</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583204</v>
+        <v>583139</v>
       </c>
       <c r="R18" t="n">
-        <v>7014157</v>
+        <v>7014123</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495406</v>
+        <v>129495408</v>
       </c>
       <c r="B19" t="n">
         <v>80186</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583170</v>
+        <v>583204</v>
       </c>
       <c r="R19" t="n">
-        <v>7014239</v>
+        <v>7014157</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129502196</v>
+        <v>129495406</v>
       </c>
       <c r="B20" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583143</v>
+        <v>583170</v>
       </c>
       <c r="R20" t="n">
-        <v>7014216</v>
+        <v>7014239</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4797,32 +4797,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502247</v>
+        <v>129502209</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>80090</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583367</v>
+        <v>583167</v>
       </c>
       <c r="R44" t="n">
-        <v>7014331</v>
+        <v>7014583</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502251</v>
+        <v>129502226</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,21 +4905,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R45" t="n">
-        <v>7014329</v>
+        <v>7014249</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4973,8 +4973,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -4991,10 +5007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502205</v>
+        <v>129502247</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5002,21 +5018,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5026,10 +5042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583055</v>
+        <v>583367</v>
       </c>
       <c r="R46" t="n">
-        <v>7014357</v>
+        <v>7014331</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,32 +5104,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502209</v>
+        <v>129502251</v>
       </c>
       <c r="B47" t="n">
-        <v>80090</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5123,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583167</v>
+        <v>583055</v>
       </c>
       <c r="R47" t="n">
-        <v>7014583</v>
+        <v>7014329</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5185,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502226</v>
+        <v>129502205</v>
       </c>
       <c r="B48" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5196,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5220,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014249</v>
+        <v>7014357</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,24 +5280,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6310,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502184</v>
+        <v>129502231</v>
       </c>
       <c r="B59" t="n">
-        <v>91563</v>
+        <v>80186</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583134</v>
+        <v>583345</v>
       </c>
       <c r="R59" t="n">
-        <v>7014134</v>
+        <v>7014389</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502231</v>
+        <v>129502227</v>
       </c>
       <c r="B60" t="n">
         <v>80186</v>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583345</v>
+        <v>583045</v>
       </c>
       <c r="R60" t="n">
-        <v>7014389</v>
+        <v>7014432</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,8 +6486,24 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6504,32 +6520,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502227</v>
+        <v>129502184</v>
       </c>
       <c r="B61" t="n">
-        <v>80186</v>
+        <v>91563</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6539,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583045</v>
+        <v>583134</v>
       </c>
       <c r="R61" t="n">
-        <v>7014432</v>
+        <v>7014134</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6583,24 +6599,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -4797,32 +4797,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502209</v>
+        <v>129502247</v>
       </c>
       <c r="B44" t="n">
-        <v>80090</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583167</v>
+        <v>583367</v>
       </c>
       <c r="R44" t="n">
-        <v>7014583</v>
+        <v>7014331</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502226</v>
+        <v>129502251</v>
       </c>
       <c r="B45" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4905,21 +4905,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R45" t="n">
-        <v>7014249</v>
+        <v>7014329</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4973,24 +4973,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5007,10 +4991,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502247</v>
+        <v>129502205</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5018,21 +5002,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5042,10 +5026,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583367</v>
+        <v>583055</v>
       </c>
       <c r="R46" t="n">
-        <v>7014331</v>
+        <v>7014357</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5104,32 +5088,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502251</v>
+        <v>129502209</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>80090</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5139,10 +5123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583055</v>
+        <v>583167</v>
       </c>
       <c r="R47" t="n">
-        <v>7014329</v>
+        <v>7014583</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,10 +5185,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502205</v>
+        <v>129502226</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>80186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5196,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5236,10 +5220,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583055</v>
+        <v>583156</v>
       </c>
       <c r="R48" t="n">
-        <v>7014357</v>
+        <v>7014249</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5280,8 +5264,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>129502244</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129502212</v>
+        <v>129502199</v>
       </c>
       <c r="B9" t="n">
-        <v>92052</v>
+        <v>92317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583184</v>
+        <v>583141</v>
       </c>
       <c r="R9" t="n">
-        <v>7014173</v>
+        <v>7014282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129502199</v>
+        <v>129502212</v>
       </c>
       <c r="B10" t="n">
-        <v>92317</v>
+        <v>92052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583141</v>
+        <v>583184</v>
       </c>
       <c r="R10" t="n">
-        <v>7014282</v>
+        <v>7014173</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2043,48 +2043,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129495405</v>
+        <v>129502196</v>
       </c>
       <c r="B16" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583128</v>
+        <v>583143</v>
       </c>
       <c r="R16" t="n">
-        <v>7014123</v>
+        <v>7014216</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2128,22 +2128,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129502196</v>
+        <v>129495410</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2151,37 +2151,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583143</v>
+        <v>583139</v>
       </c>
       <c r="R17" t="n">
-        <v>7014216</v>
+        <v>7014123</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2225,19 +2225,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129495410</v>
+        <v>129495408</v>
       </c>
       <c r="B18" t="n">
         <v>80186</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583139</v>
+        <v>583204</v>
       </c>
       <c r="R18" t="n">
-        <v>7014123</v>
+        <v>7014157</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129495408</v>
+        <v>129495406</v>
       </c>
       <c r="B19" t="n">
         <v>80186</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583204</v>
+        <v>583170</v>
       </c>
       <c r="R19" t="n">
-        <v>7014157</v>
+        <v>7014239</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2431,32 +2431,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129495406</v>
+        <v>129495405</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>92052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583170</v>
+        <v>583128</v>
       </c>
       <c r="R20" t="n">
-        <v>7014239</v>
+        <v>7014123</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -3207,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129495413</v>
+        <v>129502253</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3238,17 +3238,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583083</v>
+        <v>583143</v>
       </c>
       <c r="R28" t="n">
-        <v>7014314</v>
+        <v>7014258</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,19 +3292,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129502253</v>
+        <v>129495413</v>
       </c>
       <c r="B29" t="n">
         <v>79081</v>
@@ -3335,17 +3335,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583143</v>
+        <v>583083</v>
       </c>
       <c r="R29" t="n">
-        <v>7014258</v>
+        <v>7014314</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,12 +3389,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3498,48 +3498,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129502213</v>
+        <v>129495411</v>
       </c>
       <c r="B31" t="n">
-        <v>92052</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583198</v>
+        <v>583068</v>
       </c>
       <c r="R31" t="n">
-        <v>7014144</v>
+        <v>7014294</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3577,26 +3577,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129502224</v>
+        <v>129495409</v>
       </c>
       <c r="B32" t="n">
         <v>80186</v>
@@ -3627,17 +3626,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getklövsmyran, Ång</t>
+          <t>Runåberg, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583151</v>
+        <v>583174</v>
       </c>
       <c r="R32" t="n">
-        <v>7014252</v>
+        <v>7014111</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3675,41 +3674,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129495411</v>
+        <v>129502224</v>
       </c>
       <c r="B33" t="n">
         <v>80186</v>
@@ -3740,17 +3723,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583068</v>
+        <v>583151</v>
       </c>
       <c r="R33" t="n">
-        <v>7014294</v>
+        <v>7014252</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3788,66 +3771,82 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129495409</v>
+        <v>129502213</v>
       </c>
       <c r="B34" t="n">
-        <v>80186</v>
+        <v>92052</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Runåberg, Ång</t>
+          <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583174</v>
+        <v>583198</v>
       </c>
       <c r="R34" t="n">
-        <v>7014111</v>
+        <v>7014144</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3885,28 +3884,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129502192</v>
+        <v>129502234</v>
       </c>
       <c r="B35" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583114</v>
+        <v>583081</v>
       </c>
       <c r="R35" t="n">
-        <v>7014270</v>
+        <v>7014394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129502234</v>
+        <v>129502192</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583081</v>
+        <v>583114</v>
       </c>
       <c r="R36" t="n">
-        <v>7014394</v>
+        <v>7014270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4307,32 +4307,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129502182</v>
+        <v>129502236</v>
       </c>
       <c r="B39" t="n">
-        <v>91563</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583174</v>
+        <v>583058</v>
       </c>
       <c r="R39" t="n">
-        <v>7014597</v>
+        <v>7014379</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129502236</v>
+        <v>129502235</v>
       </c>
       <c r="B40" t="n">
         <v>80186</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583058</v>
+        <v>583064</v>
       </c>
       <c r="R40" t="n">
-        <v>7014379</v>
+        <v>7014430</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4501,32 +4501,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129502235</v>
+        <v>129502182</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>91563</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583064</v>
+        <v>583174</v>
       </c>
       <c r="R41" t="n">
-        <v>7014430</v>
+        <v>7014597</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502215</v>
+        <v>129502209</v>
       </c>
       <c r="B43" t="n">
-        <v>91897</v>
+        <v>80090</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583175</v>
+        <v>583167</v>
       </c>
       <c r="R43" t="n">
-        <v>7014579</v>
+        <v>7014583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,10 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502247</v>
+        <v>129502226</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4808,21 +4808,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583367</v>
+        <v>583156</v>
       </c>
       <c r="R44" t="n">
-        <v>7014331</v>
+        <v>7014249</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,8 +4876,24 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4894,7 +4910,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502251</v>
+        <v>129502247</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -4929,10 +4945,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583055</v>
+        <v>583367</v>
       </c>
       <c r="R45" t="n">
-        <v>7014329</v>
+        <v>7014331</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4991,10 +5007,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502205</v>
+        <v>129502251</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5002,21 +5018,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5029,7 +5045,7 @@
         <v>583055</v>
       </c>
       <c r="R46" t="n">
-        <v>7014357</v>
+        <v>7014329</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,32 +5104,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502209</v>
+        <v>129502215</v>
       </c>
       <c r="B47" t="n">
-        <v>80090</v>
+        <v>91897</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5123,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583167</v>
+        <v>583175</v>
       </c>
       <c r="R47" t="n">
-        <v>7014583</v>
+        <v>7014579</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5185,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502226</v>
+        <v>129502205</v>
       </c>
       <c r="B48" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5196,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5220,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583156</v>
+        <v>583055</v>
       </c>
       <c r="R48" t="n">
-        <v>7014249</v>
+        <v>7014357</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,24 +5280,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502194</v>
+        <v>129502206</v>
       </c>
       <c r="B49" t="n">
-        <v>91599</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583050</v>
+        <v>583074</v>
       </c>
       <c r="R49" t="n">
-        <v>7014242</v>
+        <v>7014351</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502211</v>
+        <v>129502230</v>
       </c>
       <c r="B50" t="n">
-        <v>92052</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583055</v>
+        <v>583330</v>
       </c>
       <c r="R50" t="n">
-        <v>7014372</v>
+        <v>7014339</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502230</v>
+        <v>129502194</v>
       </c>
       <c r="B51" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583330</v>
+        <v>583050</v>
       </c>
       <c r="R51" t="n">
-        <v>7014339</v>
+        <v>7014242</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502206</v>
+        <v>129502211</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>92052</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583074</v>
+        <v>583055</v>
       </c>
       <c r="R52" t="n">
-        <v>7014351</v>
+        <v>7014372</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,49 +6111,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129502243</v>
+        <v>129502216</v>
       </c>
       <c r="B57" t="n">
-        <v>98780</v>
+        <v>91897</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583046</v>
+        <v>583173</v>
       </c>
       <c r="R57" t="n">
-        <v>7014393</v>
+        <v>7014589</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,7 +6190,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6213,45 +6208,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129502216</v>
+        <v>129502243</v>
       </c>
       <c r="B58" t="n">
-        <v>91897</v>
+        <v>98790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583173</v>
+        <v>583046</v>
       </c>
       <c r="R58" t="n">
-        <v>7014589</v>
+        <v>7014393</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6292,6 +6291,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6714,32 +6714,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502232</v>
+        <v>129502239</v>
       </c>
       <c r="B63" t="n">
-        <v>80186</v>
+        <v>58106</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583323</v>
+        <v>583168</v>
       </c>
       <c r="R63" t="n">
-        <v>7014267</v>
+        <v>7014188</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502239</v>
+        <v>129502232</v>
       </c>
       <c r="B64" t="n">
-        <v>58106</v>
+        <v>80186</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583168</v>
+        <v>583323</v>
       </c>
       <c r="R64" t="n">
-        <v>7014188</v>
+        <v>7014267</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6908,10 +6908,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129502246</v>
+        <v>129502229</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583392</v>
+        <v>583107</v>
       </c>
       <c r="R65" t="n">
-        <v>7014349</v>
+        <v>7014481</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6979,6 +6979,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7005,10 +7010,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129502229</v>
+        <v>129502246</v>
       </c>
       <c r="B66" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7016,21 +7021,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7040,10 +7045,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583107</v>
+        <v>583392</v>
       </c>
       <c r="R66" t="n">
-        <v>7014481</v>
+        <v>7014349</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7076,11 +7081,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7107,10 +7107,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129502248</v>
+        <v>129502180</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>83052</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7118,21 +7118,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583117</v>
+        <v>583051</v>
       </c>
       <c r="R67" t="n">
-        <v>7014262</v>
+        <v>7014327</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7204,10 +7204,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129502180</v>
+        <v>129502248</v>
       </c>
       <c r="B68" t="n">
-        <v>83052</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7215,21 +7215,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583051</v>
+        <v>583117</v>
       </c>
       <c r="R68" t="n">
-        <v>7014327</v>
+        <v>7014262</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7506,7 +7506,7 @@
         <v>129502240</v>
       </c>
       <c r="B71" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>129502242</v>
       </c>
       <c r="B73" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129502193</v>
+        <v>129502250</v>
       </c>
       <c r="B75" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583174</v>
+        <v>583068</v>
       </c>
       <c r="R75" t="n">
-        <v>7014589</v>
+        <v>7014344</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129502250</v>
+        <v>129502193</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583068</v>
+        <v>583174</v>
       </c>
       <c r="R76" t="n">
-        <v>7014344</v>
+        <v>7014589</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8685,7 +8685,7 @@
         <v>129502241</v>
       </c>
       <c r="B83" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 6059-2024 artfynd.xlsx
+++ b/artfynd/A 6059-2024 artfynd.xlsx
@@ -4700,32 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129502209</v>
+        <v>129502205</v>
       </c>
       <c r="B43" t="n">
-        <v>80090</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583167</v>
+        <v>583055</v>
       </c>
       <c r="R43" t="n">
-        <v>7014583</v>
+        <v>7014357</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,32 +4797,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129502226</v>
+        <v>129502209</v>
       </c>
       <c r="B44" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583156</v>
+        <v>583167</v>
       </c>
       <c r="R44" t="n">
-        <v>7014249</v>
+        <v>7014583</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4876,24 +4876,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -4910,10 +4894,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129502247</v>
+        <v>129502226</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4921,21 +4905,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4945,10 +4929,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583367</v>
+        <v>583156</v>
       </c>
       <c r="R45" t="n">
-        <v>7014331</v>
+        <v>7014249</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4989,8 +4973,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5007,7 +5007,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129502251</v>
+        <v>129502247</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583055</v>
+        <v>583367</v>
       </c>
       <c r="R46" t="n">
-        <v>7014329</v>
+        <v>7014331</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129502215</v>
+        <v>129502251</v>
       </c>
       <c r="B47" t="n">
-        <v>91897</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5115,21 +5115,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583175</v>
+        <v>583055</v>
       </c>
       <c r="R47" t="n">
-        <v>7014579</v>
+        <v>7014329</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129502205</v>
+        <v>129502215</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>91897</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583055</v>
+        <v>583175</v>
       </c>
       <c r="R48" t="n">
-        <v>7014357</v>
+        <v>7014579</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5298,10 +5298,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129502206</v>
+        <v>129502194</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583074</v>
+        <v>583050</v>
       </c>
       <c r="R49" t="n">
-        <v>7014351</v>
+        <v>7014242</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5395,32 +5395,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129502230</v>
+        <v>129502211</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>92052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583330</v>
+        <v>583055</v>
       </c>
       <c r="R50" t="n">
-        <v>7014339</v>
+        <v>7014372</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129502194</v>
+        <v>129502230</v>
       </c>
       <c r="B51" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583050</v>
+        <v>583330</v>
       </c>
       <c r="R51" t="n">
-        <v>7014242</v>
+        <v>7014339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5589,32 +5589,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129502211</v>
+        <v>129502206</v>
       </c>
       <c r="B52" t="n">
-        <v>92052</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5624,10 +5624,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583055</v>
+        <v>583074</v>
       </c>
       <c r="R52" t="n">
-        <v>7014372</v>
+        <v>7014351</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6310,32 +6310,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129502231</v>
+        <v>129502184</v>
       </c>
       <c r="B59" t="n">
-        <v>80186</v>
+        <v>91563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583345</v>
+        <v>583134</v>
       </c>
       <c r="R59" t="n">
-        <v>7014389</v>
+        <v>7014134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129502227</v>
+        <v>129502231</v>
       </c>
       <c r="B60" t="n">
         <v>80186</v>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583045</v>
+        <v>583345</v>
       </c>
       <c r="R60" t="n">
-        <v>7014432</v>
+        <v>7014389</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6486,24 +6486,8 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6520,32 +6504,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129502184</v>
+        <v>129502227</v>
       </c>
       <c r="B61" t="n">
-        <v>91563</v>
+        <v>80186</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6539,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583134</v>
+        <v>583045</v>
       </c>
       <c r="R61" t="n">
-        <v>7014134</v>
+        <v>7014432</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6599,8 +6583,24 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129502249</v>
+        <v>129502232</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583114</v>
+        <v>583323</v>
       </c>
       <c r="R62" t="n">
-        <v>7014512</v>
+        <v>7014267</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,32 +6714,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129502239</v>
+        <v>129502249</v>
       </c>
       <c r="B63" t="n">
-        <v>58106</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583168</v>
+        <v>583114</v>
       </c>
       <c r="R63" t="n">
-        <v>7014188</v>
+        <v>7014512</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6811,32 +6811,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129502232</v>
+        <v>129502239</v>
       </c>
       <c r="B64" t="n">
-        <v>80186</v>
+        <v>58106</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583323</v>
+        <v>583168</v>
       </c>
       <c r="R64" t="n">
-        <v>7014267</v>
+        <v>7014188</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7406,45 +7406,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129502245</v>
+        <v>129502240</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583158</v>
+        <v>583138</v>
       </c>
       <c r="R70" t="n">
-        <v>7014222</v>
+        <v>7014124</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7485,6 +7489,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7503,49 +7508,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129502240</v>
+        <v>129502245</v>
       </c>
       <c r="B71" t="n">
-        <v>98790</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getklövsmyran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583138</v>
+        <v>583158</v>
       </c>
       <c r="R71" t="n">
-        <v>7014124</v>
+        <v>7014222</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7586,7 +7587,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129502214</v>
+        <v>129502233</v>
       </c>
       <c r="B79" t="n">
-        <v>91897</v>
+        <v>80186</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583052</v>
+        <v>583068</v>
       </c>
       <c r="R79" t="n">
-        <v>7014374</v>
+        <v>7014398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8360,6 +8360,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>apotecier</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8386,10 +8391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129502256</v>
+        <v>129502214</v>
       </c>
       <c r="B80" t="n">
-        <v>82918</v>
+        <v>91897</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8397,21 +8402,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8421,10 +8426,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583110</v>
+        <v>583052</v>
       </c>
       <c r="R80" t="n">
-        <v>7014519</v>
+        <v>7014374</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8483,10 +8488,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129502233</v>
+        <v>129502256</v>
       </c>
       <c r="B81" t="n">
-        <v>80186</v>
+        <v>82918</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8494,21 +8499,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8518,10 +8523,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583068</v>
+        <v>583110</v>
       </c>
       <c r="R81" t="n">
-        <v>7014398</v>
+        <v>7014519</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8554,11 +8559,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>apotecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
